--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -198,7 +198,7 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">35 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
+          <t xml:space="preserve">36 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
         </is>
       </c>
     </row>
@@ -210,7 +210,7 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">25 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
+          <t xml:space="preserve">26 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
         </is>
       </c>
     </row>
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">24 ไฟล์</t>
+          <t xml:space="preserve">25 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -234,7 +234,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">38 ไฟล์</t>
+          <t xml:space="preserve">39 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">16 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">17 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">70 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 66 ครั้ง</t>
+          <t xml:space="preserve">74 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 70 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -2890,6 +2890,155 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บอกให้ชัดว่ากำลังใช้รุ่นไหน และหาหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- เพิ่ม APP_BUILD ใน lib/constants.js แสดงท้ายแถบเมนูซ้าย
+มีไว้ตอบคำถามเดียว: "หน้าจอที่เปิดอยู่เป็นรุ่นที่เพิ่งแก้ หรือรุ่นเก่าในแคช"
+ถ้าเลขบนหน้าจอไม่ตรงกับที่ประกาศในไฟล์ แปลว่าเบราว์เซอร์ยังถือของเก่า
+หรือ Vercel ยัง deploy ไม่เสร็จ ซึ่งคนละเรื่องกับ "ยังไม่ได้ทำฟีเจอร์"
+ต้องอัปเดตเลขนี้ทุกครั้งที่ส่งงานรอบใหม่
+- Quick View เดิมไม่มีตัวแจ้งเมื่อฐานข้อมูลยังไม่มีตารางของฟีเจอร์นี้
+จึงขึ้นตัวเลขศูนย์เฉย ๆ ซึ่งดูไม่ออกว่าเป็นเพราะยังไม่มีข้อมูล
+หรือเพราะระบบยังไม่พร้อม คนใช้เข้าใจว่าหน้าจอนี้ยังไม่ได้ทำ
+แก้ให้ขึ้น SetupNotice แบบเดียวกับหน้ากำหนดเป้าขายและพนักงานขาย
+- หน้ากำหนดเป้าขายเพิ่มปุ่ม "โหลดจาก Excel" พาไปหน้านำเข้าข้อมูล
+พร้อมเลือกชุด "เป้าขาย" ให้เลย เพราะเป้าทั้งปีมีหลายสิบแถว
+กรอกทีละแถวช้ากว่าทำในไฟล์มาก และเดิมต้องไปหาเมนูเองแล้วเลือกชุดเอง
+ซึ่งเลือกผิดชุดได้ง่าย
+- Quick View เพิ่มปุ่ม "ตั้งเป้าขาย" พาไปหน้ากำหนดเป้าขาย
+เพราะคนที่เห็นว่ายังไม่มีเป้ามาเทียบ อยากไปตั้งต่อทันที
+- navigate(id, arg) ของ Shell ส่งค่าเริ่มต้นให้หน้าปลายทางได้
+ตอนนี้ใช้กับหน้านำเข้าข้อมูลเท่านั้น ชุดที่ส่งมาไม่มีอยู่จริงให้ถอยไปใช้ชุดแรก
+ไม่ใช่ขึ้นหน้าว่าง</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่ บอกว่าซ่อนกี่หน้าไว้</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- การหุบกลุ่มเมนูจำไว้ในเครื่องผู้ใช้ (localStorage)
+พอเพิ่มเมนูใหม่เข้าไปในกลุ่มที่ผู้ใช้หุบไว้ก่อนหน้านี้
+หน้าใหม่จะไม่โผล่มาให้เห็นเลย จนเข้าใจว่ายังไม่ได้ทำฟีเจอร์นั้น
+(เกิดขึ้นจริงกับหน้า Quick View ในกลุ่ม "ภาพรวม"
+และหน้ากำหนดเป้าขายในกลุ่ม "งานขาย")
+- แก้ให้หัวกลุ่มที่หุบอยู่แสดงจำนวนหน้าที่ซ่อนไว้เป็นตัวเลข
+เห็นแล้วรู้ทันทีว่ายังมีของอยู่ข้างใน แค่ยังไม่ได้กางออก
+- ไม่แก้ด้วยการกางกลุ่มให้เองเมื่อมีเมนูใหม่ เพราะคนที่ตั้งใจหุบไว้
+จะโดนกางคืนทุกครั้งที่อัปเดต ซึ่งน่ารำคาญกว่าปัญหาที่จะแก้</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ build ล้ม</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อาการที่ผู้ใช้เจอ: หน้าจอใหม่ตั้งแต่รอบ (68) เป็นต้นมาไม่โผล่บนเว็บเลย
+(Quick View · กำหนดเป้าขาย · กำหนดพนักงานขาย · ออกแบบฟอร์มพิมพ์)
+ทั้งที่โค้ดอยู่ครบใน GitHub และตรวจด้วยตาแล้วไม่พบอะไรผิด
+สาเหตุจริง:
+- lib/api.js ประกาศ salesReady สองครั้งในไฟล์เดียวกัน
+ครั้งแรก (บรรทัด 1040) = ตารางขายหน้าร้าน sales / sale_items
+ครั้งที่สอง (เพิ่มในรอบ 68) = ตารางพนักงานขาย salespersons
+- const ชื่อเดิมซ้ำในขอบเขตเดียวกันเป็น SyntaxError ตั้งแต่ตอน parse
+"Identifier 'salesReady' has already been declared"
+ไม่ใช่แค่ฟังก์ชันนั้นพัง แต่ทั้งไฟล์ใช้ไม่ได้ และทุกหน้าจอ import
+ไฟล์นี้ผ่าน lib/store.js จึงพังตามหมดทั้งระบบ
+- ผลคือ next build ล้ม -&gt; Vercel ไม่ deploy รุ่นใหม่ -&gt;
+เว็บที่ใช้งานอยู่ค้างอยู่กับรุ่นก่อนรอบ 68 ไปเรื่อย ๆ
+ทุกงานที่ทำหลังจากนั้นจึงไม่มีผลกับเว็บที่ผู้ใช้เปิดอยู่เลย
+บั๊กที่ซ่อนอยู่อีกตัวจากเรื่องเดียวกัน:
+- lib/store.js ใส่คีย์ salesReady ในวัตถุเดียวกันสองครั้ง
+ตัวหลังทับตัวหน้าเงียบ ๆ (คีย์ซ้ำในวัตถุไม่ใช่ error ของ JavaScript)
+ทำให้หน้า POS ที่ถาม inv.salesReady ได้คำตอบของตารางพนักงานขายแทน
+ซึ่งจะทำให้หน้า POS ขึ้นข้อความให้ไปตั้งค่าผิดเรื่อง
+การแก้:
+- เปลี่ยนชื่อตัวที่เพิ่มใหม่เป็น salespersonsReady ให้ตรงกับตารางที่ตรวจ
+แก้ทั้ง lib/api.js · lib/store.js · components/views/Salespersons.js
+- เพิ่มตัวตรวจหมวด 17: ไม่มีชื่อซ้ำที่ทำให้ทั้งไฟล์ใช้ไม่ได้
+ตรวจสองอย่าง — ประกาศ const/let/function/class ซ้ำในไฟล์เดียวกัน
+และคีย์ซ้ำในวัตถุที่ store แจกให้หน้าจอ
+ทดสอบแล้วว่าจับบั๊กตัวนี้ได้จริงทั้งสองจุด (ใส่บั๊กกลับเข้าไปแล้วต้องไม่ผ่าน)
+บทเรียนที่ต้องจำ:
+- เครื่องนี้ลง node_modules ไม่ได้ จึงรัน next build ตรวจเองไม่ได้
+ตัวตรวจใน tools/check.mjs จึงต้องรับหน้าที่แทน "ตัวคอมไพล์"
+ทุกความผิดพลาดที่คอมไพเลอร์จับได้แต่ตาคนมองข้าม ต้องมีหมวดตรวจของตัวเอง
+- ตรวจว่า "โค้ดมีอยู่จริง" ไม่เท่ากับตรวจว่า "โค้ดใช้งานได้"
+รอบก่อนหน้าตรวจครบ 50 ข้อว่าไฟล์ เมนู และตารางมีครบ ซึ่งผ่านหมด
+แต่ไม่มีข้อไหนตรวจว่าไฟล์ยัง parse ผ่านหรือเปล่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าสินค้า</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- หน้าจอใหม่ "กลุ่ม ยี่ห้อ ประเภทสินค้า" (การจัดการระบบ)
+รูปแบบเดียวกับหน้ากำหนดพนักงานขาย: รหัส + ชื่อ เพิ่ม แก้ไข ลบ
+ปิดใช้งานได้ ส่งออก CSV/Excel ได้ และนำเข้าจาก Excel ได้
+- สามมิติอยู่หน้าจอเดียวแล้วสลับด้วยแท็บ ไม่แยกสามเมนู
+เพราะใช้ตารางเดียวกัน หน้าตาเหมือนกันทุกช่อง ต่างกันแค่ความหมาย
+แยกสามเมนูคือเมนูยาวขึ้นสามรายการเพื่อฟอร์มที่เหมือนกันเป๊ะ
+และคนที่ตั้งกลุ่มเสร็จมักตั้งยี่ห้อต่อทันที สลับแท็บเร็วกว่าย้อนหาเมนู
+- ตารางเดียว (product_terms) แยกมิติด้วยคอลัมน์ dim ไม่ทำสามตาราง
+แยกสามตาราง = ตัวแปลง หน้าจอ ตัวนำเข้า และการสำรองข้อมูลซ้ำสามชุด
+แก้กติกาทีต้องไล่แก้สามที่ แล้วจะมีที่หนึ่งที่ลืมเสมอ
+เพิ่มมิติที่สี่วันหลัง (เช่น รุ่นสินค้า) เพิ่มค่า dim ค่าเดียวก็จบ
+กติกาสำคัญที่ต้องเข้าใจตรงกัน:
+- ตัวสินค้ายังเก็บ "ชื่อ" ไว้เหมือนเดิม ไม่ได้เปลี่ยนไปเก็บรหัส
+เพราะระบบเก็บเป็นชื่อมาก่อน และเป้าขายจับคู่ด้วยชื่อเหมือนกัน
+เปลี่ยนไปเก็บรหัสเมื่อไร สินค้าและเป้าขายเดิมจะจับคู่ไม่ติดทั้งหมดทันที
+ตารางนี้จึงเป็น "ทะเบียนให้เลือก" ไม่ใช่กุญแจอ้างอิง — จงใจไม่ผูก foreign key
+- เพราะสินค้าเก็บชื่อ ทะเบียนจึงกัน "ชื่อซ้ำ" ในมิติเดียวกันด้วย ไม่ใช่กันแค่รหัส
+สองรหัสชื่อเดียวกันจะแยกไม่ออกว่าสินค้าหมายถึงรายการไหน
+และเป้าขายจะนับรวมกันทั้งคู่
+- รหัสซ้ำข้ามมิติได้ (B01 เป็นได้ทั้งกลุ่มและยี่ห้อ) unique index จึงเป็น
+(dim, lower(code)) และกุญแจกันซ้ำตอนนำเข้าเป็น keyFields = [dim, code]
+- ลบรายการในทะเบียนแล้วสินค้าไม่ถูกแตะ ค่าเดิมยังอยู่ครบและเป้ายังจับคู่ได้
+แค่ค่านั้นกลายเป็น "ยังไม่ได้จดทะเบียน" ในช่องเลือก
+- หน้าแก้ไขสินค้า: สามช่องนี้เปลี่ยนจากพิมพ์อิสระ (datalist)
+เป็นช่องกดเลือกที่พิมพ์ค้นหาบางส่วนของรหัสหรือชื่อได้ (SearchSelect)
+เพราะพิมพ์เองทำให้ได้ชื่อที่สะกดไม่ตรงกันทีละนิด
+แล้วเป้าขายจะจับคู่ไม่ติดโดยไม่มีใครรู้ว่าเพราะอะไร
+- รายการในช่องเลือกรวมสองแหล่ง: ทะเบียนที่ตั้งไว้ กับค่าที่สินค้าตัวอื่น
+ใช้อยู่แล้วแต่ยังไม่ได้จดทะเบียน (ติดป้าย "ยังไม่ได้จดทะเบียน")
+ถ้าเอาเฉพาะทะเบียน ค่าที่พิมพ์ไว้ก่อนมีหน้านี้จะหายจากรายการ
+กลายเป็นบังคับให้ตั้งใหม่ทั้งระบบก่อนถึงจะแก้สินค้าเก่าได้
+และค่าที่สินค้าตัวที่กำลังแก้ใช้อยู่ต้องอยู่ในรายการเสมอ แม้ไม่มีที่ไหนแล้ว
+- หน้าทะเบ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2927,12 +3076,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -2944,12 +3093,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -2961,12 +3110,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -2978,12 +3127,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -2995,12 +3144,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3161,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3178,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3195,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3212,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3229,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3246,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3263,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3280,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3148,12 +3297,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3165,12 +3314,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3182,80 +3331,80 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3267,12 +3416,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3284,80 +3433,80 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3369,12 +3518,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3535,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3403,12 +3552,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3420,12 +3569,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3586,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3603,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3620,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3637,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -3505,12 +3654,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3671,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -3539,12 +3688,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3705,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3722,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3739,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -3607,80 +3756,80 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3841,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3858,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -3726,12 +3875,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -3743,12 +3892,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -3760,12 +3909,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -3777,12 +3926,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -3794,131 +3943,131 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -3930,80 +4079,80 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4015,27 +4164,95 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">f304aa0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1e98b03</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">4598764</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr" s="2">
+      <c r="B71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr" s="2">
+      <c r="C71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -4129,7 +4346,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>392</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4">
@@ -4429,7 +4646,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16">
@@ -4754,7 +4971,7 @@
         </is>
       </c>
       <c r="E28">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29">
@@ -4829,7 +5046,7 @@
         </is>
       </c>
       <c r="E31">
-        <v>815</v>
+        <v>857</v>
       </c>
     </row>
     <row r="32">
@@ -4865,46 +5082,46 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Password.js</t>
+          <t xml:space="preserve">components/views/ProductTerms.js</t>
         </is>
       </c>
       <c r="E33">
-        <v>170</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Reports.js</t>
+          <t xml:space="preserve">components/views/Password.js</t>
         </is>
       </c>
       <c r="E34">
-        <v>1887</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35">
@@ -4915,21 +5132,21 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุป</t>
+          <t xml:space="preserve">รายงาน</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Graphs.js</t>
+          <t xml:space="preserve">components/views/Reports.js</t>
         </is>
       </c>
       <c r="E35">
-        <v>499</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="36">
@@ -4940,20 +5157,45 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">กราฟสรุป</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Graphs.js</t>
+        </is>
+      </c>
+      <c r="E36">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สร้างรายงาน</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr" s="2">
+      <c r="C37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">เลือกคอลัมน์และจัดรูปแบบเอง</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr" s="2">
+      <c r="D37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">components/views/ReportBuilder.js</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E37">
         <v>537</v>
       </c>
     </row>
@@ -5415,12 +5657,7 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">salespersons</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">พนักงานขาย</t>
+          <t xml:space="preserve">product_terms</t>
         </is>
       </c>
       <c r="C23">
@@ -5428,65 +5665,85 @@
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, code, name, phone, note, active, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, dim, code, name, note, active, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">sales_targets</t>
+          <t xml:space="preserve">salespersons</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขายตามงวดและมิติสินค้า</t>
+          <t xml:space="preserve">พนักงานขาย</t>
         </is>
       </c>
       <c r="C24">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, year, month, sales_id, grp, brand, kind, amount, qty, note, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, code, name, phone, note, active, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">sql_connections</t>
+          <t xml:space="preserve">sales_targets</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การเชื่อมต่อฐานข้อมูลภายนอกที่บันทึกไว้ (SQL Server / MySQL / Access)</t>
+          <t xml:space="preserve">เป้าขายตามงวดและมิติสินค้า</t>
         </is>
       </c>
       <c r="C25">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, name, kind, server, port, file_path, db_name, login, password, encrypt, trust_cert, bridge_url, note, is_default, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, year, month, sales_id, grp, brand, kind, amount, qty, note, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">sql_connections</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การเชื่อมต่อฐานข้อมูลภายนอกที่บันทึกไว้ (SQL Server / MySQL / Access)</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>18</v>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, name, kind, server, port, file_path, db_name, login, password, encrypt, trust_cert, bridge_url, note, is_default, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">screen_perms</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="2">
+      <c r="B27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สิทธิการใช้งานรายหน้าจอ (ดู / แก้ไข / เปลี่ยนวันที่)</t>
         </is>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>6</v>
       </c>
-      <c r="D26" t="inlineStr" s="2">
+      <c r="D27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">id, can_view, can_edit, can_date, created_at, row_order</t>
         </is>
@@ -5533,7 +5790,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>1836</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="3">
@@ -5548,7 +5805,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4">
@@ -5624,7 +5881,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -5744,7 +6001,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>211</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17">
@@ -5780,105 +6037,120 @@
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/reportData.js</t>
+          <t xml:space="preserve">lib/productTerms.js</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
+          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C19">
-        <v>466</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/store.js</t>
+          <t xml:space="preserve">lib/reportData.js</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
+          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
         </is>
       </c>
       <c r="C20">
-        <v>968</v>
+        <v>466</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/supabase.js</t>
+          <t xml:space="preserve">lib/store.js</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
         </is>
       </c>
       <c r="C21">
-        <v>389</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/targets.js</t>
+          <t xml:space="preserve">lib/supabase.js</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
+          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C22">
-        <v>128</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/thaiAddress.js</t>
+          <t xml:space="preserve">lib/targets.js</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
         </is>
       </c>
       <c r="C23">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/thaiAddress.js</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
         </is>
       </c>
       <c r="C24">
-        <v>321</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/xlsx.js</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/xlsxRead.js</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="2">
+      <c r="B26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
         </is>
       </c>
-      <c r="C25">
+      <c r="C26">
         <v>223</v>
       </c>
     </row>
@@ -6183,6 +6455,18 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไม่มีชื่อซ้ำที่ทำให้ทั้งไฟล์ใช้ไม่ได้</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -78,7 +78,7 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ultra ERP — ระบบควบคุมสินค้าคงคลัง</t>
+          <t xml:space="preserve">One for All Ultra — ระบบควบคุมสินค้าคงคลัง</t>
         </is>
       </c>
     </row>
@@ -102,7 +102,7 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
     </row>
@@ -198,7 +198,7 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
+          <t xml:space="preserve">40 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
         </is>
       </c>
     </row>
@@ -210,7 +210,7 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">26 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
+          <t xml:space="preserve">29 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
         </is>
       </c>
     </row>
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">25 ไฟล์</t>
+          <t xml:space="preserve">26 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -234,7 +234,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39 ไฟล์</t>
+          <t xml:space="preserve">43 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">74 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 70 ครั้ง</t>
+          <t xml:space="preserve">75 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 71 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่ + เลขที่บิล POS</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra + ธีมสี + ช่วงวันที่ + เลขที่บิล POS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">- เอาชื่อหน่วยงานออกทั้งหมด เปลี่ยนเป็นชื่อโปรแกรม Ultra ERP
+          <t xml:space="preserve">- เอาชื่อหน่วยงานออกทั้งหมด เปลี่ยนเป็นชื่อโปรแกรม One for All Ultra
 แตะทั้ง layout, manifest, แถบเมนู, หน้าล็อกอิน, หัวกระดาษพิมพ์,
 ใบเสร็จ, หน้าออฟไลน์, ความรู้ของผู้ช่วย AI และรูปการ์ดพรีวิวลิงก์
 มีเทสต์กวาดทุกไฟล์ ถ้ายังเหลือคำเดิมที่ไหนจะ fail
@@ -3039,6 +3039,54 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยนชื่อโปรแกรมเป็น One for All Ultra และเพิ่มระบบ CRM เฟส 1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ชื่อใหม่: One for All Ultra · ตัวย่อ OFAU · ชื่อไทย หนึ่งเดียวเพื่อทุกสิ่ง
+- แก้ชื่อ 16 ไฟล์ (หัวเรื่องเว็บ · manifest · หน้าเข้าสู่ระบบ · แถบเมนู ·
+หัวกระดาษที่พิมพ์ · ไฟล์สำรองข้อมูล · เอกสารทั้งหมด)
+- short_name ของ manifest ใช้ "OFAU" เพราะ Android ตัดชื่อที่ยาวเกิน
+ราว 12 ตัวอักษรบนหน้าจอโฮม
+- ไม่แก้ Docs/standalone-index.html เพราะเป็นรุ่นแรกที่เก็บไว้อ้างอิง
+ของที่บันทึกว่า "เคยเป็นอย่างไร" ไม่ควรถูกแก้ย้อนหลัง
+- การกู้คืนไฟล์สำรองไม่ได้ตรวจชื่อโปรแกรมในไฟล์ (ตรวจจากตารางที่มี)
+ไฟล์สำรองที่ทำไว้ก่อนเปลี่ยนชื่อจึงยังกู้คืนได้ตามปกติ
+งานลูกค้าสัมพันธ์ (CRM) เฟส 1 — เมนูกลุ่มใหม่ 4 หน้าจอ
+- โอกาสการขาย (Pipeline) · บันทึกกิจกรรม · ลูกค้าเป้าหมาย · ภาพรวมลูกค้า
+- ตารางใหม่ 3 ตาราง: crm_leads · crm_deals · crm_activities (รวม 29 ตาราง)
+- รายงานเพิ่ม 4 แท็บในหน้ารายงานเดิม ไม่ทำหน้ารายงานแยก:
+กรวยการขาย · กิจกรรมการติดต่อ · ชนะ-แพ้และเหตุผล · ลูกค้าเงียบ
+การตัดสินใจที่สำคัญ:
+- ไม่เอาผู้สนใจ (lead) ไปปนกับทะเบียนลูกค้า
+customers ถูกใบขายอ้างแบบ restrict และรหัสลูกค้าห้ามซ้ำ
+ปนกันเมื่อไร ทะเบียนจะเต็มไปด้วยรายชื่อที่ไม่เคยซื้อ
+และรายงานทุกตัวที่นับ "จำนวนลูกค้า" จะเพี้ยนโดยไม่มีใครสังเกต
+แปลงเป็นลูกค้าได้ปุ่มเดียว แล้วผูกกลับมาที่ผู้สนใจรายเดิม
+ไม่ย้ายแล้วลบทิ้ง เพราะประวัติว่ามาจากช่องทางไหนคือสิ่งที่
+รายงานอัตราการแปลงใช้ทั้งหมด
+- ดีลผูกได้ทั้งกับลูกค้าและกับผู้สนใจ เพราะของจริงคุยกันก่อนเปิดเป็นลูกค้าเสมอ
+จงใจไม่ใส่ check ในฐานข้อมูลว่า "ต้องมีอย่างน้อยหนึ่งอย่าง"
+เพราะทั้งสองคอลัมน์เป็น on delete set null พอลบผู้สนใจ
+ฐานข้อมูลจะตั้งค่า null แล้วชน check ผลคือลบผู้สนใจไม่ได้
+พร้อม error ที่อ่านไม่รู้เรื่องว่าเกี่ยวอะไรกับดีล บังคับที่หน้าจอแทน
+- ปิดดีลว่าชนะแล้วไม่สร้างใบขายให้อัตโนมัติ ใบขายตัดสต็อกจริง
+ต้องให้คนตรวจก่อนเสมอ หน้าจอจึงมีแค่ปุ่มพาไปหน้าขาย
+- ปิดดีลว่าแพ้ต้องกรอกเหตุผล ไม่งั้นรายงานแพ้-ชนะไม่มีอะไรให้เรียนรู้
+- ไม่ทำบอร์ดลากวาง ใช้ปุ่มเปลี่ยนขั้นแทน เพราะลากวางใช้บนมือถือแทบไม่ได้
+(พนักงานขายอยู่นอกออฟฟิศเป็นหลัก) และการลากถามเหตุผลตอนแพ้ไม่ได้
+- นัดครั้งถัดไปเก็บในแถวเดียวกับการติดต่อครั้งนั้น ไม่แยกตารางนัดหมาย
+เพราะนัดเกิดจากการคุยครั้งก่อนเสมอ แ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3076,12 +3124,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3093,12 +3141,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3158,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3175,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3192,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3209,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3226,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3243,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3260,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3277,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3294,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3311,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3328,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3345,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3362,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3379,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3396,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3413,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3430,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3399,29 +3447,29 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3481,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3498,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3515,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3532,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3501,29 +3549,29 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3535,12 +3583,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3600,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3617,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3634,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3603,12 +3651,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3668,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3685,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3702,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3719,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3736,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -3705,12 +3753,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3770,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3787,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3804,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3821,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3838,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3855,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -3824,29 +3872,29 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3906,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3923,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3940,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3957,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3974,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3991,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -3960,12 +4008,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -3977,12 +4025,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -3994,12 +4042,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4011,29 +4059,29 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4093,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4062,29 +4110,29 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4144,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4161,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4178,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4147,29 +4195,29 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4229,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4198,12 +4246,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4263,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4232,27 +4280,44 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr" s="2">
+      <c r="B72" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr" s="2">
+      <c r="C72" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -4652,301 +4717,301 @@
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
+          <t xml:space="preserve">โอกาสการขาย</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
+          <t xml:space="preserve">กรวยการขายและดีลที่ไล่ปิดอยู่</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipScan.js</t>
+          <t xml:space="preserve">components/views/Deals.js</t>
         </is>
       </c>
       <c r="E16">
-        <v>454</v>
+        <v>670</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดส่งสินค้า</t>
+          <t xml:space="preserve">บันทึกกิจกรรม</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
+          <t xml:space="preserve">โทร เข้าพบ และนัดครั้งถัดไป</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Shipping.js</t>
+          <t xml:space="preserve">components/views/Activities.js</t>
         </is>
       </c>
       <c r="E17">
-        <v>623</v>
+        <v>493</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานะการจัดส่ง</t>
+          <t xml:space="preserve">ลูกค้าเป้าหมาย</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
+          <t xml:space="preserve">ผู้สนใจที่ยังไม่เป็นลูกค้า</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipStatus.js</t>
+          <t xml:space="preserve">components/views/Leads.js</t>
         </is>
       </c>
       <c r="E18">
-        <v>593</v>
+        <v>508</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
+          <t xml:space="preserve">ภาพรวมลูกค้า</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
+          <t xml:space="preserve">ทุกอย่างของลูกค้าหนึ่งรายในหน้าเดียว</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/BillImport.js</t>
+          <t xml:space="preserve">components/views/Customer360.js</t>
         </is>
       </c>
       <c r="E19">
-        <v>883</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลสินค้า</t>
+          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
+          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Products.js</t>
+          <t xml:space="preserve">components/views/ShipScan.js</t>
         </is>
       </c>
       <c r="E20">
-        <v>187</v>
+        <v>454</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สินค้าตามจังหวัด</t>
+          <t xml:space="preserve">การจัดส่งสินค้า</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
+          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Provinces.js</t>
+          <t xml:space="preserve">components/views/Shipping.js</t>
         </is>
       </c>
       <c r="E21">
-        <v>401</v>
+        <v>623</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
+          <t xml:space="preserve">สถานะการจัดส่ง</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
+          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Locations.js</t>
+          <t xml:space="preserve">components/views/ShipStatus.js</t>
         </is>
       </c>
       <c r="E22">
-        <v>697</v>
+        <v>593</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียดลูกค้า</t>
+          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
+          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Customers.js</t>
+          <t xml:space="preserve">components/views/BillImport.js</t>
         </is>
       </c>
       <c r="E23">
-        <v>539</v>
+        <v>883</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
+          <t xml:space="preserve">ข้อมูลสินค้า</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
+          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DocGroups.js</t>
+          <t xml:space="preserve">components/views/Products.js</t>
         </is>
       </c>
       <c r="E24">
-        <v>357</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
+          <t xml:space="preserve">สินค้าตามจังหวัด</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
+          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PrintForms.js</t>
+          <t xml:space="preserve">components/views/Provinces.js</t>
         </is>
       </c>
       <c r="E25">
-        <v>525</v>
+        <v>401</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
+          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
+          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
+          <t xml:space="preserve">components/views/Locations.js</t>
         </is>
       </c>
       <c r="E26">
-        <v>610</v>
+        <v>697</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลกิจการ</t>
+          <t xml:space="preserve">รายละเอียดลูกค้า</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
+          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Company.js</t>
+          <t xml:space="preserve">components/views/Customers.js</t>
         </is>
       </c>
       <c r="E27">
-        <v>164</v>
+        <v>539</v>
       </c>
     </row>
     <row r="28">
@@ -4957,21 +5022,21 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองข้อมูล</t>
+          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
+          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Backup.js</t>
+          <t xml:space="preserve">components/views/DocGroups.js</t>
         </is>
       </c>
       <c r="E28">
-        <v>288</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29">
@@ -4982,21 +5047,21 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
+          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
+          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Users.js</t>
+          <t xml:space="preserve">components/views/PrintForms.js</t>
         </is>
       </c>
       <c r="E29">
-        <v>232</v>
+        <v>525</v>
       </c>
     </row>
     <row r="30">
@@ -5007,21 +5072,21 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SQL Server / MySQL / Access</t>
+          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/SqlServer.js</t>
+          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
         </is>
       </c>
       <c r="E30">
-        <v>748</v>
+        <v>610</v>
       </c>
     </row>
     <row r="31">
@@ -5032,21 +5097,21 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
+          <t xml:space="preserve">ข้อมูลกิจการ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
+          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DataImport.js</t>
+          <t xml:space="preserve">components/views/Company.js</t>
         </is>
       </c>
       <c r="E31">
-        <v>857</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32">
@@ -5057,21 +5122,21 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดพนักงานขาย</t>
+          <t xml:space="preserve">สำรองข้อมูล</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
+          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Salespersons.js</t>
+          <t xml:space="preserve">components/views/Backup.js</t>
         </is>
       </c>
       <c r="E32">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
@@ -5082,21 +5147,21 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
+          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ProductTerms.js</t>
+          <t xml:space="preserve">components/views/Users.js</t>
         </is>
       </c>
       <c r="E33">
-        <v>321</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34">
@@ -5107,95 +5172,195 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+          <t xml:space="preserve">SQL Server / MySQL / Access</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Password.js</t>
+          <t xml:space="preserve">components/views/SqlServer.js</t>
         </is>
       </c>
       <c r="E34">
-        <v>170</v>
+        <v>748</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Reports.js</t>
+          <t xml:space="preserve">components/views/DataImport.js</t>
         </is>
       </c>
       <c r="E35">
-        <v>1887</v>
+        <v>881</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุป</t>
+          <t xml:space="preserve">กำหนดพนักงานขาย</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Graphs.js</t>
+          <t xml:space="preserve">components/views/Salespersons.js</t>
         </is>
       </c>
       <c r="E36">
-        <v>499</v>
+        <v>308</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/ProductTerms.js</t>
+        </is>
+      </c>
+      <c r="E37">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Password.js</t>
+        </is>
+      </c>
+      <c r="E38">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">รายงาน</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr" s="2">
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Reports.js</t>
+        </is>
+      </c>
+      <c r="E39">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กราฟสรุป</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Graphs.js</t>
+        </is>
+      </c>
+      <c r="E40">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สร้างรายงาน</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr" s="2">
+      <c r="C41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">เลือกคอลัมน์และจัดรูปแบบเอง</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="2">
+      <c r="D41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">components/views/ReportBuilder.js</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E41">
         <v>537</v>
       </c>
     </row>
@@ -5732,18 +5897,63 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">crm_leads</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>16</v>
+      </c>
+      <c r="D27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, code, name, contact, phone, email, province, source, status, sales_id, customer_id, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">crm_deals</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>20</v>
+      </c>
+      <c r="D28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, code, name, customer_id, lead_id, party_name, amount, stage, probability, open_date, expect_date, close_date, sales_id, source, lost_reason, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">crm_activities</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>17</v>
+      </c>
+      <c r="D29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, kind, date, customer_id, lead_id, deal_id, party_name, subject, result, next_date, next_note, sales_id, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">screen_perms</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr" s="2">
+      <c r="B30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สิทธิการใช้งานรายหน้าจอ (ดู / แก้ไข / เปลี่ยนวันที่)</t>
         </is>
       </c>
-      <c r="C27">
+      <c r="C30">
         <v>6</v>
       </c>
-      <c r="D27" t="inlineStr" s="2">
+      <c r="D30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">id, can_view, can_edit, can_date, created_at, row_order</t>
         </is>
@@ -5790,7 +6000,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>1940</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="3">
@@ -5805,7 +6015,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>301</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4">
@@ -5877,280 +6087,295 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค่าคงที่ของโปรแกรม Ultra ERP (ระบบควบคุมสินค้าคงคลัง)</t>
+          <t xml:space="preserve">ค่าคงที่ของโปรแกรม One for All Ultra (ระบบควบคุมสินค้าคงคลัง)</t>
         </is>
       </c>
       <c r="C8">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/csv.js</t>
+          <t xml:space="preserve">lib/crm.js</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกตารางเป็นไฟล์ CSV (มี BOM เพื่อให้ Excel อ่านภาษาไทยได้ถูกต้อง)</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์ (CRM) — กติกาและการคำนวณทั้งหมด</t>
         </is>
       </c>
       <c r="C9">
-        <v>29</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/dashWidgets.js</t>
+          <t xml:space="preserve">lib/csv.js</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การ์ดและกราฟที่เลือกมาแสดงบนแดชบอร์ดได้</t>
+          <t xml:space="preserve">ส่งออกตารางเป็นไฟล์ CSV (มี BOM เพื่อให้ Excel อ่านภาษาไทยได้ถูกต้อง)</t>
         </is>
       </c>
       <c r="C10">
-        <v>882</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/db.js</t>
+          <t xml:space="preserve">lib/dashWidgets.js</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชั้นข้อมูล — สร้างข้อมูลตั้งต้น และคำนวณยอดคงเหลือ (ฟังก์ชันบริสุทธิ์ทั้งหมด)</t>
+          <t xml:space="preserve">การ์ดและกราฟที่เลือกมาแสดงบนแดชบอร์ดได้</t>
         </is>
       </c>
       <c r="C11">
-        <v>928</v>
+        <v>882</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/format.js</t>
+          <t xml:space="preserve">lib/db.js</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟังก์ชันจัดรูปแบบข้อมูลสำหรับแสดงผล</t>
+          <t xml:space="preserve">ชั้นข้อมูล — สร้างข้อมูลตั้งต้น และคำนวณยอดคงเหลือ (ฟังก์ชันบริสุทธิ์ทั้งหมด)</t>
         </is>
       </c>
       <c r="C12">
-        <v>204</v>
+        <v>928</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/gemini.js</t>
+          <t xml:space="preserve">lib/format.js</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Gemini API แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">ฟังก์ชันจัดรูปแบบข้อมูลสำหรับแสดงผล</t>
         </is>
       </c>
       <c r="C13">
-        <v>504</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/geo.js</t>
+          <t xml:space="preserve">lib/gemini.js</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คณิตศาสตร์ของแผนที่ (Web Mercator) และการค้นหาสถานที่</t>
+          <t xml:space="preserve">ตัวเชื่อม Gemini API แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C14">
-        <v>167</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/image.js</t>
+          <t xml:space="preserve">lib/geo.js</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
+          <t xml:space="preserve">คณิตศาสตร์ของแผนที่ (Web Mercator) และการค้นหาสถานที่</t>
         </is>
       </c>
       <c r="C15">
-        <v>49</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/importSets.js</t>
+          <t xml:space="preserve">lib/image.js</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
+          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
         </is>
       </c>
       <c r="C16">
-        <v>229</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/inventorySummary.js</t>
+          <t xml:space="preserve">lib/importSets.js</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
+          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
         </is>
       </c>
       <c r="C17">
-        <v>445</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/printForms.js</t>
+          <t xml:space="preserve">lib/inventorySummary.js</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
+          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
         </is>
       </c>
       <c r="C18">
-        <v>191</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/productTerms.js</t>
+          <t xml:space="preserve">lib/printForms.js</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
+          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
         </is>
       </c>
       <c r="C19">
-        <v>138</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/reportData.js</t>
+          <t xml:space="preserve">lib/productTerms.js</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
+          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C20">
-        <v>466</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/store.js</t>
+          <t xml:space="preserve">lib/reportData.js</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
+          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
         </is>
       </c>
       <c r="C21">
-        <v>1001</v>
+        <v>466</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/supabase.js</t>
+          <t xml:space="preserve">lib/store.js</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
         </is>
       </c>
       <c r="C22">
-        <v>389</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/targets.js</t>
+          <t xml:space="preserve">lib/supabase.js</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
+          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C23">
-        <v>140</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/thaiAddress.js</t>
+          <t xml:space="preserve">lib/targets.js</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
         </is>
       </c>
       <c r="C24">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/thaiAddress.js</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
         </is>
       </c>
       <c r="C25">
-        <v>321</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/xlsx.js</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/xlsxRead.js</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="2">
+      <c r="B27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
         </is>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>223</v>
       </c>
     </row>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -198,7 +198,7 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">40 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
+          <t xml:space="preserve">41 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
         </is>
       </c>
     </row>
@@ -210,7 +210,7 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">29 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
+          <t xml:space="preserve">30 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
         </is>
       </c>
     </row>
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">26 ไฟล์</t>
+          <t xml:space="preserve">28 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -234,7 +234,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">43 ไฟล์</t>
+          <t xml:space="preserve">44 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">75 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 71 ครั้ง</t>
+          <t xml:space="preserve">76 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 72 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3087,6 +3087,53 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- หน้าจอใหม่ "กำหนดประเภทลูกค้า" (การจัดการระบบ)
+รูปแบบเดียวกับพนักงานขายและทะเบียนสินค้า: รหัส + ชื่อ
+เพิ่ม แก้ไข ลบ ปิดใช้งาน ส่งออก และนำเข้าจาก Excel ได้
+- เดิมประเภทลูกค้าเป็นรายการตายตัว 5 ค่าในโค้ด เพิ่มประเภทใหม่ต้องรอ deploy
+ซึ่งไม่สมเหตุสมผล เพราะเป็นเรื่องของกิจการ ไม่ใช่ของโปรแกรม
+ค่าเดิมทั้งห้ายังใช้ได้ และมีปุ่มเติมเข้าทะเบียนทั้งชุดในคลิกเดียว
+- หน้ารายละเอียดลูกค้า: ช่องประเภทเปลี่ยนจากดรอปดาวน์ค่าคงที่
+เป็นช่องกดเลือกที่พิมพ์ค้นหาบางส่วนได้ รายการมาจากทะเบียน
+บวกค่าที่ลูกค้ารายอื่นใช้อยู่แล้วแต่ยังไม่ได้จดทะเบียน
+- ลูกค้าใหม่ไม่ตั้งประเภทให้อัตโนมัติอีกแล้ว
+เดิมตั้งเป็นค่าแรกของรายการ ทำให้ลูกค้าจำนวนมากถูกบันทึกเป็น
+"ลูกค้าทั่วไป" ทั้งที่ไม่มีใครตั้งใจเลือก แล้วรายงานแยกตามประเภทก็ไร้ความหมาย
+- ตัวกรองประเภทที่หัวตารางลูกค้าอ่านจากค่าที่ข้อมูลใช้อยู่จริงด้วย
+ไม่ใช่เฉพาะที่จดทะเบียนไว้ ไม่งั้นลูกค้าที่ยังถือค่าเก่าจะกรองหาไม่เจอ
+ทั้งที่มองเห็นอยู่ในตารางตรงหน้า
+เก็บค่าประเภทลูกค้าในหน้าจอที่เอาไปใช้ (ตามที่สั่ง):
+- invoices เพิ่มคอลัมน์ cust_kind คัดลอกประเภท ณ วันที่ออกเอกสาร
+เหตุผลเดียวกับชื่อและที่อยู่: ลูกค้าเลื่อนประเภททีหลัง
+(เช่น เลื่อนเป็นตัวแทนจำหน่าย) ใบเก่าต้องยังบอกได้ว่าตอนนั้นเป็นประเภทอะไร
+ไม่งั้นรายงานยอดขายแยกตามประเภทย้อนหลังจะเปลี่ยนไปเองทุกครั้งที่แก้ทะเบียน
+- เก็บทั้งจากหน้าขายสินค้าและบริการ และจากหน้าดึงบิลอัตโนมัติ
+(หน้าดึงบิลใช้ประเภทของลูกค้าที่จับคู่ได้ จับคู่ไม่ได้เว้นว่าง ไม่เดาให้)
+- ฟังก์ชัน create_invoice ในฐานข้อมูลรับและบันทึกค่านี้ด้วย
+- รายงานใบขายเพิ่มคอลัมน์ประเภทลูกค้า ทั้งบนหน้าจอ ตอนพิมพ์ และตอนส่งออก
+อ่านจากค่าที่เก็บไว้ในใบ ไม่ได้อ่านสดจากทะเบียน
+- แยก lib/choices.js เป็นตัวช่วยกลาง ใช้ร่วมกับทะเบียนสินค้า
+เพราะทั้งสองมีปัญหาเดียวกันเป๊ะ: ตอนเพิ่มหน้าทะเบียนเข้ามาทีหลัง
+ข้อมูลเดิมมีค่าที่พิมพ์ไว้เองอยู่แล้ว กติกาการรวมสามอย่าง
+(ทะเบียนก่อน · ค่าที่ใช้อยู่ตามมา · ค่าปัจจุบันต้องอยู่ในรายการเสมอ)
+ต้องเหมือนกันทุกที่ ไม่งั้นสองหน้าจอจะทำงานคนละแบบ
+lib/productTerms.js เปลี่ยนมาใช้ตัวช่วยกลางด้วย ทดสอบเดิมยังผ่านครบ
+- ตาราง customer_kinds ไม่ยุบรวมกับ product_terms ทั้งที่โครงเหมือนกัน
+เพราะคนละโดเมน สิทธิคนละหน</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3119,17 +3166,17 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3141,12 +3188,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3205,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3175,12 +3222,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3192,12 +3239,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3256,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3273,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3290,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3307,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3277,12 +3324,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3341,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3311,12 +3358,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3328,12 +3375,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3392,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3362,12 +3409,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3379,12 +3426,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3443,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3460,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3430,12 +3477,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3447,12 +3494,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3464,29 +3511,29 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3545,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3562,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3532,12 +3579,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3596,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3566,29 +3613,29 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3600,12 +3647,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3664,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3681,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3651,12 +3698,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3668,12 +3715,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3732,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3749,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3766,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -3736,12 +3783,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -3753,12 +3800,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -3770,12 +3817,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -3787,12 +3834,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3851,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3868,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3885,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3902,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3919,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -3889,29 +3936,29 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3970,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3987,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -3957,12 +4004,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -3974,12 +4021,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -3991,12 +4038,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4008,12 +4055,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4072,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4089,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4106,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4076,29 +4123,29 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4110,12 +4157,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4127,29 +4174,29 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4161,12 +4208,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4225,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4195,12 +4242,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4212,29 +4259,29 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4246,12 +4293,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4310,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4280,12 +4327,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4297,27 +4344,44 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr" s="2">
+      <c r="B73" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr" s="2">
+      <c r="C73" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -4686,7 +4750,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15">
@@ -4911,7 +4975,7 @@
         </is>
       </c>
       <c r="E23">
-        <v>883</v>
+        <v>892</v>
       </c>
     </row>
     <row r="24">
@@ -5011,7 +5075,7 @@
         </is>
       </c>
       <c r="E27">
-        <v>539</v>
+        <v>548</v>
       </c>
     </row>
     <row r="28">
@@ -5136,7 +5200,7 @@
         </is>
       </c>
       <c r="E32">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33">
@@ -5211,7 +5275,7 @@
         </is>
       </c>
       <c r="E35">
-        <v>881</v>
+        <v>894</v>
       </c>
     </row>
     <row r="36">
@@ -5272,46 +5336,46 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Password.js</t>
+          <t xml:space="preserve">components/views/CustomerKinds.js</t>
         </is>
       </c>
       <c r="E38">
-        <v>170</v>
+        <v>372</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Reports.js</t>
+          <t xml:space="preserve">components/views/Password.js</t>
         </is>
       </c>
       <c r="E39">
-        <v>2564</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40">
@@ -5322,21 +5386,21 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุป</t>
+          <t xml:space="preserve">รายงาน</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Graphs.js</t>
+          <t xml:space="preserve">components/views/Reports.js</t>
         </is>
       </c>
       <c r="E40">
-        <v>499</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="41">
@@ -5347,20 +5411,45 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">กราฟสรุป</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Graphs.js</t>
+        </is>
+      </c>
+      <c r="E41">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สร้างรายงาน</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr" s="2">
+      <c r="C42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">เลือกคอลัมน์และจัดรูปแบบเอง</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr" s="2">
+      <c r="D42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">components/views/ReportBuilder.js</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E42">
         <v>537</v>
       </c>
     </row>
@@ -5822,27 +5911,22 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">product_terms</t>
+          <t xml:space="preserve">customer_kinds</t>
         </is>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, dim, code, name, note, active, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, code, name, note, active, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">salespersons</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">พนักงานขาย</t>
+          <t xml:space="preserve">product_terms</t>
         </is>
       </c>
       <c r="C24">
@@ -5850,110 +5934,130 @@
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, code, name, phone, note, active, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, dim, code, name, note, active, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">sales_targets</t>
+          <t xml:space="preserve">salespersons</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขายตามงวดและมิติสินค้า</t>
+          <t xml:space="preserve">พนักงานขาย</t>
         </is>
       </c>
       <c r="C25">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, year, month, sales_id, grp, brand, kind, amount, qty, note, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, code, name, phone, note, active, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">sql_connections</t>
+          <t xml:space="preserve">sales_targets</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การเชื่อมต่อฐานข้อมูลภายนอกที่บันทึกไว้ (SQL Server / MySQL / Access)</t>
+          <t xml:space="preserve">เป้าขายตามงวดและมิติสินค้า</t>
         </is>
       </c>
       <c r="C26">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, name, kind, server, port, file_path, db_name, login, password, encrypt, trust_cert, bridge_url, note, is_default, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, year, month, sales_id, grp, brand, kind, amount, qty, note, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">crm_leads</t>
+          <t xml:space="preserve">sql_connections</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การเชื่อมต่อฐานข้อมูลภายนอกที่บันทึกไว้ (SQL Server / MySQL / Access)</t>
         </is>
       </c>
       <c r="C27">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, code, name, contact, phone, email, province, source, status, sales_id, customer_id, note, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, name, kind, server, port, file_path, db_name, login, password, encrypt, trust_cert, bridge_url, note, is_default, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">crm_deals</t>
+          <t xml:space="preserve">crm_leads</t>
         </is>
       </c>
       <c r="C28">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, code, name, customer_id, lead_id, party_name, amount, stage, probability, open_date, expect_date, close_date, sales_id, source, lost_reason, note, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, code, name, contact, phone, email, province, source, status, sales_id, customer_id, note, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">crm_activities</t>
+          <t xml:space="preserve">crm_deals</t>
         </is>
       </c>
       <c r="C29">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, kind, date, customer_id, lead_id, deal_id, party_name, subject, result, next_date, next_note, sales_id, note, user_name, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, code, name, customer_id, lead_id, party_name, amount, stage, probability, open_date, expect_date, close_date, sales_id, source, lost_reason, note, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">crm_activities</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>17</v>
+      </c>
+      <c r="D30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, kind, date, customer_id, lead_id, deal_id, party_name, subject, result, next_date, next_note, sales_id, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">screen_perms</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr" s="2">
+      <c r="B31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สิทธิการใช้งานรายหน้าจอ (ดู / แก้ไข / เปลี่ยนวันที่)</t>
         </is>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>6</v>
       </c>
-      <c r="D30" t="inlineStr" s="2">
+      <c r="D31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">id, can_view, can_edit, can_date, created_at, row_order</t>
         </is>
@@ -6000,7 +6104,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>2151</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="3">
@@ -6015,7 +6119,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4">
@@ -6082,300 +6186,330 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/constants.js</t>
+          <t xml:space="preserve">lib/choices.js</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค่าคงที่ของโปรแกรม One for All Ultra (ระบบควบคุมสินค้าคงคลัง)</t>
+          <t xml:space="preserve">รายการให้เลือกที่มาจาก "ทะเบียนที่ตั้งไว้" บวก "ค่าที่ข้อมูลจริงใช้อยู่"</t>
         </is>
       </c>
       <c r="C8">
-        <v>389</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/crm.js</t>
+          <t xml:space="preserve">lib/constants.js</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานลูกค้าสัมพันธ์ (CRM) — กติกาและการคำนวณทั้งหมด</t>
+          <t xml:space="preserve">ค่าคงที่ของโปรแกรม One for All Ultra (ระบบควบคุมสินค้าคงคลัง)</t>
         </is>
       </c>
       <c r="C9">
-        <v>377</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/csv.js</t>
+          <t xml:space="preserve">lib/crm.js</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกตารางเป็นไฟล์ CSV (มี BOM เพื่อให้ Excel อ่านภาษาไทยได้ถูกต้อง)</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์ (CRM) — กติกาและการคำนวณทั้งหมด</t>
         </is>
       </c>
       <c r="C10">
-        <v>29</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/dashWidgets.js</t>
+          <t xml:space="preserve">lib/csv.js</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การ์ดและกราฟที่เลือกมาแสดงบนแดชบอร์ดได้</t>
+          <t xml:space="preserve">ส่งออกตารางเป็นไฟล์ CSV (มี BOM เพื่อให้ Excel อ่านภาษาไทยได้ถูกต้อง)</t>
         </is>
       </c>
       <c r="C11">
-        <v>882</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/db.js</t>
+          <t xml:space="preserve">lib/customerKinds.js</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชั้นข้อมูล — สร้างข้อมูลตั้งต้น และคำนวณยอดคงเหลือ (ฟังก์ชันบริสุทธิ์ทั้งหมด)</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า</t>
         </is>
       </c>
       <c r="C12">
-        <v>928</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/format.js</t>
+          <t xml:space="preserve">lib/dashWidgets.js</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟังก์ชันจัดรูปแบบข้อมูลสำหรับแสดงผล</t>
+          <t xml:space="preserve">การ์ดและกราฟที่เลือกมาแสดงบนแดชบอร์ดได้</t>
         </is>
       </c>
       <c r="C13">
-        <v>225</v>
+        <v>882</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/gemini.js</t>
+          <t xml:space="preserve">lib/db.js</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Gemini API แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">ชั้นข้อมูล — สร้างข้อมูลตั้งต้น และคำนวณยอดคงเหลือ (ฟังก์ชันบริสุทธิ์ทั้งหมด)</t>
         </is>
       </c>
       <c r="C14">
-        <v>504</v>
+        <v>928</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/geo.js</t>
+          <t xml:space="preserve">lib/format.js</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คณิตศาสตร์ของแผนที่ (Web Mercator) และการค้นหาสถานที่</t>
+          <t xml:space="preserve">ฟังก์ชันจัดรูปแบบข้อมูลสำหรับแสดงผล</t>
         </is>
       </c>
       <c r="C15">
-        <v>167</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/image.js</t>
+          <t xml:space="preserve">lib/gemini.js</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
+          <t xml:space="preserve">ตัวเชื่อม Gemini API แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C16">
-        <v>49</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/importSets.js</t>
+          <t xml:space="preserve">lib/geo.js</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
+          <t xml:space="preserve">คณิตศาสตร์ของแผนที่ (Web Mercator) และการค้นหาสถานที่</t>
         </is>
       </c>
       <c r="C17">
-        <v>251</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/inventorySummary.js</t>
+          <t xml:space="preserve">lib/image.js</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
+          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
         </is>
       </c>
       <c r="C18">
-        <v>445</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/printForms.js</t>
+          <t xml:space="preserve">lib/importSets.js</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
+          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
         </is>
       </c>
       <c r="C19">
-        <v>191</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/productTerms.js</t>
+          <t xml:space="preserve">lib/inventorySummary.js</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
+          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
         </is>
       </c>
       <c r="C20">
-        <v>138</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/reportData.js</t>
+          <t xml:space="preserve">lib/printForms.js</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
+          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
         </is>
       </c>
       <c r="C21">
-        <v>466</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/store.js</t>
+          <t xml:space="preserve">lib/productTerms.js</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
+          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C22">
-        <v>1093</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/supabase.js</t>
+          <t xml:space="preserve">lib/reportData.js</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
         </is>
       </c>
       <c r="C23">
-        <v>389</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/targets.js</t>
+          <t xml:space="preserve">lib/store.js</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
+          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
         </is>
       </c>
       <c r="C24">
-        <v>140</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/thaiAddress.js</t>
+          <t xml:space="preserve">lib/supabase.js</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C25">
-        <v>166</v>
+        <v>389</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/targets.js</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
         </is>
       </c>
       <c r="C26">
-        <v>321</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/thaiAddress.js</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">lib/xlsx.js</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/xlsxRead.js</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr" s="2">
+      <c r="B29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
         </is>
       </c>
-      <c r="C27">
+      <c r="C29">
         <v>223</v>
       </c>
     </row>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -198,7 +198,7 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">41 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
+          <t xml:space="preserve">42 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
         </is>
       </c>
     </row>
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">28 ไฟล์</t>
+          <t xml:space="preserve">29 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -234,7 +234,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44 ไฟล์</t>
+          <t xml:space="preserve">45 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">17 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">18 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 72 ครั้ง</t>
+          <t xml:space="preserve">77 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 73 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3134,6 +3134,47 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- หน้าจอใหม่ "วิธีการใช้งาน" อยู่บนสุดของกลุ่มภาพรวม
+เพราะเป็นที่แรกที่คนใหม่เปิดหา
+- สองมุมมองในหน้าเดียว เพราะคนเข้ามาด้วยคำถามคนละแบบ:
+"งานนี้เริ่มตรงไหน" -&gt; ดูสายงาน 7 สายที่เรียงเป็นทอด ๆ
+"หน้านี้ทำอะไร" -&gt; ค้นหาชื่อหน้าจอแล้วอ่านการ์ดของหน้านั้น
+- สายงาน 7 สาย 35 ขั้น: งานซื้อ · งานขาย · งานคลัง · งานตรวจนับ ·
+งานลูกค้าสัมพันธ์ · การวัดผล · ตั้งค่าครั้งแรก
+แต่ละขั้นบอกทั้ง "ทำอะไร" และ "ได้อะไร" ไม่ใช่แค่ชื่อหน้าจอเรียงกัน
+- การ์ดรายหน้าจอบอกห้าอย่าง: ทำอะไร · ขั้นตอนใช้งานจริง ·
+กดบันทึกแล้วเกิดอะไรขึ้น · รับข้อมูลจากหน้าไหน · ส่งต่อไปหน้าไหน
+พร้อมข้อควรรู้ที่คนใช้มักพลาด
+- ทุกชื่อหน้าจอในคู่มือกดแล้วกระโดดไปหน้าจริงได้
+ไม่ใช่ข้อความที่ต้องไปไล่หาในเมนูเอง
+- เคารพสิทธิ: หน้าที่ผู้ใช้ไม่มีสิทธิดู จะไม่ขึ้นในคู่มือและกดไปไม่ได้
+ไม่งั้นคู่มือจะพาไปหน้าที่กดแล้วไม่มีอะไรเกิดขึ้น
+- พิมพ์คู่มือทั้งเล่มได้ ใช้ระบบพิมพ์เดียวกับรายงานอื่น
+- เนื้อหาอยู่ใน lib/guide.js เป็นข้อมูลล้วน ไม่ใช่ข้อความยาวในหน้าจอ
+เพราะตัวตรวจอัตโนมัติเทียบกับรายชื่อหน้าจอจริงได้
+และปุ่ม "ไปที่หน้านั้น" ต้องรู้จักรหัสหน้าจอจริง
+- เพิ่มตัวตรวจหมวด 18: คู่มือต้องครอบคลุมทุกหน้าจอ ไม่มีคู่มือของหน้าที่
+ไม่มีแล้ว ทุกหน้ามีครบสี่ส่วน และลิงก์ทุกเส้นชี้ไปหน้าที่มีอยู่จริง
+ทดสอบแล้วว่าจับได้ทั้งกรณีเพิ่มหน้าจอแล้วลืมเขียนคู่มือ และลิงก์เสีย
+(คู่มือที่ตามโค้ดไม่ทันคือข้อมูลผิดที่คนเชื่อ ซึ่งแย่กว่าไม่มีคู่มือ)
+- ทดสอบ 32 ข้อ: ความครอบคลุม · คุณภาพเนื้อหา (ไม่มีขั้นตอนสั้นจนไม่ได้ความ)
+· หน้าที่บันทึกข้อมูลต้องบอกว่าบันทึกอะไร · หน้าที่ดูอย่างเดียวต้องไม่อ้างว่าบันทึก
+· สายงานไม่มีหน้าจอซ้ำ · การค้นหา · และความเชื่อมโยงที่ต้องเป็นจริง
+(ใบขาย -&gt; จัดส่ง · เตรียมใบตรวจนับ -&gt; นับ -&gt; ปรับปรุง)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3171,29 +3212,29 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3205,12 +3246,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3222,12 +3263,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3280,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3297,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3314,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3331,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3307,12 +3348,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3365,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3382,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3399,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3416,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3433,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3450,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3467,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3484,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3501,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3518,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3535,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3511,12 +3552,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3528,29 +3569,29 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3603,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3620,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3637,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3654,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3630,29 +3671,29 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3664,12 +3705,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3681,12 +3722,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3739,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3756,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3773,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3790,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3807,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3824,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3841,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3858,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3875,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3892,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -3868,12 +3909,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -3885,12 +3926,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3943,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -3919,12 +3960,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3977,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -3953,29 +3994,29 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -3987,12 +4028,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4045,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4062,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4079,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4096,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4113,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4130,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4147,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4123,12 +4164,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4140,29 +4181,29 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4215,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4191,29 +4232,29 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4266,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4283,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4300,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4276,29 +4317,29 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4351,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4368,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4385,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4361,27 +4402,44 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr" s="2">
+      <c r="B74" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr" s="2">
+      <c r="C74" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -4461,46 +4519,46 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Quick View (มือถือ)</t>
+          <t xml:space="preserve">วิธีการใช้งาน</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยอดขายเทียบเป้า ดูเร็วบนมือถือ</t>
+          <t xml:space="preserve">แต่ละหน้าจอทำงานยังไง เชื่อมกันตรงไหน</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/QuickView.js</t>
+          <t xml:space="preserve">components/views/Guide.js</t>
         </is>
       </c>
       <c r="E3">
-        <v>416</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำรายการ</t>
+          <t xml:space="preserve">ภาพรวม</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับสินค้า</t>
+          <t xml:space="preserve">Quick View (มือถือ)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกการรับสินค้าเข้าคลัง</t>
+          <t xml:space="preserve">ยอดขายเทียบเป้า ดูเร็วบนมือถือ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/TxnScreen.js</t>
+          <t xml:space="preserve">components/views/QuickView.js</t>
         </is>
       </c>
       <c r="E4">
-        <v>546</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5">
@@ -4511,12 +4569,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เบิกสินค้า</t>
+          <t xml:space="preserve">รับสินค้า</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกการเบิก-จ่ายสินค้า</t>
+          <t xml:space="preserve">บันทึกการรับสินค้าเข้าคลัง</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
@@ -4536,12 +4594,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โอนสินค้า</t>
+          <t xml:space="preserve">เบิกสินค้า</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โอนย้ายระหว่างคลัง</t>
+          <t xml:space="preserve">บันทึกการเบิก-จ่ายสินค้า</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -4561,21 +4619,21 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับปรุงสินค้า</t>
+          <t xml:space="preserve">โอนสินค้า</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับยอดตามผลการตรวจนับ</t>
+          <t xml:space="preserve">โอนย้ายระหว่างคลัง</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/AdjustScreen.js</t>
+          <t xml:space="preserve">components/views/TxnScreen.js</t>
         </is>
       </c>
       <c r="E7">
-        <v>474</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4586,21 +4644,21 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เตรียมใบตรวจนับ</t>
+          <t xml:space="preserve">ปรับปรุงสินค้า</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างใบและพิมพ์ออกไปนับ</t>
+          <t xml:space="preserve">ปรับยอดตามผลการตรวจนับ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/CountPrep.js</t>
+          <t xml:space="preserve">components/views/AdjustScreen.js</t>
         </is>
       </c>
       <c r="E8">
-        <v>486</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -4611,46 +4669,46 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">นับสินค้า (มือถือ)</t>
+          <t xml:space="preserve">เตรียมใบตรวจนับ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สแกนบาร์โค๊ดแล้วกรอกจำนวน</t>
+          <t xml:space="preserve">สร้างใบและพิมพ์ออกไปนับ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/CountScan.js</t>
+          <t xml:space="preserve">components/views/CountPrep.js</t>
         </is>
       </c>
       <c r="E9">
-        <v>614</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานซื้อ</t>
+          <t xml:space="preserve">ทำรายการ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ซื้อสินค้าและบริการ</t>
+          <t xml:space="preserve">นับสินค้า (มือถือ)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับของเข้าและบันทึกภาษีซื้อ</t>
+          <t xml:space="preserve">สแกนบาร์โค๊ดแล้วกรอกจำนวน</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PurchaseInvoice.js</t>
+          <t xml:space="preserve">components/views/CountScan.js</t>
         </is>
       </c>
       <c r="E10">
-        <v>578</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11">
@@ -4661,21 +4719,21 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งคืนสินค้าและบริการ</t>
+          <t xml:space="preserve">ซื้อสินค้าและบริการ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คืนของให้เจ้าหนี้ตามใบซื้อ</t>
+          <t xml:space="preserve">รับของเข้าและบันทึกภาษีซื้อ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PurchaseReturn.js</t>
+          <t xml:space="preserve">components/views/PurchaseInvoice.js</t>
         </is>
       </c>
       <c r="E11">
-        <v>479</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12">
@@ -4686,46 +4744,46 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียดเจ้าหนี้</t>
+          <t xml:space="preserve">ส่งคืนสินค้าและบริการ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนเจ้าหนี้และที่อยู่</t>
+          <t xml:space="preserve">คืนของให้เจ้าหนี้ตามใบซื้อ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Suppliers.js</t>
+          <t xml:space="preserve">components/views/PurchaseReturn.js</t>
         </is>
       </c>
       <c r="E12">
-        <v>527</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานขาย</t>
+          <t xml:space="preserve">งานซื้อ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ขายสินค้า (POS)</t>
+          <t xml:space="preserve">รายละเอียดเจ้าหนี้</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยิงบาร์โค๊ด ขาย และออกใบเสร็จ</t>
+          <t xml:space="preserve">ทะเบียนเจ้าหนี้และที่อยู่</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/POS.js</t>
+          <t xml:space="preserve">components/views/Suppliers.js</t>
         </is>
       </c>
       <c r="E13">
-        <v>782</v>
+        <v>527</v>
       </c>
     </row>
     <row r="14">
@@ -4736,21 +4794,21 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ขายสินค้าและบริการ</t>
+          <t xml:space="preserve">ขายสินค้า (POS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกใบกำกับภาษีเต็มรูปแบบ</t>
+          <t xml:space="preserve">ยิงบาร์โค๊ด ขาย และออกใบเสร็จ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/SalesInvoice.js</t>
+          <t xml:space="preserve">components/views/POS.js</t>
         </is>
       </c>
       <c r="E14">
-        <v>685</v>
+        <v>782</v>
       </c>
     </row>
     <row r="15">
@@ -4761,46 +4819,46 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดเป้าขาย</t>
+          <t xml:space="preserve">ขายสินค้าและบริการ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งเป้าและเทียบกับยอดจริง</t>
+          <t xml:space="preserve">ออกใบกำกับภาษีเต็มรูปแบบ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Targets.js</t>
+          <t xml:space="preserve">components/views/SalesInvoice.js</t>
         </is>
       </c>
       <c r="E15">
-        <v>464</v>
+        <v>685</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
+          <t xml:space="preserve">งานขาย</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โอกาสการขาย</t>
+          <t xml:space="preserve">กำหนดเป้าขาย</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กรวยการขายและดีลที่ไล่ปิดอยู่</t>
+          <t xml:space="preserve">ตั้งเป้าและเทียบกับยอดจริง</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Deals.js</t>
+          <t xml:space="preserve">components/views/Targets.js</t>
         </is>
       </c>
       <c r="E16">
-        <v>670</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17">
@@ -4811,21 +4869,21 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกกิจกรรม</t>
+          <t xml:space="preserve">โอกาสการขาย</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โทร เข้าพบ และนัดครั้งถัดไป</t>
+          <t xml:space="preserve">กรวยการขายและดีลที่ไล่ปิดอยู่</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Activities.js</t>
+          <t xml:space="preserve">components/views/Deals.js</t>
         </is>
       </c>
       <c r="E17">
-        <v>493</v>
+        <v>670</v>
       </c>
     </row>
     <row r="18">
@@ -4836,21 +4894,21 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลูกค้าเป้าหมาย</t>
+          <t xml:space="preserve">บันทึกกิจกรรม</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้สนใจที่ยังไม่เป็นลูกค้า</t>
+          <t xml:space="preserve">โทร เข้าพบ และนัดครั้งถัดไป</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Leads.js</t>
+          <t xml:space="preserve">components/views/Activities.js</t>
         </is>
       </c>
       <c r="E18">
-        <v>508</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19">
@@ -4861,46 +4919,46 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ภาพรวมลูกค้า</t>
+          <t xml:space="preserve">ลูกค้าเป้าหมาย</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทุกอย่างของลูกค้าหนึ่งรายในหน้าเดียว</t>
+          <t xml:space="preserve">ผู้สนใจที่ยังไม่เป็นลูกค้า</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Customer360.js</t>
+          <t xml:space="preserve">components/views/Leads.js</t>
         </is>
       </c>
       <c r="E19">
-        <v>288</v>
+        <v>508</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
+          <t xml:space="preserve">ภาพรวมลูกค้า</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
+          <t xml:space="preserve">ทุกอย่างของลูกค้าหนึ่งรายในหน้าเดียว</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipScan.js</t>
+          <t xml:space="preserve">components/views/Customer360.js</t>
         </is>
       </c>
       <c r="E20">
-        <v>454</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21">
@@ -4911,21 +4969,21 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดส่งสินค้า</t>
+          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
+          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Shipping.js</t>
+          <t xml:space="preserve">components/views/ShipScan.js</t>
         </is>
       </c>
       <c r="E21">
-        <v>623</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22">
@@ -4936,21 +4994,21 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานะการจัดส่ง</t>
+          <t xml:space="preserve">การจัดส่งสินค้า</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
+          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipStatus.js</t>
+          <t xml:space="preserve">components/views/Shipping.js</t>
         </is>
       </c>
       <c r="E22">
-        <v>593</v>
+        <v>623</v>
       </c>
     </row>
     <row r="23">
@@ -4961,46 +5019,46 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
+          <t xml:space="preserve">สถานะการจัดส่ง</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
+          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/BillImport.js</t>
+          <t xml:space="preserve">components/views/ShipStatus.js</t>
         </is>
       </c>
       <c r="E23">
-        <v>892</v>
+        <v>593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลสินค้า</t>
+          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
+          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Products.js</t>
+          <t xml:space="preserve">components/views/BillImport.js</t>
         </is>
       </c>
       <c r="E24">
-        <v>187</v>
+        <v>892</v>
       </c>
     </row>
     <row r="25">
@@ -5011,21 +5069,21 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สินค้าตามจังหวัด</t>
+          <t xml:space="preserve">ข้อมูลสินค้า</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
+          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Provinces.js</t>
+          <t xml:space="preserve">components/views/Products.js</t>
         </is>
       </c>
       <c r="E25">
-        <v>401</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26">
@@ -5036,21 +5094,21 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
+          <t xml:space="preserve">สินค้าตามจังหวัด</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
+          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Locations.js</t>
+          <t xml:space="preserve">components/views/Provinces.js</t>
         </is>
       </c>
       <c r="E26">
-        <v>697</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27">
@@ -5061,46 +5119,46 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียดลูกค้า</t>
+          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
+          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Customers.js</t>
+          <t xml:space="preserve">components/views/Locations.js</t>
         </is>
       </c>
       <c r="E27">
-        <v>548</v>
+        <v>697</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
+          <t xml:space="preserve">รายละเอียดลูกค้า</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
+          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DocGroups.js</t>
+          <t xml:space="preserve">components/views/Customers.js</t>
         </is>
       </c>
       <c r="E28">
-        <v>357</v>
+        <v>548</v>
       </c>
     </row>
     <row r="29">
@@ -5111,21 +5169,21 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
+          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
+          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PrintForms.js</t>
+          <t xml:space="preserve">components/views/DocGroups.js</t>
         </is>
       </c>
       <c r="E29">
-        <v>525</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30">
@@ -5136,21 +5194,21 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
+          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
+          <t xml:space="preserve">components/views/PrintForms.js</t>
         </is>
       </c>
       <c r="E30">
-        <v>610</v>
+        <v>525</v>
       </c>
     </row>
     <row r="31">
@@ -5161,21 +5219,21 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลกิจการ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
+          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Company.js</t>
+          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
         </is>
       </c>
       <c r="E31">
-        <v>164</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32">
@@ -5186,21 +5244,21 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองข้อมูล</t>
+          <t xml:space="preserve">ข้อมูลกิจการ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
+          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Backup.js</t>
+          <t xml:space="preserve">components/views/Company.js</t>
         </is>
       </c>
       <c r="E32">
-        <v>292</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33">
@@ -5211,21 +5269,21 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
+          <t xml:space="preserve">สำรองข้อมูล</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
+          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Users.js</t>
+          <t xml:space="preserve">components/views/Backup.js</t>
         </is>
       </c>
       <c r="E33">
-        <v>232</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34">
@@ -5236,21 +5294,21 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
+          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SQL Server / MySQL / Access</t>
+          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/SqlServer.js</t>
+          <t xml:space="preserve">components/views/Users.js</t>
         </is>
       </c>
       <c r="E34">
-        <v>748</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35">
@@ -5261,21 +5319,21 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
+          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
+          <t xml:space="preserve">SQL Server / MySQL / Access</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DataImport.js</t>
+          <t xml:space="preserve">components/views/SqlServer.js</t>
         </is>
       </c>
       <c r="E35">
-        <v>894</v>
+        <v>748</v>
       </c>
     </row>
     <row r="36">
@@ -5286,21 +5344,21 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดพนักงานขาย</t>
+          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
+          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Salespersons.js</t>
+          <t xml:space="preserve">components/views/DataImport.js</t>
         </is>
       </c>
       <c r="E36">
-        <v>308</v>
+        <v>894</v>
       </c>
     </row>
     <row r="37">
@@ -5311,21 +5369,21 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+          <t xml:space="preserve">กำหนดพนักงานขาย</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
+          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ProductTerms.js</t>
+          <t xml:space="preserve">components/views/Salespersons.js</t>
         </is>
       </c>
       <c r="E37">
-        <v>321</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38">
@@ -5336,21 +5394,21 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
+          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/CustomerKinds.js</t>
+          <t xml:space="preserve">components/views/ProductTerms.js</t>
         </is>
       </c>
       <c r="E38">
-        <v>372</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39">
@@ -5361,46 +5419,46 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Password.js</t>
+          <t xml:space="preserve">components/views/CustomerKinds.js</t>
         </is>
       </c>
       <c r="E39">
-        <v>170</v>
+        <v>372</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Reports.js</t>
+          <t xml:space="preserve">components/views/Password.js</t>
         </is>
       </c>
       <c r="E40">
-        <v>2578</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41">
@@ -5411,21 +5469,21 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุป</t>
+          <t xml:space="preserve">รายงาน</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Graphs.js</t>
+          <t xml:space="preserve">components/views/Reports.js</t>
         </is>
       </c>
       <c r="E41">
-        <v>499</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="42">
@@ -5436,20 +5494,45 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">กราฟสรุป</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Graphs.js</t>
+        </is>
+      </c>
+      <c r="E42">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สร้างรายงาน</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr" s="2">
+      <c r="C43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">เลือกคอลัมน์และจัดรูปแบบเอง</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr" s="2">
+      <c r="D43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">components/views/ReportBuilder.js</t>
         </is>
       </c>
-      <c r="E42">
+      <c r="E43">
         <v>537</v>
       </c>
     </row>
@@ -6119,7 +6202,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4">
@@ -6210,7 +6293,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10">
@@ -6336,180 +6419,195 @@
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/image.js</t>
+          <t xml:space="preserve">lib/guide.js</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
+          <t xml:space="preserve">คู่มือการใช้งาน — อธิบายว่าแต่ละหน้าจอทำอะไร และเชื่อมโยงกับหน้าไหนบ้าง</t>
         </is>
       </c>
       <c r="C18">
-        <v>49</v>
+        <v>642</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/importSets.js</t>
+          <t xml:space="preserve">lib/image.js</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
+          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
         </is>
       </c>
       <c r="C19">
-        <v>266</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/inventorySummary.js</t>
+          <t xml:space="preserve">lib/importSets.js</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
+          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
         </is>
       </c>
       <c r="C20">
-        <v>445</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/printForms.js</t>
+          <t xml:space="preserve">lib/inventorySummary.js</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
+          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
         </is>
       </c>
       <c r="C21">
-        <v>191</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/productTerms.js</t>
+          <t xml:space="preserve">lib/printForms.js</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
+          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
         </is>
       </c>
       <c r="C22">
-        <v>88</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/reportData.js</t>
+          <t xml:space="preserve">lib/productTerms.js</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
+          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C23">
-        <v>466</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/store.js</t>
+          <t xml:space="preserve">lib/reportData.js</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
+          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
         </is>
       </c>
       <c r="C24">
-        <v>1125</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/supabase.js</t>
+          <t xml:space="preserve">lib/store.js</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
         </is>
       </c>
       <c r="C25">
-        <v>389</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/targets.js</t>
+          <t xml:space="preserve">lib/supabase.js</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
+          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C26">
-        <v>140</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/thaiAddress.js</t>
+          <t xml:space="preserve">lib/targets.js</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
         </is>
       </c>
       <c r="C27">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/thaiAddress.js</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
         </is>
       </c>
       <c r="C28">
-        <v>321</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/xlsx.js</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/xlsxRead.js</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr" s="2">
+      <c r="B30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
         </is>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>223</v>
       </c>
     </row>
@@ -6826,6 +6924,18 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">คู่มือการใช้งานครอบคลุมทุกหน้าจอ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">29 ไฟล์</t>
+          <t xml:space="preserve">30 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">19 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">77 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 73 ครั้ง</t>
+          <t xml:space="preserve">78 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 74 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3175,6 +3175,55 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- โลโก้ใหม่: เปลวไฟสีส้มพร้อมไส้ในสีอ่อน และลูกศรเขียวพุ่งขึ้นลอดหลังเปลวไฟ
+แทนโลโก้ใบยางในวงกลมของเดิม
+- เปลี่ยนครบทุกจุดที่ใช้โลโก้: แถบเมนูซ้าย · หน้าเข้าสู่ระบบ ·
+หัวกระดาษที่พิมพ์ · หัวเอกสารการค้า · ไอคอน PWA ทุกขนาด ·
+ไอคอนแท็บเบราว์เซอร์ (favicon.ico) · รูปพรีวิวตอนแชร์ลิงก์
+- รูปทรงเก็บที่ lib/logo.js ที่เดียว แล้วให้ทั้งสองที่ใช้ชุดเดียวกัน:
+components/Icons.js วาดเป็น SVG · tools/make-icons.mjs วาดเป็น PNG
+เดิมไฟล์ไอคอนลอกรูปทรงไปเขียนซ้ำ พร้อมหมายเหตุว่า "ถ้าแก้โลโก้
+ให้แก้ที่นี่ด้วย" ซึ่งแปลว่าวันหนึ่งจะมีที่หนึ่งที่ลืมแก้
+แล้วไอคอนบนหน้าจอโฮมกับโลโก้ในเว็บจะคนละรูป โดยไม่มีใครสังเกต
+จนกว่าจะมีคนติดตั้งแอปใหม่
+- เก็บรูปทรงเป็นรูปหลายเหลี่ยมและเส้นต่อจุด ไม่ใช่เส้นโค้งเบซิเยร์
+เพราะตัววาด PNG ทดสอบ "จุดอยู่ในรูป" และ "ระยะถึงเส้น" ได้ตรง ๆ
+ส่วน SVG ก็วาดจากจุดชุดเดียวกันได้ ผลจึงตรงกันทั้งสองที่
+ที่ขนาดจริง (36-62 พิกเซล) ตาแยกไม่ออกจากเส้นโค้ง
+- สีของตราเป็นค่าคงที่ ไม่ผูกกับตัวแปรธีม
+เพราะตราที่เปลี่ยนสีตามพื้นหลังไม่ใช่ตราสัญลักษณ์แล้ว
+เขียวของลูกศรใช้โทนอ่อนกว่าเขียวหลัก จึงอ่านออกทั้งบนพื้นขาว
+และบนแถบเมนูสีเขียวเข้ม
+- Logo รับ prop bg แทน ring/leaf/vein เดิม (พื้นวงกลมจาง ๆ
+ใช้เฉพาะตอนวางบนพื้นสีใกล้เคียงกับตัวตรา เช่นแถบเมนู)
+- tools/make-icons.mjs เพิ่มการสร้างสองอย่างที่เดิมต้องใช้ PowerShell:
+favicon.ico (ห่อ PNG หลายขนาดในไฟล์เดียว เขียนหัวไฟล์เอง)
+และ og-image.png 1200x630 สำหรับพรีวิวตอนแชร์ลิงก์
+ทั้งโปรเจกต์จึงสร้างไอคอนได้ด้วย node อย่างเดียว ไม่ต้องพึ่ง Windows
+- รูปแชร์ลิงก์เป็นตราบนพื้นเขียว ไม่มีตัวหนังสือ
+เพราะสคริปต์ไม่มีตัววาดฟอนต์ และการวาดตัวอักษรเองทีละเส้น
+จะได้ผลแย่กว่าไม่มีเลย ชื่อโปรแกรมมีอยู่ในหัวข้อของลิงก์อยู่แล้ว
+- เพิ่มตัวตรวจหมวด 19: ทั้งสองที่ต้องอ่านรูปทรงจาก lib/logo.js
+ไม่มีใครนิยามรูปทรงซ้ำ ทุกจุดอยู่ในกรอบ 64x64 และสีไม่ผูกกับธีม
+ทดสอบแล้วว่าจับได้ทั้งกรณีลอกรูปทรงไปเขียนซ้ำ และจุดหลุดออกนอกกรอบ
+- ทดสอบ 26 ข้อ: รูปทรงอยู่ในกรอบ · คณิตศาสตร์ที่ตัววาด PNG ใช้
+(จุดในรูปหลายเหลี่ยม ระยะถึงส่วนของเส้น เส้นยาวศูนย์) ·
+ลำดับการซ้อนชั้น (เปลวไฟต้องทับลูกศร ไม่ใช่กลับกัน) ·
+และสัดส่วนพื้นที่ที่ตรากิน ต้องพอเห็นตอนย่อเป็นไอ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3212,12 +3261,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3229,29 +3278,29 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3312,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3329,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3346,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3363,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3380,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3397,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3414,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3431,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3399,12 +3448,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3465,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3482,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3499,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3516,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3533,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3550,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3567,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3535,12 +3584,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3601,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3618,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3586,29 +3635,29 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3669,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3686,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3703,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3720,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3688,29 +3737,29 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3771,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3788,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3805,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3822,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3839,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3856,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3873,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3890,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3907,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -3875,12 +3924,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3941,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3958,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3975,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -3943,12 +3992,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -3960,12 +4009,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -3977,12 +4026,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -3994,12 +4043,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4011,29 +4060,29 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4045,12 +4094,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4111,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4079,12 +4128,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4096,12 +4145,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4162,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4179,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4196,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4213,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4230,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4198,29 +4247,29 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4281,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4249,29 +4298,29 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4332,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4300,12 +4349,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4366,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4334,29 +4383,29 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4417,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4434,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4451,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4419,27 +4468,44 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr" s="2">
+      <c r="B75" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr" s="2">
+      <c r="C75" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -6479,135 +6545,150 @@
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/printForms.js</t>
+          <t xml:space="preserve">lib/logo.js</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
+          <t xml:space="preserve">ตราสัญลักษณ์ One for All Ultra (OFAU) — เปลวไฟกับลูกศรพุ่งขึ้น</t>
         </is>
       </c>
       <c r="C22">
-        <v>191</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/productTerms.js</t>
+          <t xml:space="preserve">lib/printForms.js</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
+          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
         </is>
       </c>
       <c r="C23">
-        <v>88</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/reportData.js</t>
+          <t xml:space="preserve">lib/productTerms.js</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
+          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C24">
-        <v>466</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/store.js</t>
+          <t xml:space="preserve">lib/reportData.js</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
+          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
         </is>
       </c>
       <c r="C25">
-        <v>1125</v>
+        <v>466</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/supabase.js</t>
+          <t xml:space="preserve">lib/store.js</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
         </is>
       </c>
       <c r="C26">
-        <v>389</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/targets.js</t>
+          <t xml:space="preserve">lib/supabase.js</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
+          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C27">
-        <v>140</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/thaiAddress.js</t>
+          <t xml:space="preserve">lib/targets.js</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
         </is>
       </c>
       <c r="C28">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/thaiAddress.js</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
         </is>
       </c>
       <c r="C29">
-        <v>321</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/xlsx.js</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/xlsxRead.js</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr" s="2">
+      <c r="B31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
         </is>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>223</v>
       </c>
     </row>
@@ -6936,6 +7017,18 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตราสัญลักษณ์มาจากรูปทรงชุดเดียว</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">78 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 74 ครั้ง</t>
+          <t xml:space="preserve">78 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 75 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3211,16 +3211,17 @@
 favicon.ico (ห่อ PNG หลายขนาดในไฟล์เดียว เขียนหัวไฟล์เอง)
 และ og-image.png 1200x630 สำหรับพรีวิวตอนแชร์ลิงก์
 ทั้งโปรเจกต์จึงสร้างไอคอนได้ด้วย node อย่างเดียว ไม่ต้องพึ่ง Windows
-- รูปแชร์ลิงก์เป็นตราบนพื้นเขียว ไม่มีตัวหนังสือ
+- พื้นของตราเป็นสีขาว ไม่ใช่เขียว
+ลองพื้นเขียวก่อนแล้วลูกศรเขียวจมหายไปกับพื้น เหลือแต่เปลวไฟให้เห็น
+พื้นขาวทำให้ทั้งเปลวไฟและลูกศรตัดกับพื้นชัดทั้งคู่ เหมือนตราต้นฉบับ
+และเพิ่มเส้นขอบจาง ๆ รอบวงกลม กันไอคอนพื้นขาวกลืนไปกับ
+หน้าจอโฮมที่พื้นหลังสว่าง
+- เขียวของลูกศรปรับให้เข้มขึ้นเล็กน้อย (#3F9152) เพื่อให้อ่านออกบนพื้นขาว
+- รูปแชร์ลิงก์เป็นตราบนพื้นขาว ไม่มีตัวหนังสือ
 เพราะสคริปต์ไม่มีตัววาดฟอนต์ และการวาดตัวอักษรเองทีละเส้น
 จะได้ผลแย่กว่าไม่มีเลย ชื่อโปรแกรมมีอยู่ในหัวข้อของลิงก์อยู่แล้ว
 - เพิ่มตัวตรวจหมวด 19: ทั้งสองที่ต้องอ่านรูปทรงจาก lib/logo.js
-ไม่มีใครนิยามรูปทรงซ้ำ ทุกจุดอยู่ในกรอบ 64x64 และสีไม่ผูกกับธีม
-ทดสอบแล้วว่าจับได้ทั้งกรณีลอกรูปทรงไปเขียนซ้ำ และจุดหลุดออกนอกกรอบ
-- ทดสอบ 26 ข้อ: รูปทรงอยู่ในกรอบ · คณิตศาสตร์ที่ตัววาด PNG ใช้
-(จุดในรูปหลายเหลี่ยม ระยะถึงส่วนของเส้น เส้นยาวศูนย์) ·
-ลำดับการซ้อนชั้น (เปลวไฟต้องทับลูกศร ไม่ใช่กลับกัน) ·
-และสัดส่วนพื้นที่ที่ตรากิน ต้องพอเห็นตอนย่อเป็นไอ</t>
+ไม่มีใครนิยามรูปทรงซ้ำ ทุกจุดอย</t>
         </is>
       </c>
     </row>
@@ -3261,12 +3262,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3278,12 +3279,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3295,29 +3296,29 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3330,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3347,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3364,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3380,12 +3381,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3397,12 +3398,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3415,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3432,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3449,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3466,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3483,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3500,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3516,12 +3517,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3534,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3551,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3568,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3585,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3602,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3619,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3636,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3652,29 +3653,29 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3687,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3704,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3721,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3738,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3754,29 +3755,29 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3789,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3806,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3823,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3839,12 +3840,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3857,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3874,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3890,12 +3891,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3908,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3925,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3942,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3959,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -3975,12 +3976,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -3992,12 +3993,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4010,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4027,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4043,12 +4044,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4060,12 +4061,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4077,29 +4078,29 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4111,12 +4112,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4129,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4146,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4162,12 +4163,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4179,12 +4180,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4197,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4214,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4230,12 +4231,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4248,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4264,29 +4265,29 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4299,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4315,29 +4316,29 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4349,12 +4350,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4367,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4384,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4400,29 +4401,29 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4434,12 +4435,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4452,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4469,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4485,27 +4486,44 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr" s="2">
+      <c r="B76" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr" s="2">
+      <c r="C76" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -6554,7 +6572,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">78 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 75 ครั้ง</t>
+          <t xml:space="preserve">78 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 76 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3313,29 +3313,29 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3415,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3449,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3517,12 +3517,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3534,12 +3534,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3568,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3602,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3619,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3636,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3670,29 +3670,29 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3721,12 +3721,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3755,12 +3755,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3772,29 +3772,29 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3840,12 +3840,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3874,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -3976,12 +3976,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4044,12 +4044,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4095,29 +4095,29 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4231,12 +4231,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4265,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4282,29 +4282,29 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4316,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4333,29 +4333,29 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4418,29 +4418,29 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4503,27 +4503,44 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr" s="2">
+      <c r="B77" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr" s="2">
+      <c r="C77" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -6572,7 +6589,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>153</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23">

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">78 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 76 ครั้ง</t>
+          <t xml:space="preserve">79 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 77 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3225,6 +3225,40 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80">
+        <v>80</v>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">โลโก้บนหน้าจอใช้ไฟล์ภาพต้นฉบับ แทนการวาดเลียนแบบ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- ผู้ใช้ส่งไฟล์ components/fav/NewLogo.jpg (1408x768) มาให้
+คัดลอกไปไว้ที่ public/logo.jpg แล้วให้หน้าจอแสดงไฟล์นั้นตรง ๆ
+- เลิกวาดตัวอักษร OFAU ด้วย &lt;text&gt; ของ SVG ที่ทำไว้รอบก่อน
+เพราะผลไม่เหมือนต้นฉบับ: ทรงตัวอักษรขึ้นกับฟอนต์ของเครื่องที่เปิด
+และรายละเอียดของเปลวไฟกับลูกศร (ไล่เฉดสี ปลายเรียว)
+วาดด้วยรูปหลายเหลี่ยมให้เหมือนไม่ได้
+ใช้ไฟล์ภาพจึงตรงกับต้นฉบับ 100% และไม่ต้องเพิ่มฟอนต์หรือไลบรารี
+- ใช้ไฟล์ภาพทุกที่ที่มีพื้นที่แนวนอน: หน้าเข้าสู่ระบบ · แถบเมนูซ้าย ·
+หัวกระดาษที่พิมพ์ · หัวเอกสารการค้า · รูปพรีวิวตอนแชร์ลิงก์
+- แถบเมนูเป็นสีเขียวเข้ม ตัวอักษรบนตราเป็นเขียวเข้มเหมือนกัน
+จึงวางตราบนแผ่นขาวมุมมน (.logo-plaque) ไม่งั้นอ่านไม่ออก
+- ที่อยู่ของไฟล์ประกาศที่เดียวใน lib/logo.js (LOGO_SRC)
+ตัวตรวจหมวด 19 กันไม่ให้หน้าจอเขียน "/logo.jpg" เอง
+เปลี่ยนชื่อไฟล์ทีเดียวแล้วเปลี่ยนตามทุกที่ รวมถึง metadata ของ Open Graph
+- ไอคอนแอปและไอคอนแท็บยังเป็นตราย่อที่วาดด้วยโค้ด (เปลวไฟกับลูกศร)
+เพราะเป็นกรอบจัตุรัสเล็ก ตราแนวนอนย่อลงไปแล้วอ่านตัวอักษรไม่ออก
+และตัวสร้างไอคอนไม่มีตัวถอดรหัส JPEG จะอ่านไฟล์ภาพมาทำไอคอนไม่ได้
+- ลบคอมโพเนนต์ Logo (ตราย่อบนหน้าจอ) ที่ไม่มีใครใช้แล้วออก
+รูปทรงยังอยู่ใน lib/logo.js เพราะตัวสร้างไอคอนใช้
+- รูปพรีวิวตอนแชร์ลิงก์ที่เคยสร้างเป็น PNG ถูกลบทิ้ง ใช้ไฟล์โลโก้จริงแทน</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3262,12 +3296,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3313,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3330,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3313,12 +3347,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3330,29 +3364,29 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3398,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3415,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3432,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3449,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3466,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3483,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3500,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3517,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3534,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3517,12 +3551,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3534,12 +3568,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3585,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3602,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3619,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3636,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3653,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3670,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3687,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3704,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3687,29 +3721,29 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3721,12 +3755,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3738,12 +3772,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3755,12 +3789,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3772,12 +3806,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3789,29 +3823,29 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3857,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3840,12 +3874,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3891,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3908,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3925,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3942,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3959,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3976,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -3959,12 +3993,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -3976,12 +4010,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -3993,12 +4027,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4044,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4061,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4044,12 +4078,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4095,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4112,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4095,12 +4129,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4112,29 +4146,29 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4180,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4197,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4214,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4231,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4248,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4231,12 +4265,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4282,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4299,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4316,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4299,29 +4333,29 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4333,12 +4367,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4350,29 +4384,29 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4418,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4435,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4452,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4435,29 +4469,29 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4503,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4520,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4503,12 +4537,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4520,27 +4554,44 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr" s="2">
+      <c r="B78" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr" s="2">
+      <c r="C78" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -6589,7 +6640,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23">

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -102,7 +102,7 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">79 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 77 ครั้ง</t>
+          <t xml:space="preserve">80 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 78 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3259,6 +3259,53 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81">
+        <v>81</v>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้งานได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- รอบก่อนเอา NewLogo.jpg มาวางตรง ๆ ซึ่งยังใช้ไม่ได้จริงสามข้อ:
+1. พื้นหลังเป็นเทาอ่อน ~#F0F0F0 ไม่ใช่ขาว วางบนการ์ดขาวแล้วเห็นเป็นกล่องเทา
+2. ขอบว่างรอบตรากว้างมาก พอกำหนดความสูงเป็นพิกเซล ตัวตราจึงเล็กกว่าที่ควร
+3. JPEG ไม่มีความโปร่งใส และมีรอยหยักรอบตัวอักษรจากการบีบอัด
+- เพิ่ม tools/trim-logo.ps1 แก้ทั้งสามข้อแล้วสร้างไฟล์ปลายทางครบ 8 ไฟล์
+ตัดขอบว่าง 1408x768 -&gt; 728x527 · คีย์พื้นหลังให้โปร่งใส
+และถอดสีพื้นออกจากขอบที่ถูกเกลี่ย (c = (c_obs - BG*(1-a)) / a)
+ไม่งั้นขอบตัวอักษรจะติดคราบเทาของพื้นเดิมไปด้วย
+- ตราเต็มมีสองฉบับ ขนาดเท่ากันเป๊ะ: logo.png ตัวอักษรเขียวเข้ม
+กับ logo-light.png ตัวอักษรขาว สำหรับแถบเมนูสีเข้ม
+เลิกใช้แผ่นขาวมุมมน (.logo-plaque) ที่ทำไว้รอบก่อน เพราะดูเป็นป้ายแปะทับเมนู
+- ไอคอนแอปกับไอคอนแท็บเลิกวาดเลียนแบบด้วยรูปหลายเหลี่ยมแล้ว
+ตัดเปลวไฟกับลูกศรจากภาพจริงมาเป็นจัตุรัสแทน ทั้ง 6 ไฟล์
+จึงเป็นตราเดียวกับที่เห็นบนหน้าจอ ไม่ใช่ของที่วาดให้คล้าย
+- หากรอบครอปเองจากตัวภาพ ไม่ต้องกรอกพิกัดมือ:
+หาหัวตัวอักษรจากแถวแรกที่เนื้อหากว้างเกินครึ่งภาพ (ตัวอักษรกินเกือบเต็มความกว้าง
+ส่วนเปลวไฟกับลูกศรกินไม่ถึงครึ่ง) แล้วระบายก้อนที่ติดกันเหนือแถวนั้น
+เก็บเฉพาะก้อนที่ใหญ่กว่าหนึ่งในสิบของก้อนใหญ่สุด
+- ที่ต้องคัดด้วยขนาดก้อน ไม่ใช่ด้วยสีหรือด้วยแถว:
+หัวตัว A กับ O โผล่ขึ้นเหนือหัวตัวอักษรก่อนตัวอื่น (219 กับ 114 จุด)
+ตัดด้วยแถวเฉย ๆ จึงติดหัวตัวอักษรมาโผล่ในไอคอน
+คัดด้วยสีก็ไม่ได้ เพราะใต้ลูกศรเป็นเขียวเข้มเท่ากับตัวอักษร
+แต่ขนาดก้อนต่างกันสิบเท่า (เปลวไฟ 16298 ลูกศร 14269) จึงแยกได้ขาด
+วิธีนี้กำจัดจุดสีหลงจาก JPEG ไปด้วยในตัว
+(ก่อนหน้านี้จุดหลงจุดเดียวที่ขอบซ้ายดันกรอบกว้างจาก 276 เป็น 470
+ตราในไอคอนเลยเล็กและเบี้ยว)
+- ลบ tools/make-icons.mjs (วาดไอคอนจากรูปหลายเหลี่ยม)
+ลบ tools/make-icons.ps1 และ tools/make-og-image.ps1 ที่ไม่มีใครเรียกแล้ว
+ลบรูปทรงทั้งหมดออกจาก lib/logo.js เหลือแค่ที่อยู่ไฟล์กับสัดส่วน
+- ตัวตรวจหมวด 19 เขียนใหม่ทั้งหมด จากเดิมที่ตรวจรูปทรง เปลี่ยนเป็นตรวจไฟล์จริง:
+อ่านขนาดจากหัวไฟล์ PNG (IHDR) มาเทียบกับ LOGO_RATIO ที่ประกาศไว้
+ตราสองฉบับต้องขนาดเท่ากัน · ต้องมีชั้นความโปร่งใส (color type 4 หรือ 6)
+ไอคอนครบทุกไฟล์และขนาดตรง · ไฟล์ใน app/man</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3296,12 +3343,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3313,12 +3360,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3330,12 +3377,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3394,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3411,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3381,29 +3428,29 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3462,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3479,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3496,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3513,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3530,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3547,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3517,12 +3564,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3534,12 +3581,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3598,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3615,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3632,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3602,12 +3649,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3666,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3683,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3700,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3717,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3734,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3751,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3721,12 +3768,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3738,29 +3785,29 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3772,12 +3819,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3836,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3853,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3870,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3840,29 +3887,29 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3921,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3938,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3955,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3972,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3989,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -3959,12 +4006,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3976,12 +4023,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -3993,12 +4040,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4057,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4074,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4044,12 +4091,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4108,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4125,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4095,12 +4142,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4112,12 +4159,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4176,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4193,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4163,29 +4210,29 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4244,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4261,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4231,12 +4278,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4295,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4265,12 +4312,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4329,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4299,12 +4346,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4363,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4333,12 +4380,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4350,29 +4397,29 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4431,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4401,29 +4448,29 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4435,12 +4482,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4499,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4516,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4486,29 +4533,29 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4567,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4537,12 +4584,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4554,12 +4601,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4571,27 +4618,44 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr" s="2">
+      <c r="B79" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr" s="2">
+      <c r="C79" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -6636,11 +6700,11 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตราสัญลักษณ์ One for All Ultra (OFAU) — เปลวไฟกับลูกศรพุ่งขึ้น</t>
+          <t xml:space="preserve">ตราสัญลักษณ์ One for All Ultra (OFAU) — เปลวไฟกับลูกศรพุ่งขึ้นเหนือตัวอักษร OFAU</t>
         </is>
       </c>
       <c r="C22">
-        <v>175</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -7111,7 +7175,7 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตราสัญลักษณ์มาจากรูปทรงชุดเดียว</t>
+          <t xml:space="preserve">ตราสัญลักษณ์มาจากไฟล์ภาพต้นฉบับไฟล์เดียว</t>
         </is>
       </c>
     </row>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -198,7 +198,7 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
+          <t xml:space="preserve">49 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
         </is>
       </c>
     </row>
@@ -210,7 +210,7 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">30 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
+          <t xml:space="preserve">36 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
         </is>
       </c>
     </row>
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">30 ไฟล์</t>
+          <t xml:space="preserve">34 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -234,7 +234,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">45 ไฟล์</t>
+          <t xml:space="preserve">53 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">20 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">80 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 78 ครั้ง</t>
+          <t xml:space="preserve">81 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 79 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3306,6 +3306,55 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82">
+        <v>82</v>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- ผู้ใช้ขอระบบตามเกณฑ์ประเมินรัฐวิสาหกิจ หมวด 3 น้ำหนัก 10%
+สองข้อย่อย (3.1 การรับฟังลูกค้า · 3.2 การประเมินความพึงพอใจ
+ความไม่พึงพอใจ และความผูกพัน) ข้อละ 5 ระดับ
+พร้อมคู่มือ ผังการทำงาน ไฟล์นำเสนอ และรายงานความคืบหน้าให้ผู้บริหาร
+- แยกเป็นกลุ่มเมนูของตัวเองตามที่สั่ง ไม่ปนกับหน้าจออื่น
+7 หน้าจอ: ภาพรวม · ช่องทางการรับฟัง · เสียงของลูกค้า ·
+ประเมินความพึงพอใจ · ประเมินระดับตามเกณฑ์ · แผนปรับปรุงและนวัตกรรม ·
+รายงานและนำเสนอ
+- 6 ตารางใหม่ (รวมเป็น 36 ตาราง): voc_channels · voc_records ·
+voc_surveys · voc_survey_results · voc_actions · voc_levels
+- เก็บข้อความของเกณฑ์ทั้ง 10 ระดับตามต้นฉบับ ไม่ย่อ ไม่ตีความใหม่
+เพราะเวลาถูกตรวจจริง ผู้ตรวจอ่านจากต้นฉบับ
+- แตกเกณฑ์เป็นจุดตรวจ 43 ข้อ ที่ตรวจได้จริงทีละข้อ
+37 ข้อระบบตรวจให้เองจากข้อมูลจริง เหลือ 6 ข้อที่ให้คนยืนยัน
+และการยืนยันต้องแนบหลักฐานเสมอ ติ๊กเปล่า ๆ ระบบไม่นับให้
+- ทุกตัวตรวจบอกเหตุผลเสมอ ไม่ใช่แค่ผ่าน/ไม่ผ่าน
+เช่น "ยังขาดกลุ่มลูกค้าด้านส่งเสริม" หรือ
+"4 ไตรมาสล่าสุดมีรายงานเพียง 2 ไตรมาส (ยังขาด 2 ไตรมาส)"
+- ระดับเป็นแบบสะสม ระดับที่ผ่านแบบข้ามขั้นแสดงให้เห็นแต่ไม่นับ
+และระดับของทั้งหมวดตัดสินจากข้อย่อยที่อ่อนที่สุด ไม่ใช่ค่าเฉลี่ย
+- เพิ่ม lib/pptx.js เขียนไฟล์ PowerPoint (.pptx) เองทั้งไฟล์
+ไม่ใช้ไลบรารี ตามข้อกำหนดที่ไม่เพิ่ม dependency
+แยกตัวประกอบ zip ออกมาที่ lib/zip.js ให้ .xlsx กับ .pptx ใช้ร่วมกัน
+(เดิม zip อยู่ใน xlsx.js ที่เดียว ถ้าปล่อยให้ pptx เขียนซ้ำ
+วันแก้บั๊กของตัวประกอบ zip จะต้องไล่แก้สองที่ แล้วจะลืมที่หนึ่ง)
+- สิ่งที่ PowerPoint บังคับและขาดไม่ได้แม้ไฟล์เดียว:
+[Content_Types].xml · _rels/.rels · presentation.xml ·
+slideMaster · slideLayout · theme (ต้องมี fillStyleLst/lnStyleLst/
+effectStyleLst/bgFillStyleLst อย่างละ 3 แบบเป๊ะ) และ .rels ของทุกส่วน
+ขาดอันเดียวจะฟ้องว่า "ไฟล์เสียหาย" โดยไม่บอกว่าเสียตรงไหน
+- วางตำแหน่งทุกอย่างเป็นพิกัดตรง ๆ ไม่ใช้ placeholder ของเค้าโครง
+placeholder ต้องพึ่งเค้าโครงและแม่แบบให้ตรงกันเป๊ะ ผิดนิดเดียว
+PowerPoint จะซ่อนข้อความทิ้งเงียบ ๆ โดยไม่ฟ้อง
+- ตั้งฟอนต์ที่ a:cs ด้วย ไม่ใช่แค่ a:latin เพราะข้อความไทยถูกจัดเป็น
+complex script ตั้งแต่ latin อย่างเดียวสระจะลอ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3338,17 +3387,17 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3360,12 +3409,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3377,12 +3426,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3443,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3411,12 +3460,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3428,12 +3477,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3445,29 +3494,29 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3528,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3496,12 +3545,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3513,12 +3562,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3530,12 +3579,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3547,12 +3596,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3613,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3630,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3598,12 +3647,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3615,12 +3664,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3681,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3649,12 +3698,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3666,12 +3715,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3732,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3749,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3766,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3783,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3751,12 +3800,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3768,12 +3817,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3834,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3802,29 +3851,29 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3885,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3853,12 +3902,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3870,12 +3919,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3936,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3904,29 +3953,29 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3987,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -3955,12 +4004,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -3972,12 +4021,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -3989,12 +4038,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4055,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4072,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4089,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4057,12 +4106,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4123,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4140,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4157,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4125,12 +4174,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4191,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4208,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4225,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4242,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4259,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4227,29 +4276,29 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4310,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4278,12 +4327,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4295,12 +4344,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4361,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4329,12 +4378,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4395,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4412,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4429,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4446,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4414,29 +4463,29 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4497,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4465,29 +4514,29 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4548,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4565,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4582,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4550,29 +4599,29 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4633,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4650,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4618,12 +4667,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4635,27 +4684,44 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr" s="2">
+      <c r="B80" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr" s="2">
+      <c r="C80" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -5180,376 +5246,376 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
+          <t xml:space="preserve">ภาพรวมการรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
+          <t xml:space="preserve">ระดับตามเกณฑ์ เสียงลูกค้า และงานที่ค้าง</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipScan.js</t>
+          <t xml:space="preserve">components/views/VocDash.js</t>
         </is>
       </c>
       <c r="E21">
-        <v>454</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดส่งสินค้า</t>
+          <t xml:space="preserve">ช่องทางการรับฟัง</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
+          <t xml:space="preserve">ทะเบียนช่องทางและความครอบคลุมตามเกณฑ์</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Shipping.js</t>
+          <t xml:space="preserve">components/views/VocChannels.js</t>
         </is>
       </c>
       <c r="E22">
-        <v>623</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานะการจัดส่ง</t>
+          <t xml:space="preserve">เสียงของลูกค้า</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
+          <t xml:space="preserve">บันทึกทีละเรื่อง จำแนกครบทุกมิติ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipStatus.js</t>
+          <t xml:space="preserve">components/views/VocRecords.js</t>
         </is>
       </c>
       <c r="E23">
-        <v>593</v>
+        <v>515</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
+          <t xml:space="preserve">ประเมินความพึงพอใจ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
+          <t xml:space="preserve">รอบประเมิน ความผูกพัน และผลรายกลุ่ม</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/BillImport.js</t>
+          <t xml:space="preserve">components/views/VocSurveys.js</t>
         </is>
       </c>
       <c r="E24">
-        <v>892</v>
+        <v>629</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">การรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลสินค้า</t>
+          <t xml:space="preserve">ประเมินระดับตามเกณฑ์</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
+          <t xml:space="preserve">จุดตรวจ 5 ระดับ พร้อมหลักฐาน</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Products.js</t>
+          <t xml:space="preserve">components/views/VocLevels.js</t>
         </is>
       </c>
       <c r="E25">
-        <v>187</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">การรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สินค้าตามจังหวัด</t>
+          <t xml:space="preserve">แผนปรับปรุงและนวัตกรรม</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
+          <t xml:space="preserve">รายงานผู้บริหาร ความรู้ และการนำไปใช้</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Provinces.js</t>
+          <t xml:space="preserve">components/views/VocActions.js</t>
         </is>
       </c>
       <c r="E26">
-        <v>401</v>
+        <v>491</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">การรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
+          <t xml:space="preserve">รายงานและนำเสนอ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
+          <t xml:space="preserve">ส่งออก Excel และไฟล์ PowerPoint</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Locations.js</t>
+          <t xml:space="preserve">components/views/VocReports.js</t>
         </is>
       </c>
       <c r="E27">
-        <v>697</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียดลูกค้า</t>
+          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
+          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Customers.js</t>
+          <t xml:space="preserve">components/views/ShipScan.js</t>
         </is>
       </c>
       <c r="E28">
-        <v>548</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
+          <t xml:space="preserve">การจัดส่งสินค้า</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
+          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DocGroups.js</t>
+          <t xml:space="preserve">components/views/Shipping.js</t>
         </is>
       </c>
       <c r="E29">
-        <v>357</v>
+        <v>623</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
+          <t xml:space="preserve">สถานะการจัดส่ง</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
+          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PrintForms.js</t>
+          <t xml:space="preserve">components/views/ShipStatus.js</t>
         </is>
       </c>
       <c r="E30">
-        <v>525</v>
+        <v>593</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
+          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
+          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
+          <t xml:space="preserve">components/views/BillImport.js</t>
         </is>
       </c>
       <c r="E31">
-        <v>610</v>
+        <v>892</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลกิจการ</t>
+          <t xml:space="preserve">ข้อมูลสินค้า</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
+          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Company.js</t>
+          <t xml:space="preserve">components/views/Products.js</t>
         </is>
       </c>
       <c r="E32">
-        <v>164</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองข้อมูล</t>
+          <t xml:space="preserve">สินค้าตามจังหวัด</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
+          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Backup.js</t>
+          <t xml:space="preserve">components/views/Provinces.js</t>
         </is>
       </c>
       <c r="E33">
-        <v>292</v>
+        <v>401</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
+          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
+          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Users.js</t>
+          <t xml:space="preserve">components/views/Locations.js</t>
         </is>
       </c>
       <c r="E34">
-        <v>232</v>
+        <v>697</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
+          <t xml:space="preserve">รายละเอียดลูกค้า</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SQL Server / MySQL / Access</t>
+          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/SqlServer.js</t>
+          <t xml:space="preserve">components/views/Customers.js</t>
         </is>
       </c>
       <c r="E35">
-        <v>748</v>
+        <v>548</v>
       </c>
     </row>
     <row r="36">
@@ -5560,21 +5626,21 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
+          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
+          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DataImport.js</t>
+          <t xml:space="preserve">components/views/DocGroups.js</t>
         </is>
       </c>
       <c r="E36">
-        <v>894</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37">
@@ -5585,21 +5651,21 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดพนักงานขาย</t>
+          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
+          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Salespersons.js</t>
+          <t xml:space="preserve">components/views/PrintForms.js</t>
         </is>
       </c>
       <c r="E37">
-        <v>308</v>
+        <v>525</v>
       </c>
     </row>
     <row r="38">
@@ -5610,21 +5676,21 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
+          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ProductTerms.js</t>
+          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
         </is>
       </c>
       <c r="E38">
-        <v>321</v>
+        <v>610</v>
       </c>
     </row>
     <row r="39">
@@ -5635,21 +5701,21 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
+          <t xml:space="preserve">ข้อมูลกิจการ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
+          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/CustomerKinds.js</t>
+          <t xml:space="preserve">components/views/Company.js</t>
         </is>
       </c>
       <c r="E39">
-        <v>372</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40">
@@ -5660,95 +5726,270 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">สำรองข้อมูล</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Password.js</t>
+          <t xml:space="preserve">components/views/Backup.js</t>
         </is>
       </c>
       <c r="E40">
-        <v>170</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Reports.js</t>
+          <t xml:space="preserve">components/views/Users.js</t>
         </is>
       </c>
       <c r="E41">
-        <v>2578</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุป</t>
+          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+          <t xml:space="preserve">SQL Server / MySQL / Access</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Graphs.js</t>
+          <t xml:space="preserve">components/views/SqlServer.js</t>
         </is>
       </c>
       <c r="E42">
-        <v>499</v>
+        <v>748</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/DataImport.js</t>
+        </is>
+      </c>
+      <c r="E43">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กำหนดพนักงานขาย</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Salespersons.js</t>
+        </is>
+      </c>
+      <c r="E44">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/ProductTerms.js</t>
+        </is>
+      </c>
+      <c r="E45">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/CustomerKinds.js</t>
+        </is>
+      </c>
+      <c r="E46">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Password.js</t>
+        </is>
+      </c>
+      <c r="E47">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">รายงาน</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr" s="2">
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Reports.js</t>
+        </is>
+      </c>
+      <c r="E48">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กราฟสรุป</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Graphs.js</t>
+        </is>
+      </c>
+      <c r="E49">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สร้างรายงาน</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr" s="2">
+      <c r="C50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">เลือกคอลัมน์และจัดรูปแบบเอง</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr" s="2">
+      <c r="D50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">components/views/ReportBuilder.js</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E50">
         <v>537</v>
       </c>
     </row>
@@ -6345,18 +6586,108 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">voc_channels</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>16</v>
+      </c>
+      <c r="D31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, code, name, kind, groups, lifecycle, dimension, freq, owner, practice, note, active, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">voc_records</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>24</v>
+      </c>
+      <c r="D32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, code, date, channel_id, group_id, lifecycle, dimension, product_id, kind, priority, status, customer_id, party_name, province, subject, detail, response, owner, due_date, closed_date, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">voc_surveys</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>22</v>
+      </c>
+      <c r="D33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, code, name, kind, fiscal_year, purpose, form, freq, method, sampling, sample_size, responded, start_date, end_date, status, vendor, owner, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">voc_survey_results</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>14</v>
+      </c>
+      <c r="D34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, survey_id, group_id, product_id, dimension, score, full_score, respondents, benchmark, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">voc_actions</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>18</v>
+      </c>
+      <c r="D35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, code, kind, crit, title, detail, record_id, survey_id, owner, due_date, done_date, status, result, store_url, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">voc_levels</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>13</v>
+      </c>
+      <c r="D36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, crit, level, check_id, done, evidence, owner, done_date, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">screen_perms</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr" s="2">
+      <c r="B37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สิทธิการใช้งานรายหน้าจอ (ดู / แก้ไข / เปลี่ยนวันที่)</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C37">
         <v>6</v>
       </c>
-      <c r="D31" t="inlineStr" s="2">
+      <c r="D37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">id, can_view, can_edit, can_date, created_at, row_order</t>
         </is>
@@ -6403,7 +6734,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>2206</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="3">
@@ -6509,7 +6840,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10">
@@ -6644,7 +6975,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>642</v>
+        <v>760</v>
       </c>
     </row>
     <row r="19">
@@ -6710,136 +7041,196 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/printForms.js</t>
+          <t xml:space="preserve">lib/pptx.js</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์นำเสนอ PowerPoint (.pptx) จริง — เขียน XML เอง ไม่ใช้ไลบรารี</t>
         </is>
       </c>
       <c r="C23">
-        <v>191</v>
+        <v>652</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/productTerms.js</t>
+          <t xml:space="preserve">lib/printForms.js</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
+          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
         </is>
       </c>
       <c r="C24">
-        <v>88</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/reportData.js</t>
+          <t xml:space="preserve">lib/productTerms.js</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
+          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C25">
-        <v>466</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/store.js</t>
+          <t xml:space="preserve">lib/reportData.js</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
+          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
         </is>
       </c>
       <c r="C26">
-        <v>1125</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/supabase.js</t>
+          <t xml:space="preserve">lib/store.js</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
         </is>
       </c>
       <c r="C27">
-        <v>389</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/targets.js</t>
+          <t xml:space="preserve">lib/supabase.js</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
+          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C28">
-        <v>140</v>
+        <v>389</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/thaiAddress.js</t>
+          <t xml:space="preserve">lib/targets.js</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
         </is>
       </c>
       <c r="C29">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/thaiAddress.js</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
         </is>
       </c>
       <c r="C30">
-        <v>321</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/voc.js</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การรับฟังลูกค้า (SE-AM หมวด 3) — กติกา เกณฑ์ และการคำนวณทั้งหมด</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">lib/vocReport.js</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงานของหมวดการรับฟังลูกค้า — ประกอบตารางและไฟล์นำเสนอจากข้อมูลชุดเดียว</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">lib/xlsx.js</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/xlsxRead.js</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr" s="2">
+      <c r="B34" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C34">
         <v>223</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">lib/zip.js</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ประกอบไฟล์ zip เอง — ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -7179,6 +7570,18 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หมวดการรับฟังลูกค้าต่อครบทุกชั้น</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">34 ไฟล์</t>
+          <t xml:space="preserve">36 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">81 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 79 ครั้ง</t>
+          <t xml:space="preserve">82 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 80 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3355,6 +3355,44 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83">
+        <v>83</v>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- ผู้ใช้ขอไฟล์สรุปวิธีใช้งานแต่ละหน้าจอ พร้อมตัวอย่างการทำ เป็นไฟล์ Word
+- เพิ่ม lib/docx.js เขียนไฟล์ .docx เองทั้งไฟล์ ไม่ใช้ไลบรารี
+ใช้ตัวประกอบ zip ตัวเดียวกับ .xlsx และ .pptx ที่ lib/zip.js
+ตอนนี้ lib/zip.js จึงรองรับ Open XML ครบทั้งสามชนิดแล้ว
+- เพิ่ม lib/vocManual.js เก็บเนื้อหาคู่มือเป็นข้อมูล ไม่ใช่ไฟล์ Word ที่พิมพ์ทิ้งไว้
+ดึงข้อความเกณฑ์ จุดตรวจ และรายการตั้งต้นจาก lib/voc.js โดยตรง
+แก้เกณฑ์ที่เดียว คู่มือเปลี่ยนตามเองทั้งเล่ม
+- เล่มที่ได้: 14 หัวข้อใหญ่ · 43 ตาราง · 221 บล็อกเนื้อหา (496 KB)
+ทุกบทของหน้าจอมีตารางตัวอย่างการกรอกจริงพร้อมค่าที่ควรใส่ทุกช่อง
+และมีบทเดินให้ดูทั้งกระบวนการตั้งแต่ตั้งช่องทางจนได้ระดับ 5
+- เพิ่ม tools/make-voc-manual.mjs สร้างไฟล์ไว้ในโครงงานที่
+Docs/คู่มือการรับฟังลูกค้า.docx คนที่เพิ่งเข้ามาจะได้อ่านได้ทันที
+โดยไม่ต้องเปิดระบบก่อน และมีปุ่ม คู่มือ Word ที่หน้ารายงานด้วย
+- ใส่นามสกุล .js ให้ import ของ lib/voc.js lib/vocManual.js และ
+lib/vocReport.js เพื่อให้เครื่องมือที่รันด้วย Node ตรง ๆ อ่านได้
+(webpack ของ Next รับได้ทั้งสองแบบ แต่ Node ต้องการนามสกุลเสมอ)
+- ขยายตัวตรวจหมวด 20: คู่มือต้องมีบทครบทุกหน้าจอ ทุกบทต้องบอกครบว่า
+ทำอะไร ใครใช้ ใช้ตอนไหน ได้อะไร และตอบเกณฑ์ข้อไหน ·
+ไฟล์คู่มือในโครงงานต้องมีอยู่จริงและเปิดได้ ·
+lib/docx.js ต้องสร้างส่วนที่ Word บังคับครบและต้องมีตัวกันช่องตารางว่าง
+ทดสอบย้อน 3 กรณี จับได้ทุกกรณี
+- ทดสอบ 51 ข้อ และแกะไฟล์ .docx ที่สร้างได้ด้วย System.IO.Compression
+ของวินโดวส์ ยืนยันว่าเป็น zip ที่ถูกต้อง ทุกส่วนเป็น XML ที่ parse ผ่าน
+และไม่มีช่องตารางว่างเปล่าเลยสักช่องจาก 1,049 ช่อง</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3392,29 +3430,29 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3464,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3443,12 +3481,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3498,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3515,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3532,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3511,29 +3549,29 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3583,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3600,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3617,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3634,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3651,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3630,12 +3668,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3685,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3664,12 +3702,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3681,12 +3719,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3736,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3753,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3770,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3787,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3804,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3821,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3838,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3855,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3872,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3889,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3868,29 +3906,29 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3940,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3919,12 +3957,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3974,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -3953,12 +3991,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -3970,29 +4008,29 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4042,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4059,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4076,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4093,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4110,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4127,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4144,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4123,12 +4161,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4178,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4195,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4212,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4191,12 +4229,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4246,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4263,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4280,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4297,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4276,12 +4314,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4293,29 +4331,29 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4365,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4382,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4399,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4416,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4433,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4450,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4467,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4484,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4501,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4480,29 +4518,29 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4552,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4531,29 +4569,29 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4603,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4620,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4637,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4616,29 +4654,29 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4650,12 +4688,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4705,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4684,12 +4722,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4701,27 +4739,44 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr" s="2">
+      <c r="B81" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr" s="2">
+      <c r="C81" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -5415,7 +5470,7 @@
         </is>
       </c>
       <c r="E27">
-        <v>196</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28">
@@ -6921,315 +6976,345 @@
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/format.js</t>
+          <t xml:space="preserve">lib/docx.js</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟังก์ชันจัดรูปแบบข้อมูลสำหรับแสดงผล</t>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์เอกสาร Word (.docx) จริง — เขียน XML เอง ไม่ใช้ไลบรารี</t>
         </is>
       </c>
       <c r="C15">
-        <v>225</v>
+        <v>509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/gemini.js</t>
+          <t xml:space="preserve">lib/format.js</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Gemini API แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">ฟังก์ชันจัดรูปแบบข้อมูลสำหรับแสดงผล</t>
         </is>
       </c>
       <c r="C16">
-        <v>504</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/geo.js</t>
+          <t xml:space="preserve">lib/gemini.js</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คณิตศาสตร์ของแผนที่ (Web Mercator) และการค้นหาสถานที่</t>
+          <t xml:space="preserve">ตัวเชื่อม Gemini API แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C17">
-        <v>167</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/guide.js</t>
+          <t xml:space="preserve">lib/geo.js</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือการใช้งาน — อธิบายว่าแต่ละหน้าจอทำอะไร และเชื่อมโยงกับหน้าไหนบ้าง</t>
+          <t xml:space="preserve">คณิตศาสตร์ของแผนที่ (Web Mercator) และการค้นหาสถานที่</t>
         </is>
       </c>
       <c r="C18">
-        <v>760</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/image.js</t>
+          <t xml:space="preserve">lib/guide.js</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
+          <t xml:space="preserve">คู่มือการใช้งาน — อธิบายว่าแต่ละหน้าจอทำอะไร และเชื่อมโยงกับหน้าไหนบ้าง</t>
         </is>
       </c>
       <c r="C19">
-        <v>49</v>
+        <v>760</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/importSets.js</t>
+          <t xml:space="preserve">lib/image.js</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
+          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
         </is>
       </c>
       <c r="C20">
-        <v>266</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/inventorySummary.js</t>
+          <t xml:space="preserve">lib/importSets.js</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
+          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
         </is>
       </c>
       <c r="C21">
-        <v>445</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/logo.js</t>
+          <t xml:space="preserve">lib/inventorySummary.js</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตราสัญลักษณ์ One for All Ultra (OFAU) — เปลวไฟกับลูกศรพุ่งขึ้นเหนือตัวอักษร OFAU</t>
+          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
         </is>
       </c>
       <c r="C22">
-        <v>32</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/pptx.js</t>
+          <t xml:space="preserve">lib/logo.js</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์นำเสนอ PowerPoint (.pptx) จริง — เขียน XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">ตราสัญลักษณ์ One for All Ultra (OFAU) — เปลวไฟกับลูกศรพุ่งขึ้นเหนือตัวอักษร OFAU</t>
         </is>
       </c>
       <c r="C23">
-        <v>652</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/printForms.js</t>
+          <t xml:space="preserve">lib/pptx.js</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์นำเสนอ PowerPoint (.pptx) จริง — เขียน XML เอง ไม่ใช้ไลบรารี</t>
         </is>
       </c>
       <c r="C24">
-        <v>191</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/productTerms.js</t>
+          <t xml:space="preserve">lib/printForms.js</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
+          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
         </is>
       </c>
       <c r="C25">
-        <v>88</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/reportData.js</t>
+          <t xml:space="preserve">lib/productTerms.js</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
+          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C26">
-        <v>466</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/store.js</t>
+          <t xml:space="preserve">lib/reportData.js</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
+          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
         </is>
       </c>
       <c r="C27">
-        <v>1294</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/supabase.js</t>
+          <t xml:space="preserve">lib/store.js</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
         </is>
       </c>
       <c r="C28">
-        <v>389</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/targets.js</t>
+          <t xml:space="preserve">lib/supabase.js</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
+          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C29">
-        <v>140</v>
+        <v>389</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/thaiAddress.js</t>
+          <t xml:space="preserve">lib/targets.js</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
         </is>
       </c>
       <c r="C30">
-        <v>166</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/voc.js</t>
+          <t xml:space="preserve">lib/thaiAddress.js</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (SE-AM หมวด 3) — กติกา เกณฑ์ และการคำนวณทั้งหมด</t>
+          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
         </is>
       </c>
       <c r="C31">
-        <v>1033</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/vocReport.js</t>
+          <t xml:space="preserve">lib/voc.js</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานของหมวดการรับฟังลูกค้า — ประกอบตารางและไฟล์นำเสนอจากข้อมูลชุดเดียว</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (SE-AM หมวด 3) — กติกา เกณฑ์ และการคำนวณทั้งหมด</t>
         </is>
       </c>
       <c r="C32">
-        <v>498</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/vocManual.js</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">คู่มือการใช้งานหมวดการรับฟังลูกค้า — เนื้อหาของไฟล์ Word</t>
         </is>
       </c>
       <c r="C33">
-        <v>253</v>
+        <v>864</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsxRead.js</t>
+          <t xml:space="preserve">lib/vocReport.js</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
+          <t xml:space="preserve">รายงานของหมวดการรับฟังลูกค้า — ประกอบตารางและไฟล์นำเสนอจากข้อมูลชุดเดียว</t>
         </is>
       </c>
       <c r="C34">
-        <v>223</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/xlsx.js</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">lib/xlsxRead.js</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/zip.js</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr" s="2">
+      <c r="B37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ประกอบไฟล์ zip เอง — ไม่ใช้ไลบรารี</t>
         </is>
       </c>
-      <c r="C35">
+      <c r="C37">
         <v>124</v>
       </c>
     </row>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">82 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 80 ครั้ง</t>
+          <t xml:space="preserve">83 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 81 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3393,6 +3393,55 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84">
+        <v>84</v>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- ผู้ใช้แจ้งว่าเจอ error บางหน้าจอ จึงไล่ตรวจทุกชั้นแบบละเอียด
+- เขียนตัวไล่หา "ตัวแปรที่ใช้แต่ไม่ได้ประกาศ" (ต้นเหตุของ ReferenceError
+ที่ขึ้นเฉพาะบางหน้าจอ) สแกน 108 ไฟล์ ไม่พบของจริงสักจุด
+ที่ค้างเป็นคำในข้อความ JSX กับชื่อแอตทริบิวต์ทั้งหมด
+- เขียนตัวเทียบคอลัมน์ในฐานข้อมูลกับตัวแปลงใน lib/api.js ทั้ง 6 ตาราง
+ไม่มีคอลัมน์ที่ห้ามว่างแล้วไม่ได้ส่ง และไม่มีคอลัมน์ที่ส่งไปแต่ไม่มีในตาราง
+- สิ่งที่พบและแก้:
+1. ชื่อกลุ่มในเมนูเป็น "การรับฟังลูกค้า (หมวด 3)" แต่ในตารางสิทธิ
+เป็น "การรับฟังลูกค้า" คนตั้งสิทธิจะหากลุ่มไม่เจอ เพราะสองหน้า
+อ่านคนละไฟล์กันจึงไม่มีอะไรฟ้อง — แก้ให้ตรงกันแล้ว
+2. lib/xlsx.js ยัง import utf8 ค้างไว้ตั้งแต่ย้าย zip ออกไป
+ทั้งที่ไม่มีใครใช้แล้ว — ลบทิ้ง
+3. ตัวแปลงเสียงลูกค้าส่งวันที่เป็นสตริงว่างได้ ซึ่ง Postgres จะฟ้อง
+invalid input syntax for type date ที่อ่านแล้วไม่รู้ว่าต้องแก้ตรงไหน
+— เปลี่ยนเป็นส่ง null แล้วให้ not null เป็นคนฟ้องแทน
+4. หน้าภาพรวมเรียก assessAll ซ้ำอีกรอบ ทั้งที่ executiveSummary
+ประเมินให้แล้วและคืน items กับ level มาด้วย เท่ากับไล่ตัวตรวจ
+ทั้ง 37 ตัวสองเที่ยวทุกครั้งที่วาดใหม่โดยได้ผลเหมือนเดิม — ตัดออก
+5. allowedOf ของตัวตรวจอ่าน constraint ที่ขึ้นบรรทัดใหม่หลังคำว่า in
+ไม่ได้ แล้วเลยไปจับ constraint ตัวถัดไปแทน รายงานผลผิดโดยไม่มี
+อะไรฟ้อง — แก้ให้ยอมรับช่องว่างและการขึ้นบรรทัดใหม่
+- เพิ่มการตรวจถาวรสองอย่าง:
+หมวด 5  ชื่อกลุ่มต้องตรงกันทั้งในเมนูและในตารางสิทธิ
+หมวด 10 เทียบรายการค่าของหมวดการรับฟังลูกค้ากับ check constraint
+ครบทั้ง 15 ชุด (ชนิดช่องทาง ความถี่ กลุ่มลูกค้า วงจรชีวิต
+มิติ ประเภทเสียง ความสำคัญ สถานะ ชนิดการประเมิน ฯลฯ)
+เพิ่มค่าในโค้ดแล้วลืมแก้ constraint = กดบันทึกแล้ว error
+ของ Postgres ซึ่งเป็นอาการที่หาต้นเหตุยากที่สุดแบบหนึ่ง
+ทดสอบย้อน 3 กรณี จับได้ทุกกรณี
+- ตรวจด้านความปลอดภัย ไม่พบช่องโหว่ที่เพิ่มเข้ามาในหมวดนี้:
+ไม่มี dangerouslySetInnerHTML ที่รับข้อมูลผู้ใช้ (ที่มีอยู่ที่เดียว
+ใน app/layout.js เป็นสตริงคงที่สำหรับตั้งธีมก่อนวาดครั้งแรก)
+ทุกคำสั่งลบต่อ id เข้า URL ผ่าน encodeURIComponent ครบทั้ง 6 ตาราง
+ที่จัดเก็บดิจิทัล (store_url) แสดงเป็นข้อความอย่างเดียว ไม่ได้ทำเป็น
+ลิงก์ จึงไม่เปิดช่องให้ ja</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3430,12 +3479,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3447,29 +3496,29 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3530,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3547,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3564,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3532,12 +3581,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3598,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3566,29 +3615,29 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3600,12 +3649,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3666,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3683,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3651,12 +3700,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3668,12 +3717,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3734,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3751,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3768,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3736,12 +3785,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3753,12 +3802,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3770,12 +3819,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3787,12 +3836,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3853,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3870,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3887,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3904,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3921,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3889,12 +3938,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3955,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3923,29 +3972,29 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -3957,12 +4006,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -3974,12 +4023,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -3991,12 +4040,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4008,12 +4057,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4025,29 +4074,29 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4108,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4125,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4142,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4110,12 +4159,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4176,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4193,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4161,12 +4210,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4178,12 +4227,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4195,12 +4244,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4212,12 +4261,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4229,12 +4278,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4246,12 +4295,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4312,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4280,12 +4329,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4297,12 +4346,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4363,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4331,12 +4380,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4348,29 +4397,29 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4431,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4448,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4416,12 +4465,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4433,12 +4482,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4499,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4516,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4533,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4501,12 +4550,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4567,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4535,29 +4584,29 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4569,12 +4618,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4586,29 +4635,29 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4669,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4637,12 +4686,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4654,12 +4703,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4671,29 +4720,29 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4754,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4722,12 +4771,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4788,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4756,27 +4805,44 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr" s="2">
+      <c r="B82" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr" s="2">
+      <c r="C82" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -5301,7 +5367,7 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -5320,13 +5386,13 @@
         </is>
       </c>
       <c r="E21">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -5351,7 +5417,7 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -5376,7 +5442,7 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -5401,7 +5467,7 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -5426,7 +5492,7 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -5451,7 +5517,7 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -6789,7 +6855,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>2621</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="3">

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -102,7 +102,7 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
     </row>
@@ -210,7 +210,7 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
+          <t xml:space="preserve">38 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">20 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">21 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">83 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 81 ครั้ง</t>
+          <t xml:space="preserve">84 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 82 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3442,6 +3442,55 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85">
+        <v>85</v>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- เดิมสิทธิเป็นของทั้งระบบ ตั้งครั้งเดียวมีผลกับทุกคนเหมือนกันหมด
+ซึ่งใช้ไม่ได้จริงเมื่อมีหลายฝ่ายใช้ระบบเดียวกัน
+- เพิ่มสองตาราง (รวมเป็น 38 ตาราง):
+app_users   ทะเบียนผู้ใช้พร้อมบทบาท (แอดมิน / ผู้ใช้ทั่วไป)
+user_perms  สิทธิรายคนรายหน้าจอ
+ส่วน screen_perms ของเดิมกลายเป็น "ค่าเริ่มต้นของทุกคน"
+- ลำดับการตัดสิน: สิทธิเฉพาะตัว &gt; ค่าเริ่มต้นของทุกคน &gt; เปิดหมด
+จงใจไม่เอาสองชั้นมารวมกัน เพราะสิทธิที่ต้องเดาว่าชั้นไหนชนะ
+คนตั้งค่าอ่านไม่ออก และอธิบายให้คนใช้ฟังไม่ได้
+- ตั้งสิทธิให้คนหนึ่งแล้วเขียนครบทุกหน้าจอของคนนั้น ไม่ใช่เฉพาะที่ต่าง
+ไม่งั้นวันที่แก้ค่าเริ่มต้นทีหลัง สิทธิของคนที่ตั้งเฉพาะตัวไว้
+จะขยับตามไปด้วยโดยไม่มีใครตั้งใจ และ "ใช้ค่าเริ่มต้น" กลายเป็น
+สถานะที่ชัดเจนอีกอันหนึ่ง (ไม่มีแถวของตัวเองเลย) กดกลับได้ปุ่มเดียว
+- ทำไมต้องมี app_users ทั้งที่ Supabase มี auth.users อยู่แล้ว:
+auth.users อ่านจากฝั่งเว็บไม่ได้ ต้องใช้ service_role key
+ซึ่งข้ามทุกสิทธิ์ ฝังไว้ในเว็บเมื่อไรใครเปิดหน้าเว็บก็ลบข้อมูลได้ทั้งระบบ
+จึงทำทะเบียนคู่ขนานใน public ที่อ่านได้ตามปกติ
+รหัสผ่านยังอยู่ใน auth.users ที่เดียว ไม่ได้คัดลอกมา
+- ผู้ใช้เข้าทะเบียนได้สองทาง กันพลาด:
+1. trigger บน auth.users ตอนสร้างบัญชี
+2. ตัวโปรแกรมลงทะเบียนตัวเองตอนล็อกอิน (ensureAppUser)
+เพราะบางโปรเจกต์สร้าง trigger บน schema auth ไม่ได้ (สิทธิ์ถูกจำกัด)
+ถ้าพึ่งทางเดียว ผู้ใช้จะไม่โผล่ในทะเบียนแล้วแอดมินตั้งสิทธิให้ไม่ได้เลย
+do block ของ trigger ดัก exception ไว้ ไฟล์ทั้งไฟล์จึงไม่ล้มเพราะเรื่องนี้
+- ฐานข้อมูลบังคับกติกาเอง ไม่ใช่แค่ซ่อนปุ่มบนหน้าจอ:
+สามตารางที่คุมสิทธิใช้ policy คนละแบบกับตารางข้อมูลทั่วไป
+อ่านได้ทุกคนที่ล็อกอินแล้ว แต่เขียนได้เฉพาะแอดมิน
+(ลบ policy เปิดกว้างของเดิมออกด้วย ไม่งั้นยังเขียนได้ทุกคนอยู่)
+ยกเว้นข้อเดียว: ลงทะเบียนตัวเองได้ แต่เป็นบทบาท user เท่านั้น
+จึงยกตัวเองเป็นแอดมินด้วยวิธีนี้ไม่ได้
+- ฟังก์ชัน is_admin() เป็น security definer เพราะต้องอ่าน app_users
+ได้แม้ policy ของตารางนั้นจะยังไม่อนุญาต ไม่งั้นวนเป็นงูกินหาง
+(อ่าน app_users ต้องรู้ว่าเป็นแอดมิน ซึ่งต้องอ่าน app_users)
+- ข้อยกเว้นกันล็อกตัวเองออก: ยังไม่มีแอดมินเลยสักคน = ทุกคนเป็นแอดมิน
+เขียนไว้ทั้งฝั่งเว็บ (isAdminOf) แ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3479,12 +3528,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -3496,12 +3545,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3513,29 +3562,29 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3547,12 +3596,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3613,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3630,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3598,12 +3647,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3615,12 +3664,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3632,29 +3681,29 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3666,12 +3715,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3732,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3749,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3766,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3783,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3751,12 +3800,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3768,12 +3817,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3834,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3851,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3819,12 +3868,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3885,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3853,12 +3902,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3870,12 +3919,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3936,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3904,12 +3953,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3970,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3987,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -3955,12 +4004,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -3972,12 +4021,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -3989,29 +4038,29 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4072,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4089,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4057,12 +4106,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4123,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4091,29 +4140,29 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4125,12 +4174,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4191,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4208,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4225,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4242,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4259,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4227,12 +4276,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4293,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4310,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4278,12 +4327,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4295,12 +4344,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4361,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4329,12 +4378,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4395,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4412,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4429,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4446,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4414,29 +4463,29 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4497,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4514,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4531,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4548,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4565,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4582,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4550,12 +4599,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4567,12 +4616,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4633,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4601,29 +4650,29 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4684,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4652,29 +4701,29 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4686,12 +4735,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4703,12 +4752,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4769,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4737,29 +4786,29 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4771,12 +4820,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4837,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4805,12 +4854,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4822,27 +4871,44 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr" s="2">
+      <c r="B83" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr" s="2">
+      <c r="C83" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -5861,7 +5927,7 @@
         </is>
       </c>
       <c r="E40">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41">
@@ -6797,18 +6863,48 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">app_users</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, email, name, role, active, note, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">user_perms</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>9</v>
+      </c>
+      <c r="D38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, user_id, screen_id, can_view, can_edit, can_date, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">screen_perms</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr" s="2">
+      <c r="B39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สิทธิการใช้งานรายหน้าจอ (ดู / แก้ไข / เปลี่ยนวันที่)</t>
         </is>
       </c>
-      <c r="C37">
+      <c r="C39">
         <v>6</v>
       </c>
-      <c r="D37" t="inlineStr" s="2">
+      <c r="D39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">id, can_view, can_edit, can_date, created_at, row_order</t>
         </is>
@@ -6855,7 +6951,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>2623</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="3">
@@ -7036,7 +7132,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>928</v>
+        <v>982</v>
       </c>
     </row>
     <row r="15">
@@ -7111,7 +7207,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="20">
@@ -7246,7 +7342,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>1294</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="29">
@@ -7733,6 +7829,18 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สิทธิรายผู้ใช้บังคับได้จริง ไม่ใช่แค่ซ่อนปุ่ม</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">84 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 82 ครั้ง</t>
+          <t xml:space="preserve">85 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 83 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3491,6 +3491,41 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86">
+        <v>86</v>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- ผู้ใช้เจอ 42501 permission denied for sequence user_perms_row_order_seq
+ตอนกดบันทึกสิทธิรายคน
+- สาเหตุ: ทุกตารางมีคอลัมน์ row_order ที่ตั้งค่าเริ่มต้นเป็น nextval(...)
+ตอน insert Postgres ต้องเรียก nextval ซึ่งขอสิทธิ์บน sequence
+แยกจากสิทธิ์บนตาราง และ grant all privileges on table ...
+ไม่ครอบคลุมถึง sequence
+- ที่ผ่านมาไม่เจอเพราะโปรเจกต์ Supabase ตั้ง default privileges
+ของ sequence ไว้ให้ตอนสร้างโปรเจกต์ ตารางที่สร้างก่อนหน้าจึงได้สิทธิ์
+ติดมาเอง แต่พึ่งค่านั้นไม่ได้ เพราะขึ้นกับว่า role ไหนเป็นคนสร้าง
+- เพิ่ม grant usage, select on all sequences in schema public
+วางไว้หลังบล็อก row_order เสมอ (ก่อนหน้านั้น all sequences
+จะยังไม่เห็นตัวที่เพิ่งสร้าง) และเพิ่ม alter default privileges
+ให้ตารางที่เพิ่มทีหลังได้สิทธิ์เองโดยไม่ต้องมาไล่แก้
+- ตารางตรวจผลท้าย schema.sql เพิ่มการดู has_sequence_privilege
+ไม่งั้นทุกแถวขึ้น "ผ่าน" ทั้งที่ insert ไม่ได้จริง
+- แยกข้อความ error ของกรณี sequence ออกจากกรณีสิทธิ์ตาราง
+ข้อความเดิมบอกให้ไปดู GRANT ของตาราง ซึ่งครบอยู่แล้ว
+คนอ่านจึงไล่ผิดที่ทั้งที่ต้นเหตุอยู่คนละที่
+- เพิ่มการตรวจในหมวด 6: ต้องมี GRANT sequence · ต้องอยู่หลังบล็อก
+ที่สร้าง sequence · ตารางตรวจผลต้องรายงานเรื่องนี้ด้วย
+ทดสอบย้อน 3 กรณี จับได้ทุกกรณี</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3523,17 +3558,17 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3580,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3597,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3579,29 +3614,29 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3648,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3630,12 +3665,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3647,12 +3682,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3664,12 +3699,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3681,12 +3716,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3698,29 +3733,29 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3767,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3784,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3801,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3818,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3835,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3852,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3869,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3886,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3868,12 +3903,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3885,12 +3920,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3937,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3919,12 +3954,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3971,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -3953,12 +3988,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -3970,12 +4005,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -3987,12 +4022,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4039,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4056,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4073,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4055,29 +4090,29 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4124,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4141,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4123,12 +4158,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4175,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4157,29 +4192,29 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4191,12 +4226,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4243,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4260,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4277,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4294,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4276,12 +4311,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4328,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4345,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4362,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4379,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4396,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4413,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4430,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4447,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4464,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4481,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4498,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4480,29 +4515,29 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4549,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4531,12 +4566,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4548,12 +4583,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4600,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4617,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4634,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4651,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4633,12 +4668,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4650,12 +4685,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4667,29 +4702,29 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4736,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4718,29 +4753,29 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4787,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4804,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4821,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4803,29 +4838,29 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4872,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4889,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4906,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4888,27 +4923,44 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr" s="2">
+      <c r="B84" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr" s="2">
+      <c r="C84" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -7357,7 +7409,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="30">

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">21 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">22 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">85 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 83 ครั้ง</t>
+          <t xml:space="preserve">86 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 84 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3526,6 +3526,54 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87">
+        <v>87</v>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- เดิมบิล POS มีแต่ช่อง "ชื่อลูกค้า" ที่พิมพ์เอง ซึ่งพิมพ์ผิดได้ ซ้ำได้
+และเทียบกับทะเบียนลูกค้าไม่ได้เลย รายงานยอดขายรายลูกค้าจึงรวมชื่อ
+ที่สะกดต่างกันไม่ติด และตามกลับไปหาทะเบียนไม่ได้ว่าเป็นใคร
+- เพิ่มช่อง "รหัสลูกค้า" แบบพิมพ์ค้นได้ (รหัส ชื่อ จังหวัด เบอร์โทร
+เลขผู้เสียภาษี) ใช้ SearchSelect ตัวเดียวกับหน้าขายสินค้าและบริการ
+คนที่ใช้หน้านั้นเป็นแล้วใช้หน้านี้ได้ทันทีโดยไม่ต้องเรียนใหม่
+- เลือกรหัสแล้วชื่อวิ่งตามรหัสเสมอ และช่องชื่อถูกล็อก
+ไม่งั้นจะได้บิลที่รหัสกับชื่อเป็นคนละคน แล้วตอนทำรายงาน
+จะแยกไม่ออกว่าควรเชื่อช่องไหน
+- ยังขายให้คนที่ไม่อยู่ในทะเบียนได้เหมือนเดิม ปล่อยรหัสเป็น
+"ลูกค้าทั่วไป" แล้วพิมพ์ชื่อเอง — ร้านหน้าร้านส่วนใหญ่ขายแบบนี้
+ถ้าบังคับให้เลือกรหัสทุกบิลจะขายไม่ได้เลย
+- บิลเก็บทั้ง customer_id และ cust_code (snapshot) เหตุผลเดียวกับ
+ใบกำกับภาษี เอกสารต้องคงข้อความเดิม ณ วันที่ขาย ต่อให้ทะเบียน
+ถูกแก้รหัสหรือถูกลบทีหลัง บิลเก่าต้องยังอ่านได้เหมือนเดิม
+(customer_id เป็น on delete set null ด้วยเหตุผลนี้)
+- ลูกค้าเริ่มต้นของหน้า POS: เพิ่มปุ่มในฟอร์มลูกค้า ติ๊กไว้ที่รายไหน
+หน้า POS จะเลือกรายนั้นให้เองทุกบิล รวมถึงบิลถัดไปหลังปิดการขาย
+เพราะร้านที่ตั้งค่านี้ไว้คือร้านที่ขายให้ลูกค้ารายนั้นเป็นหลัก
+- ตั้งได้ทีละรายเดียว ตัวโปรแกรมปลดของรายอื่นก่อนบันทึกเสมอ
+(วิธีเดียวกับฟอร์มพิมพ์ที่เป็นค่าเริ่มต้น) จงใจไม่ทำ unique index
+ที่ฐานข้อมูล เพราะวันที่กู้คืนไฟล์สำรองที่มีสองรายติ๊กไว้
+จะกู้ไม่ขึ้นทั้งไฟล์ พร้อม error ที่ไม่มีใครเดาได้ว่าเกี่ยวกับหน้า POS
+ฝั่งอ่าน (posCustomerOf) จึงเลือกรายที่รหัสน้อยสุดเสมอ ผลไม่แกว่ง
+- effect ที่เติมค่าเริ่มต้นต้องจำว่าเติมค่าไหนไปแล้ว ไม่งั้นพอผู้ใช้
+เปลี่ยนกลับเป็นลูกค้าทั่วไปเอง มันจะเติมรายเดิมกลับทันที
+จนเลือกเป็นลูกค้าทั่วไปไม่ได้เลย
+- ใบเสร็จ รายงานบิลขาย และชุดข้อมูลรายงานที่สร้างเอง แสดงรหัสลูกค้าด้วย
+รหัสเป็นมิติของตัวเองในรายงาน จึงรวมยอดรายลูกค้าได้ตรง ๆ
+- แก้บั๊กเก่าที่เจอระหว่างทาง: ฟอร์มลูกค้ามีช่อง "พนักงานขายประจำ"
+ให้เลือกมาตลอด แต่ตอนกดบันทึกไม่ได้ส่งค่านั้นไป ค่าที่เลือกจึงหาย
+ทุกครั้งโดยไม่มีข้อความเตือนอะไรเลย
+- เพิ่มตัวตรวจหมวด 22 ไล่ทั้งเส้น: หน้าจอเลือกรหัสได้และชื่อถูกล็อก ·
+รหัสลงถึงตาราง sal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3563,29 +3611,29 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3645,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3662,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3631,29 +3679,29 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3713,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3730,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3747,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3716,12 +3764,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3781,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3750,29 +3798,29 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3784,12 +3832,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3849,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3818,12 +3866,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3835,12 +3883,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3900,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3917,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3886,12 +3934,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3903,12 +3951,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3920,12 +3968,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3985,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -3954,12 +4002,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -3971,12 +4019,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -3988,12 +4036,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4053,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4070,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4087,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4104,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4073,12 +4121,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4138,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4107,29 +4155,29 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4189,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4206,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4223,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4192,12 +4240,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4209,29 +4257,29 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4291,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4308,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4277,12 +4325,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4342,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4311,12 +4359,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4376,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4393,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4410,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4427,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4444,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4461,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4430,12 +4478,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4447,12 +4495,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4464,12 +4512,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4529,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4546,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4563,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4532,29 +4580,29 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4566,12 +4614,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4583,12 +4631,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4648,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4617,12 +4665,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4682,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4651,12 +4699,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4668,12 +4716,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4685,12 +4733,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4702,12 +4750,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4719,29 +4767,29 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4801,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4770,29 +4818,29 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4804,12 +4852,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4821,12 +4869,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4886,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4855,29 +4903,29 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4937,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4906,12 +4954,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4971,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -4940,27 +4988,44 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr" s="2">
+      <c r="B85" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr" s="2">
+      <c r="C85" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -5329,7 +5394,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>782</v>
+        <v>863</v>
       </c>
     </row>
     <row r="15">
@@ -5854,7 +5919,7 @@
         </is>
       </c>
       <c r="E35">
-        <v>548</v>
+        <v>596</v>
       </c>
     </row>
     <row r="36">
@@ -6179,7 +6244,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>2578</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="49">
@@ -7003,7 +7068,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>2777</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="3">
@@ -7018,7 +7083,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4">
@@ -7184,7 +7249,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>982</v>
+        <v>996</v>
       </c>
     </row>
     <row r="15">
@@ -7259,7 +7324,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="20">
@@ -7379,7 +7444,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28">
@@ -7394,7 +7459,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>1388</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="29">
@@ -7893,6 +7958,18 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลูกค้าของบิลขายหน้าร้านต่อครบทั้งสาย</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -234,7 +234,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">53 ไฟล์</t>
+          <t xml:space="preserve">54 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">22 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">23 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">86 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 84 ครั้ง</t>
+          <t xml:space="preserve">87 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 85 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3574,6 +3574,54 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88">
+        <v>88</v>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- เดิมหน้ารายละเอียดสินค้าบอกยอดรายคลัง ส่วนช่องเก็บถูกยัดรวมไว้
+ในเซลล์เดียวเป็นข้อความ "A-01 (5), A-02 (3)" ซึ่งอ่านยากเมื่อของ
+กระจายหลายช่อง และเอาไปใช้เดินหยิบของจริงไม่ได้
+ส่วนฟอร์มแก้ไขสินค้าไม่บอกเรื่องที่เก็บเลย
+- เปลี่ยนเป็นหนึ่งบรรทัดต่อหนึ่งช่องเก็บ บอกรหัสช่อง โซน หมายเลขช่อง
+และจำนวน ชื่อคลังเขียนครั้งเดียวต่อคลังแล้วคร่อมแถว (rowSpan)
+จะได้เห็นว่าของกองไหนอยู่คลังเดียวกันโดยไม่ต้องอ่านชื่อซ้ำทุกบรรทัด
+- เพิ่มตารางชุดเดียวกันนี้ในฟอร์มแก้ไขสินค้าด้วย
+เพราะคนที่เข้ามาแก้ข้อมูลมักต้องรู้ว่าของอยู่ที่ไหนก่อนตัดสินใจ
+(จะตั้งช่องเก็บประจำที่ไหน หรือจะลบสินค้าได้หรือยัง)
+ไม่ควรต้องปิดฟอร์มไปเปิดหน้ารายละเอียดก่อน
+แสดงอย่างเดียว แก้ไม่ได้ — การย้ายของยังทำที่หน้าผังที่เก็บสินค้าที่เดียว
+- ตรรกะการนับอยู่ที่ stockByBin ใน lib/db.js ที่เดียว
+และทั้งสองหน้าใช้ตาราง components/views/StockBins.js ตัวเดียวกัน
+ถ้าต่างฝ่ายต่างคิดเอง วันที่แก้กติกาการนับจะมีที่หนึ่งที่ลืมแก้
+แล้วสองหน้าจะบอกยอดของสินค้าตัวเดียวกันไม่ตรงกัน
+ซึ่งคนใช้จับได้แน่ และไม่มีทางรู้ว่าควรเชื่อหน้าไหน
+- แถว "ไม่ได้ระบุที่เก็บ": ยอดของคลังมาจากรายการเคลื่อนไหว (txns)
+ส่วนยอดรายช่องมาจากตารางของในช่องเก็บ (product_locations)
+สองฝั่งนี้ไม่เท่ากันได้ กับข้อมูลที่บันทึกก่อนระบบบังคับให้ระบุช่อง
+และกับไฟล์สำรองรุ่นเก่าที่กู้คืนเข้ามา
+จึงแสดงส่วนต่างเป็นบรรทัดของตัวเอง ไม่ซ่อน
+ไม่งั้นผลรวมของช่องจะไม่เท่ากับยอดของคลัง แล้วคนอ่านจะคิดว่า
+ตัวเลขใดตัวเลขหนึ่งผิด ทั้งที่ทั้งคู่ถูก แค่ของบางส่วนไม่รู้ว่าอยู่ช่องไหน
+- ส่วนต่างติดลบก็ไม่กลบให้เป็นศูนย์ (ของในช่องมากกว่ายอดของคลัง)
+เพราะเป็นสัญญาณว่าข้อมูลสองฝั่งไม่ตรงกัน ซึ่งเป็นเรื่องที่ต้องรู้
+- ช่องเก็บเรียงตามผังคลัง (โซนแล้วคอลัมน์) ไม่ใช่ตามลำดับที่ฐานข้อมูล
+คืนมา คนที่ถือรายการนี้ไปเดินหยิบของจะได้เดินไล่ตามผังได้เลย
+- เพิ่มตัวตรวจหมวด 23: มี stockByBin ที่ lib/db.js · store แจกให้หน้าจอ ·
+สองหน้าจอสินค้าใช้ตารางตัวกลางและเรียก stockByBin จริง ·
+ไม่มีหน้าไหนกลับไปไล่นับของในช่องเองอีก · ตารางต้องแสดงส่วนที่ยัง
+ไม่ระบุที่เก็บ ทดสอบย้อน 7 กรณี จับได้ทุกกรณี
+- ทดสอบ 16 ข้อของ stockByBin ครอบคลุมกรณีขอบ: ไม่มีคลัง ·
+ของกระจายหลายช่อง · ไม่เคยระบุช่องเลย · </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3611,12 +3659,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -3628,29 +3676,29 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3710,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -3679,12 +3727,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3696,29 +3744,29 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3778,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3747,12 +3795,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3812,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3829,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3846,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3815,29 +3863,29 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3897,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3866,12 +3914,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3883,12 +3931,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3948,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3965,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3982,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -3951,12 +3999,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -3968,12 +4016,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -3985,12 +4033,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4002,12 +4050,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4067,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4084,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4101,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4118,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4087,12 +4135,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4104,12 +4152,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4169,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4186,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4203,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4172,29 +4220,29 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4206,12 +4254,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4223,12 +4271,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4240,12 +4288,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4305,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4274,29 +4322,29 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4308,12 +4356,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4325,12 +4373,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4342,12 +4390,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4359,12 +4407,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4424,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4393,12 +4441,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4410,12 +4458,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4427,12 +4475,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4444,12 +4492,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4461,12 +4509,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4526,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4543,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4560,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4529,12 +4577,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4546,12 +4594,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4611,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4628,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4597,29 +4645,29 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4631,12 +4679,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4696,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4713,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4682,12 +4730,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4699,12 +4747,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4764,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4733,12 +4781,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4750,12 +4798,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4767,12 +4815,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4784,29 +4832,29 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4866,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4835,29 +4883,29 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4869,12 +4917,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4886,12 +4934,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4903,12 +4951,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4920,29 +4968,29 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -4954,12 +5002,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -4971,12 +5019,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -4988,12 +5036,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5005,27 +5053,44 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr" s="2">
+      <c r="B86" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr" s="2">
+      <c r="C86" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -7083,7 +7148,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4">
@@ -7249,7 +7314,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>996</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="15">
@@ -7324,7 +7389,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="20">
@@ -7459,7 +7524,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>1395</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="29">
@@ -7970,6 +8035,18 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยอดคงเหลือรายช่องเก็บคิดที่เดียว ทุกหน้าตอบตรงกัน</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -198,7 +198,7 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">49 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
+          <t xml:space="preserve">50 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
         </is>
       </c>
     </row>
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36 ไฟล์</t>
+          <t xml:space="preserve">37 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -234,7 +234,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">54 ไฟล์</t>
+          <t xml:space="preserve">55 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">23 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">24 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">87 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 85 ครั้ง</t>
+          <t xml:space="preserve">88 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 86 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3622,6 +3622,55 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89">
+        <v>89</v>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- เพิ่มหน้าจอใหม่ในกลุ่ม "ภาพรวม" ต่อจากแดชบอร์ด
+ตอบคำถามที่หน้าอื่นตอบไม่ได้ในหน้าเดียว: คลังไหนมีของเท่าไร
+มูลค่าเท่าไร งวดนี้เข้าออกไปเท่าไร และของไปกองอยู่ที่ไหน
+- ทำไมไม่ไปใส่เป็นการ์ดบนแดชบอร์ดที่มีอยู่แล้ว:
+แดชบอร์ดเป็นภาพรวมทั้งระบบ ตัวเลขรวมก้อนเดียว
+ส่วนหน้านี้คือการ "เทียบคลังต่อคลัง" ซึ่งต้องเป็นตารางที่มี
+ยอดยกมาและยอดปลายงวดครบทุกแถว ใส่เป็นการ์ดใบเดียวไม่ได้
+และคนที่ต้องใช้คือคนทำรายงานปิดงวด ไม่ใช่คนเปิดดูผ่าน ๆ
+- แต่ละแถวมี ยกมา · รับเข้า · จ่ายออก · คงเหลือ · มูลค่า · จำนวนรายการ
+พร้อมแถวรวมทุกคลังท้ายตาราง และการ์ดสรุปสี่ใบด้านบน
+- ตารางบวกลงเสมอ: ยกมา + รับเข้า - จ่ายออก = คงเหลือ
+ยอดยกมาคิดย้อนจาก "คงเหลือปลายงวด ลบ การเคลื่อนไหวในงวด"
+ไม่ได้ไล่นับใหม่ถึงวันก่อนวันเริ่ม เพราะถ้าคิดแยกอีกชุด
+ตัวเลขสองฝั่งจะมาจากคนละที่ วันที่กติกาการนับเปลี่ยน (เช่น
+เพิ่มชนิดรายการใหม่) จะมีที่หนึ่งที่ลืมแก้ แล้วตารางจะบวกไม่ลง
+โดยไม่มีใครรู้ว่าผิดตรงไหน · ตารางการเงินที่บวกไม่ลง
+คือตารางที่ใช้ไม่ได้เลย คนอ่านจะเลิกเชื่อทั้งหน้า
+วิธีนี้ยังไม่ต้องคิด "วันก่อนวันเริ่ม" เองด้วย ซึ่งพลาดง่ายเรื่องเขตเวลา
+- ปรับปรุงแยกขึ้น/ลงเป็นคนละช่อง ไม่รวมแล้วบวกกัน
+เพราะปรับขึ้น 10 กับปรับลง 10 จะหักล้างกันเป็นศูนย์
+แล้วรายงานจะบอกว่า "ไม่มีการปรับปรุงเลย" ทั้งที่มีสองรายการ
+ที่ต้องอธิบายให้ผู้ตรวจฟัง
+- การโอนนับสองฝั่ง: ออกที่คลังต้นทาง เข้าที่คลังปลายทาง
+ของยังอยู่ในระบบเท่าเดิม แต่ในมุมของ "คลังหนึ่ง" คือของที่ขยับจริง
+กราฟจึงเขียนป้ายกำกับไว้ชัดว่ารวมโอนและปรับปรุงด้วย
+- คลังที่ไม่มีความเคลื่อนไหวเลยยังอยู่ในตาราง ไม่ถูกกรองออก
+เพราะ "คลังนี้ทั้งเดือนไม่มีอะไรเข้าออกเลย" เป็นข้อมูลที่ต้องเห็น
+- กดรายละเอียดที่คลังไหน จะเห็นสินค้าในคลังนั้นรายตัว (ยกมา/เข้า/ออก/
+คงเหลือ/มูลค่า) และรายการเคลื่อนไหว 50 รายการล่าสุด
+เครื่องหมายเข้า/ออกในรายการคิดจากมุมของคลังที่เลือกเสมอ
+ใบโอนใบเดียวกันจึงขึ้นเป็น "ออก" ที่ต้นทาง และ "เข้า" ที่ปลายทาง
+- ยอดคงเหลือคิด ณ วันสุดท้ายของช่วงที่เลือก ไม่ใช่ ณ วันนี้
+ไม่งั้นดูย้อนหลังแล้วจะได้ยอดของวันนี้ปนมากับการเคลื่อนไหวของเดือนก่อน
+- ตรรกะทั้งหมดอยู่ใน lib/whSummary.js ไม่มี JSX เลย ทดสอบใน Node ได้ตรง ๆ
+ยอดคงเหลือมาจาก stockMap ตัวเดียวกับที่ทั้ง</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3659,12 +3708,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3725,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -3693,29 +3742,29 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -3727,12 +3776,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -3744,12 +3793,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3761,29 +3810,29 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3844,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3861,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3829,12 +3878,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3895,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3912,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3880,29 +3929,29 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3963,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3931,12 +3980,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -3948,12 +3997,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -3965,12 +4014,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -3982,12 +4031,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -3999,12 +4048,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4065,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4033,12 +4082,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4099,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4067,12 +4116,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4084,12 +4133,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4101,12 +4150,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4118,12 +4167,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4184,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4152,12 +4201,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4218,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4235,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4252,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4220,12 +4269,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4237,29 +4286,29 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4320,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4337,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4354,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4322,12 +4371,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4339,29 +4388,29 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4422,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4439,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4407,12 +4456,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4473,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4490,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4507,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4524,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4541,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4558,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4526,12 +4575,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4543,12 +4592,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4560,12 +4609,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4577,12 +4626,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4643,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4660,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4677,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4645,12 +4694,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4662,29 +4711,29 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4696,12 +4745,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4762,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4779,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4747,12 +4796,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4764,12 +4813,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4781,12 +4830,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4798,12 +4847,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4815,12 +4864,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4832,12 +4881,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4849,29 +4898,29 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4883,12 +4932,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4900,29 +4949,29 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4983,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -4951,12 +5000,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -4968,12 +5017,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -4985,29 +5034,29 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5019,12 +5068,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5085,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5102,12 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5070,27 +5119,44 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr" s="2">
+      <c r="B87" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr" s="2">
+      <c r="C87" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -5170,21 +5236,21 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">วิธีการใช้งาน</t>
+          <t xml:space="preserve">สรุปยอดคงเหลือรายคลัง</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แต่ละหน้าจอทำงานยังไง เชื่อมกันตรงไหน</t>
+          <t xml:space="preserve">ยอดยกมา เข้า ออก คงเหลือ ของแต่ละคลัง</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Guide.js</t>
+          <t xml:space="preserve">components/views/WarehouseSummary.js</t>
         </is>
       </c>
       <c r="E3">
-        <v>262</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4">
@@ -5195,46 +5261,46 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Quick View (มือถือ)</t>
+          <t xml:space="preserve">วิธีการใช้งาน</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยอดขายเทียบเป้า ดูเร็วบนมือถือ</t>
+          <t xml:space="preserve">แต่ละหน้าจอทำงานยังไง เชื่อมกันตรงไหน</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/QuickView.js</t>
+          <t xml:space="preserve">components/views/Guide.js</t>
         </is>
       </c>
       <c r="E4">
-        <v>416</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำรายการ</t>
+          <t xml:space="preserve">ภาพรวม</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับสินค้า</t>
+          <t xml:space="preserve">Quick View (มือถือ)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกการรับสินค้าเข้าคลัง</t>
+          <t xml:space="preserve">ยอดขายเทียบเป้า ดูเร็วบนมือถือ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/TxnScreen.js</t>
+          <t xml:space="preserve">components/views/QuickView.js</t>
         </is>
       </c>
       <c r="E5">
-        <v>546</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6">
@@ -5245,12 +5311,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เบิกสินค้า</t>
+          <t xml:space="preserve">รับสินค้า</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกการเบิก-จ่ายสินค้า</t>
+          <t xml:space="preserve">บันทึกการรับสินค้าเข้าคลัง</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -5270,12 +5336,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โอนสินค้า</t>
+          <t xml:space="preserve">เบิกสินค้า</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โอนย้ายระหว่างคลัง</t>
+          <t xml:space="preserve">บันทึกการเบิก-จ่ายสินค้า</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -5295,21 +5361,21 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับปรุงสินค้า</t>
+          <t xml:space="preserve">โอนสินค้า</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับยอดตามผลการตรวจนับ</t>
+          <t xml:space="preserve">โอนย้ายระหว่างคลัง</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/AdjustScreen.js</t>
+          <t xml:space="preserve">components/views/TxnScreen.js</t>
         </is>
       </c>
       <c r="E8">
-        <v>474</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9">
@@ -5320,21 +5386,21 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เตรียมใบตรวจนับ</t>
+          <t xml:space="preserve">ปรับปรุงสินค้า</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างใบและพิมพ์ออกไปนับ</t>
+          <t xml:space="preserve">ปรับยอดตามผลการตรวจนับ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/CountPrep.js</t>
+          <t xml:space="preserve">components/views/AdjustScreen.js</t>
         </is>
       </c>
       <c r="E9">
-        <v>486</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10">
@@ -5345,46 +5411,46 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">นับสินค้า (มือถือ)</t>
+          <t xml:space="preserve">เตรียมใบตรวจนับ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สแกนบาร์โค๊ดแล้วกรอกจำนวน</t>
+          <t xml:space="preserve">สร้างใบและพิมพ์ออกไปนับ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/CountScan.js</t>
+          <t xml:space="preserve">components/views/CountPrep.js</t>
         </is>
       </c>
       <c r="E10">
-        <v>614</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานซื้อ</t>
+          <t xml:space="preserve">ทำรายการ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ซื้อสินค้าและบริการ</t>
+          <t xml:space="preserve">นับสินค้า (มือถือ)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับของเข้าและบันทึกภาษีซื้อ</t>
+          <t xml:space="preserve">สแกนบาร์โค๊ดแล้วกรอกจำนวน</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PurchaseInvoice.js</t>
+          <t xml:space="preserve">components/views/CountScan.js</t>
         </is>
       </c>
       <c r="E11">
-        <v>578</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12">
@@ -5395,21 +5461,21 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งคืนสินค้าและบริการ</t>
+          <t xml:space="preserve">ซื้อสินค้าและบริการ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คืนของให้เจ้าหนี้ตามใบซื้อ</t>
+          <t xml:space="preserve">รับของเข้าและบันทึกภาษีซื้อ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PurchaseReturn.js</t>
+          <t xml:space="preserve">components/views/PurchaseInvoice.js</t>
         </is>
       </c>
       <c r="E12">
-        <v>479</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13">
@@ -5420,46 +5486,46 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียดเจ้าหนี้</t>
+          <t xml:space="preserve">ส่งคืนสินค้าและบริการ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนเจ้าหนี้และที่อยู่</t>
+          <t xml:space="preserve">คืนของให้เจ้าหนี้ตามใบซื้อ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Suppliers.js</t>
+          <t xml:space="preserve">components/views/PurchaseReturn.js</t>
         </is>
       </c>
       <c r="E13">
-        <v>527</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานขาย</t>
+          <t xml:space="preserve">งานซื้อ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ขายสินค้า (POS)</t>
+          <t xml:space="preserve">รายละเอียดเจ้าหนี้</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยิงบาร์โค๊ด ขาย และออกใบเสร็จ</t>
+          <t xml:space="preserve">ทะเบียนเจ้าหนี้และที่อยู่</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/POS.js</t>
+          <t xml:space="preserve">components/views/Suppliers.js</t>
         </is>
       </c>
       <c r="E14">
-        <v>863</v>
+        <v>527</v>
       </c>
     </row>
     <row r="15">
@@ -5470,21 +5536,21 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ขายสินค้าและบริการ</t>
+          <t xml:space="preserve">ขายสินค้า (POS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกใบกำกับภาษีเต็มรูปแบบ</t>
+          <t xml:space="preserve">ยิงบาร์โค๊ด ขาย และออกใบเสร็จ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/SalesInvoice.js</t>
+          <t xml:space="preserve">components/views/POS.js</t>
         </is>
       </c>
       <c r="E15">
-        <v>685</v>
+        <v>863</v>
       </c>
     </row>
     <row r="16">
@@ -5495,46 +5561,46 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดเป้าขาย</t>
+          <t xml:space="preserve">ขายสินค้าและบริการ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งเป้าและเทียบกับยอดจริง</t>
+          <t xml:space="preserve">ออกใบกำกับภาษีเต็มรูปแบบ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Targets.js</t>
+          <t xml:space="preserve">components/views/SalesInvoice.js</t>
         </is>
       </c>
       <c r="E16">
-        <v>464</v>
+        <v>685</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
+          <t xml:space="preserve">งานขาย</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โอกาสการขาย</t>
+          <t xml:space="preserve">กำหนดเป้าขาย</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กรวยการขายและดีลที่ไล่ปิดอยู่</t>
+          <t xml:space="preserve">ตั้งเป้าและเทียบกับยอดจริง</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Deals.js</t>
+          <t xml:space="preserve">components/views/Targets.js</t>
         </is>
       </c>
       <c r="E17">
-        <v>670</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18">
@@ -5545,21 +5611,21 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกกิจกรรม</t>
+          <t xml:space="preserve">โอกาสการขาย</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โทร เข้าพบ และนัดครั้งถัดไป</t>
+          <t xml:space="preserve">กรวยการขายและดีลที่ไล่ปิดอยู่</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Activities.js</t>
+          <t xml:space="preserve">components/views/Deals.js</t>
         </is>
       </c>
       <c r="E18">
-        <v>493</v>
+        <v>670</v>
       </c>
     </row>
     <row r="19">
@@ -5570,21 +5636,21 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลูกค้าเป้าหมาย</t>
+          <t xml:space="preserve">บันทึกกิจกรรม</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้สนใจที่ยังไม่เป็นลูกค้า</t>
+          <t xml:space="preserve">โทร เข้าพบ และนัดครั้งถัดไป</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Leads.js</t>
+          <t xml:space="preserve">components/views/Activities.js</t>
         </is>
       </c>
       <c r="E19">
-        <v>508</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20">
@@ -5595,46 +5661,46 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ภาพรวมลูกค้า</t>
+          <t xml:space="preserve">ลูกค้าเป้าหมาย</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทุกอย่างของลูกค้าหนึ่งรายในหน้าเดียว</t>
+          <t xml:space="preserve">ผู้สนใจที่ยังไม่เป็นลูกค้า</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Customer360.js</t>
+          <t xml:space="preserve">components/views/Leads.js</t>
         </is>
       </c>
       <c r="E20">
-        <v>288</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ภาพรวมการรับฟังลูกค้า</t>
+          <t xml:space="preserve">ภาพรวมลูกค้า</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ระดับตามเกณฑ์ เสียงลูกค้า และงานที่ค้าง</t>
+          <t xml:space="preserve">ทุกอย่างของลูกค้าหนึ่งรายในหน้าเดียว</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocDash.js</t>
+          <t xml:space="preserve">components/views/Customer360.js</t>
         </is>
       </c>
       <c r="E21">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22">
@@ -5645,21 +5711,21 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องทางการรับฟัง</t>
+          <t xml:space="preserve">ภาพรวมการรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนช่องทางและความครอบคลุมตามเกณฑ์</t>
+          <t xml:space="preserve">ระดับตามเกณฑ์ เสียงลูกค้า และงานที่ค้าง</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocChannels.js</t>
+          <t xml:space="preserve">components/views/VocDash.js</t>
         </is>
       </c>
       <c r="E22">
-        <v>482</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23">
@@ -5670,21 +5736,21 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เสียงของลูกค้า</t>
+          <t xml:space="preserve">ช่องทางการรับฟัง</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกทีละเรื่อง จำแนกครบทุกมิติ</t>
+          <t xml:space="preserve">ทะเบียนช่องทางและความครอบคลุมตามเกณฑ์</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocRecords.js</t>
+          <t xml:space="preserve">components/views/VocChannels.js</t>
         </is>
       </c>
       <c r="E23">
-        <v>515</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24">
@@ -5695,21 +5761,21 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ประเมินความพึงพอใจ</t>
+          <t xml:space="preserve">เสียงของลูกค้า</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รอบประเมิน ความผูกพัน และผลรายกลุ่ม</t>
+          <t xml:space="preserve">บันทึกทีละเรื่อง จำแนกครบทุกมิติ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocSurveys.js</t>
+          <t xml:space="preserve">components/views/VocRecords.js</t>
         </is>
       </c>
       <c r="E24">
-        <v>629</v>
+        <v>515</v>
       </c>
     </row>
     <row r="25">
@@ -5720,21 +5786,21 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ประเมินระดับตามเกณฑ์</t>
+          <t xml:space="preserve">ประเมินความพึงพอใจ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">จุดตรวจ 5 ระดับ พร้อมหลักฐาน</t>
+          <t xml:space="preserve">รอบประเมิน ความผูกพัน และผลรายกลุ่ม</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocLevels.js</t>
+          <t xml:space="preserve">components/views/VocSurveys.js</t>
         </is>
       </c>
       <c r="E25">
-        <v>319</v>
+        <v>629</v>
       </c>
     </row>
     <row r="26">
@@ -5745,21 +5811,21 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แผนปรับปรุงและนวัตกรรม</t>
+          <t xml:space="preserve">ประเมินระดับตามเกณฑ์</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานผู้บริหาร ความรู้ และการนำไปใช้</t>
+          <t xml:space="preserve">จุดตรวจ 5 ระดับ พร้อมหลักฐาน</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocActions.js</t>
+          <t xml:space="preserve">components/views/VocLevels.js</t>
         </is>
       </c>
       <c r="E26">
-        <v>491</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27">
@@ -5770,46 +5836,46 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานและนำเสนอ</t>
+          <t xml:space="preserve">แผนปรับปรุงและนวัตกรรม</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออก Excel และไฟล์ PowerPoint</t>
+          <t xml:space="preserve">รายงานผู้บริหาร ความรู้ และการนำไปใช้</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocReports.js</t>
+          <t xml:space="preserve">components/views/VocActions.js</t>
         </is>
       </c>
       <c r="E27">
-        <v>261</v>
+        <v>491</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
+          <t xml:space="preserve">รายงานและนำเสนอ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
+          <t xml:space="preserve">ส่งออก Excel และไฟล์ PowerPoint</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipScan.js</t>
+          <t xml:space="preserve">components/views/VocReports.js</t>
         </is>
       </c>
       <c r="E28">
-        <v>454</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29">
@@ -5820,21 +5886,21 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดส่งสินค้า</t>
+          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
+          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Shipping.js</t>
+          <t xml:space="preserve">components/views/ShipScan.js</t>
         </is>
       </c>
       <c r="E29">
-        <v>623</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30">
@@ -5845,21 +5911,21 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานะการจัดส่ง</t>
+          <t xml:space="preserve">การจัดส่งสินค้า</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
+          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipStatus.js</t>
+          <t xml:space="preserve">components/views/Shipping.js</t>
         </is>
       </c>
       <c r="E30">
-        <v>593</v>
+        <v>623</v>
       </c>
     </row>
     <row r="31">
@@ -5870,46 +5936,46 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
+          <t xml:space="preserve">สถานะการจัดส่ง</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
+          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/BillImport.js</t>
+          <t xml:space="preserve">components/views/ShipStatus.js</t>
         </is>
       </c>
       <c r="E31">
-        <v>892</v>
+        <v>593</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลสินค้า</t>
+          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
+          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Products.js</t>
+          <t xml:space="preserve">components/views/BillImport.js</t>
         </is>
       </c>
       <c r="E32">
-        <v>187</v>
+        <v>892</v>
       </c>
     </row>
     <row r="33">
@@ -5920,21 +5986,21 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สินค้าตามจังหวัด</t>
+          <t xml:space="preserve">ข้อมูลสินค้า</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
+          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Provinces.js</t>
+          <t xml:space="preserve">components/views/Products.js</t>
         </is>
       </c>
       <c r="E33">
-        <v>401</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34">
@@ -5945,21 +6011,21 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
+          <t xml:space="preserve">สินค้าตามจังหวัด</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
+          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Locations.js</t>
+          <t xml:space="preserve">components/views/Provinces.js</t>
         </is>
       </c>
       <c r="E34">
-        <v>697</v>
+        <v>401</v>
       </c>
     </row>
     <row r="35">
@@ -5970,46 +6036,46 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียดลูกค้า</t>
+          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
+          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Customers.js</t>
+          <t xml:space="preserve">components/views/Locations.js</t>
         </is>
       </c>
       <c r="E35">
-        <v>596</v>
+        <v>697</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
+          <t xml:space="preserve">รายละเอียดลูกค้า</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
+          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DocGroups.js</t>
+          <t xml:space="preserve">components/views/Customers.js</t>
         </is>
       </c>
       <c r="E36">
-        <v>357</v>
+        <v>596</v>
       </c>
     </row>
     <row r="37">
@@ -6020,21 +6086,21 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
+          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
+          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PrintForms.js</t>
+          <t xml:space="preserve">components/views/DocGroups.js</t>
         </is>
       </c>
       <c r="E37">
-        <v>525</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38">
@@ -6045,21 +6111,21 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
+          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
+          <t xml:space="preserve">components/views/PrintForms.js</t>
         </is>
       </c>
       <c r="E38">
-        <v>610</v>
+        <v>525</v>
       </c>
     </row>
     <row r="39">
@@ -6070,21 +6136,21 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลกิจการ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
+          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Company.js</t>
+          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
         </is>
       </c>
       <c r="E39">
-        <v>164</v>
+        <v>610</v>
       </c>
     </row>
     <row r="40">
@@ -6095,21 +6161,21 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองข้อมูล</t>
+          <t xml:space="preserve">ข้อมูลกิจการ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
+          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Backup.js</t>
+          <t xml:space="preserve">components/views/Company.js</t>
         </is>
       </c>
       <c r="E40">
-        <v>300</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41">
@@ -6120,21 +6186,21 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
+          <t xml:space="preserve">สำรองข้อมูล</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
+          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Users.js</t>
+          <t xml:space="preserve">components/views/Backup.js</t>
         </is>
       </c>
       <c r="E41">
-        <v>232</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
@@ -6145,21 +6211,21 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
+          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SQL Server / MySQL / Access</t>
+          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/SqlServer.js</t>
+          <t xml:space="preserve">components/views/Users.js</t>
         </is>
       </c>
       <c r="E42">
-        <v>748</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43">
@@ -6170,21 +6236,21 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
+          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
+          <t xml:space="preserve">SQL Server / MySQL / Access</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DataImport.js</t>
+          <t xml:space="preserve">components/views/SqlServer.js</t>
         </is>
       </c>
       <c r="E43">
-        <v>894</v>
+        <v>748</v>
       </c>
     </row>
     <row r="44">
@@ -6195,21 +6261,21 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดพนักงานขาย</t>
+          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
+          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Salespersons.js</t>
+          <t xml:space="preserve">components/views/DataImport.js</t>
         </is>
       </c>
       <c r="E44">
-        <v>308</v>
+        <v>894</v>
       </c>
     </row>
     <row r="45">
@@ -6220,21 +6286,21 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+          <t xml:space="preserve">กำหนดพนักงานขาย</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
+          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ProductTerms.js</t>
+          <t xml:space="preserve">components/views/Salespersons.js</t>
         </is>
       </c>
       <c r="E45">
-        <v>321</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46">
@@ -6245,21 +6311,21 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
+          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/CustomerKinds.js</t>
+          <t xml:space="preserve">components/views/ProductTerms.js</t>
         </is>
       </c>
       <c r="E46">
-        <v>372</v>
+        <v>321</v>
       </c>
     </row>
     <row r="47">
@@ -6270,46 +6336,46 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Password.js</t>
+          <t xml:space="preserve">components/views/CustomerKinds.js</t>
         </is>
       </c>
       <c r="E47">
-        <v>170</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Reports.js</t>
+          <t xml:space="preserve">components/views/Password.js</t>
         </is>
       </c>
       <c r="E48">
-        <v>2585</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49">
@@ -6320,21 +6386,21 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุป</t>
+          <t xml:space="preserve">รายงาน</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Graphs.js</t>
+          <t xml:space="preserve">components/views/Reports.js</t>
         </is>
       </c>
       <c r="E49">
-        <v>499</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="50">
@@ -6345,20 +6411,45 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">กราฟสรุป</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Graphs.js</t>
+        </is>
+      </c>
+      <c r="E50">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สร้างรายงาน</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr" s="2">
+      <c r="C51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">เลือกคอลัมน์และจัดรูปแบบเอง</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr" s="2">
+      <c r="D51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">components/views/ReportBuilder.js</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E51">
         <v>537</v>
       </c>
     </row>
@@ -7148,7 +7239,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4">
@@ -7239,7 +7330,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10">
@@ -7389,7 +7480,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="20">
@@ -7620,45 +7711,60 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/whSummary.js</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">สรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า–ออกในช่วงที่เลือก</t>
         </is>
       </c>
       <c r="C35">
-        <v>253</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsxRead.js</t>
+          <t xml:space="preserve">lib/xlsx.js</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
         </is>
       </c>
       <c r="C36">
-        <v>223</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/xlsxRead.js</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/zip.js</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr" s="2">
+      <c r="B38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ประกอบไฟล์ zip เอง — ไม่ใช้ไลบรารี</t>
         </is>
       </c>
-      <c r="C37">
+      <c r="C38">
         <v>124</v>
       </c>
     </row>
@@ -8047,6 +8153,18 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สรุปยอดคงเหลือรายคลังบวกลงเสมอ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -198,7 +198,7 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">50 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
+          <t xml:space="preserve">56 หน้า (ตามชีต หน้าจอทั้งหมด)</t>
         </is>
       </c>
     </row>
@@ -210,7 +210,7 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">38 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
+          <t xml:space="preserve">44 ตาราง (ตามชีต ตารางฐานข้อมูล)</t>
         </is>
       </c>
     </row>
@@ -222,7 +222,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37 ไฟล์</t>
+          <t xml:space="preserve">40 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -234,7 +234,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">55 ไฟล์</t>
+          <t xml:space="preserve">62 ไฟล์</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">24 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">25 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">88 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 86 ครั้ง</t>
+          <t xml:space="preserve">89 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 87 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3671,6 +3671,56 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90">
+        <v>90</v>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">งานผ่านไลน์ — ดึงคำสั่งซื้อจากแชทมาทำเป็นเอกสาร และใบเสนอราคา</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- โจทย์: ลูกค้าสั่งของทางไลน์ แล้วพนักงานพิมพ์ซ้ำเข้าระบบเอง
+ซึ่งพิมพ์ตก พิมพ์ผิด และตามไม่ได้ว่าใบไหนมาจากข้อความไหน
+- เพิ่มเมนูใหม่ "งานผ่านไลน์" 5 หน้าจอ และ "ใบเสนอราคา" ในกลุ่มงานขาย
+รวม 6 ตาราง (เป็น 44 ตาราง)
+โครงสามชั้น แยกกันชัดเจนโดยตั้งใจ
+- ชั้นที่ 1 ข้อความดิบ (line_messages) = "สิ่งที่ลูกค้าพิมพ์"
+แก้ไม่ได้ เป็นหลักฐาน เวลามีข้อโต้แย้งว่า "สั่ง 10 ไม่ใช่ 100"
+ต้องย้อนกลับไปดูของจริงได้ และตัวแปลงจะเก่งขึ้นเรื่อย ๆ
+ข้อความเดิมจึงต้องแปลงใหม่ได้เมื่อสอนคำเพิ่ม
+- ชั้นที่ 2 คำสั่งซื้อ (line_orders + items) = "สิ่งที่เราตีความ"
+แก้ได้ ตรวจได้ และบอกได้ว่าแต่ละบรรทัดจับคู่สินค้าด้วยวิธีไหน
+- ชั้นที่ 3 เอกสาร (ใบเสนอราคา / ใบขาย) = "สิ่งที่เรารับผิดชอบ"
+ถ้ายุบสามชั้นนี้เป็นชั้นเดียว จะแยกไม่ออกว่าตัวเลขที่ผิดมาจาก
+ลูกค้าพิมพ์ผิด ระบบอ่านผิด หรือคนแก้ผิด
+ข้อความเข้าระบบได้สามทาง
+- รับอัตโนมัติจากบัญชีทางการ ผ่าน webhook ของ LINE Messaging API
+- นำเข้าไฟล์แชท .txt ที่ส่งออกจากแอปไลน์ (อ่านได้ทั้งไฟล์ไทยและอังกฤษ)
+- วางข้อความที่คัดลอกมาเอง
+- ทางที่สองกับสามสำคัญพอกับทางแรก เพราะการรับอัตโนมัติต้องมีบัญชีทางการ
+ซึ่งหลายที่ยังไม่มี และบทสนทนาที่เกิดก่อนเชื่อมระบบก็ดึงย้อนไม่ได้
+สองทางนั้นใช้ได้ทันทีตั้งแต่วันแรกและดึงของเก่าย้อนหลังได้
+ตัวอ่านข้อความ (lib/lineParse.js)
+- อ่านจำนวนจาก "10 ใบ" · "x3" · "เอา 5" · เลขไทย ๑๒๓ · "1,250 กก."
+ไล่ตามลำดับความชัดเจน เลขลอย ๆ อยู่ท้ายสุดและติดธงว่าเดามา
+- ไม่เดาราคาจากเลขลอย ๆ เอาเฉพาะที่เขียนชัดว่าเป็นเงิน (@ / ราคา / บาท)
+เพราะเดาราคาผิดแล้วออกเอกสารไป เสียหายกว่าเดาจำนวนผิดมาก
+ไม่เจอก็ใช้ราคาจากทะเบียนสินค้าแทน ซึ่งถูกเสมอ
+- จับคู่สินค้าโดยหาทุกตำแหน่งที่ปรากฏในบรรทัด ไม่ทับซ้อนกัน ยาวก่อนสั้น
+จึงแยก "หมอน 2 ใบ ท้อปเปอร์ 1 ชิ้น" ได้โดยไม่ต้องมีเครื่องหมายคั่น
+ซึ่งเป็นวิธีพิมพ์ที่พบบ่อยที่สุดในไลน์ คนไม่ได้พิมพ์เป็นตารางให้
+และชื่อยาวชนะชื่อสั้นที่ซ้อนอยู่ข้างใน (หมอนยางพารา ไม่ใช่ หมอน)
+- บรรทัดที่อ่านไม่ออกไม่ถูกทิ้งเงียบ ๆ แต่ยกไปให้คนเลือกเอง
+ทิ้งไปแล้วของหายจากใบเสนอราคาโดยไม่มีใครรู้ว่าเคยมี
+- เลือกเองแล้วกด "จำคำ" บันทึกเป็นคำเรียกของลูกค้า (line_aliases)
+ระบบจึงแม่นขึ้นเรื่อย ๆ ตามคำที่ลูกค้ากลุ่มนี้ใช้จริง
+แทนที่จ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3708,12 +3758,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3775,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3792,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -3759,29 +3809,29 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3843,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3860,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3827,29 +3877,29 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3861,12 +3911,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3928,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3945,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3962,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3979,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -3946,29 +3996,29 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -3980,12 +4030,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -3997,12 +4047,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4014,12 +4064,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4081,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4048,12 +4098,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4065,12 +4115,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4132,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4149,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4166,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4183,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4200,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4217,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4234,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4201,12 +4251,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4218,12 +4268,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4285,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4302,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4319,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4336,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4303,29 +4353,29 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4387,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4404,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4421,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4388,12 +4438,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4405,29 +4455,29 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4439,12 +4489,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4456,12 +4506,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4523,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4540,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4507,12 +4557,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4524,12 +4574,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4591,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4608,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4575,12 +4625,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4642,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4659,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4676,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4643,12 +4693,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4710,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4677,12 +4727,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4744,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4761,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4728,29 +4778,29 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4812,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4779,12 +4829,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4796,12 +4846,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4813,12 +4863,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4830,12 +4880,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4847,12 +4897,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4914,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4881,12 +4931,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4898,12 +4948,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4915,29 +4965,29 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4999,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -4966,29 +5016,29 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5000,12 +5050,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5067,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5034,12 +5084,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5051,29 +5101,29 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5135,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5152,12 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5119,12 +5169,12 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5136,27 +5186,44 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr" s="2">
+      <c r="B88" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr" s="2">
+      <c r="C88" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -5575,7 +5642,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>685</v>
+        <v>726</v>
       </c>
     </row>
     <row r="17">
@@ -5586,271 +5653,271 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดเป้าขาย</t>
+          <t xml:space="preserve">ใบเสนอราคา</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งเป้าและเทียบกับยอดจริง</t>
+          <t xml:space="preserve">เสนอราคาก่อนขาย แปลงเป็นใบขายได้</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Targets.js</t>
+          <t xml:space="preserve">components/views/Quotes.js</t>
         </is>
       </c>
       <c r="E17">
-        <v>464</v>
+        <v>746</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
+          <t xml:space="preserve">งานขาย</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โอกาสการขาย</t>
+          <t xml:space="preserve">กำหนดเป้าขาย</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กรวยการขายและดีลที่ไล่ปิดอยู่</t>
+          <t xml:space="preserve">ตั้งเป้าและเทียบกับยอดจริง</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Deals.js</t>
+          <t xml:space="preserve">components/views/Targets.js</t>
         </is>
       </c>
       <c r="E18">
-        <v>670</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
+          <t xml:space="preserve">งานผ่านไลน์</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกกิจกรรม</t>
+          <t xml:space="preserve">กล่องข้อความจากไลน์</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โทร เข้าพบ และนัดครั้งถัดไป</t>
+          <t xml:space="preserve">ข้อความที่ลูกค้าทักเข้ามา</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Activities.js</t>
+          <t xml:space="preserve">components/views/LineInbox.js</t>
         </is>
       </c>
       <c r="E19">
-        <v>493</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
+          <t xml:space="preserve">งานผ่านไลน์</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลูกค้าเป้าหมาย</t>
+          <t xml:space="preserve">คำสั่งซื้อจากไลน์</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้สนใจที่ยังไม่เป็นลูกค้า</t>
+          <t xml:space="preserve">ตรวจรายการแล้วออกเอกสาร</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Leads.js</t>
+          <t xml:space="preserve">components/views/LineOrders.js</t>
         </is>
       </c>
       <c r="E20">
-        <v>508</v>
+        <v>797</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
+          <t xml:space="preserve">งานผ่านไลน์</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ภาพรวมลูกค้า</t>
+          <t xml:space="preserve">คำเรียกสินค้าของลูกค้า</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทุกอย่างของลูกค้าหนึ่งรายในหน้าเดียว</t>
+          <t xml:space="preserve">สอนระบบว่าคำไหนคือสินค้าตัวไหน</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Customer360.js</t>
+          <t xml:space="preserve">components/views/LineAliases.js</t>
         </is>
       </c>
       <c r="E21">
-        <v>288</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
+          <t xml:space="preserve">งานผ่านไลน์</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ภาพรวมการรับฟังลูกค้า</t>
+          <t xml:space="preserve">รายงานงานผ่านไลน์</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ระดับตามเกณฑ์ เสียงลูกค้า และงานที่ค้าง</t>
+          <t xml:space="preserve">ปริมาณงาน อัตราปิด และของที่ถูกถาม</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocDash.js</t>
+          <t xml:space="preserve">components/views/LineReports.js</t>
         </is>
       </c>
       <c r="E22">
-        <v>295</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
+          <t xml:space="preserve">งานผ่านไลน์</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องทางการรับฟัง</t>
+          <t xml:space="preserve">ตั้งค่าการเชื่อมต่อไลน์</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนช่องทางและความครอบคลุมตามเกณฑ์</t>
+          <t xml:space="preserve">เชื่อมบัญชีทางการเข้ากับระบบ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocChannels.js</t>
+          <t xml:space="preserve">components/views/LineSetup.js</t>
         </is>
       </c>
       <c r="E23">
-        <v>482</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เสียงของลูกค้า</t>
+          <t xml:space="preserve">โอกาสการขาย</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกทีละเรื่อง จำแนกครบทุกมิติ</t>
+          <t xml:space="preserve">กรวยการขายและดีลที่ไล่ปิดอยู่</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocRecords.js</t>
+          <t xml:space="preserve">components/views/Deals.js</t>
         </is>
       </c>
       <c r="E24">
-        <v>515</v>
+        <v>670</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ประเมินความพึงพอใจ</t>
+          <t xml:space="preserve">บันทึกกิจกรรม</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รอบประเมิน ความผูกพัน และผลรายกลุ่ม</t>
+          <t xml:space="preserve">โทร เข้าพบ และนัดครั้งถัดไป</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocSurveys.js</t>
+          <t xml:space="preserve">components/views/Activities.js</t>
         </is>
       </c>
       <c r="E25">
-        <v>629</v>
+        <v>493</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ประเมินระดับตามเกณฑ์</t>
+          <t xml:space="preserve">ลูกค้าเป้าหมาย</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">จุดตรวจ 5 ระดับ พร้อมหลักฐาน</t>
+          <t xml:space="preserve">ผู้สนใจที่ยังไม่เป็นลูกค้า</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocLevels.js</t>
+          <t xml:space="preserve">components/views/Leads.js</t>
         </is>
       </c>
       <c r="E26">
-        <v>319</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
+          <t xml:space="preserve">งานลูกค้าสัมพันธ์</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แผนปรับปรุงและนวัตกรรม</t>
+          <t xml:space="preserve">ภาพรวมลูกค้า</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานผู้บริหาร ความรู้ และการนำไปใช้</t>
+          <t xml:space="preserve">ทุกอย่างของลูกค้าหนึ่งรายในหน้าเดียว</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocActions.js</t>
+          <t xml:space="preserve">components/views/Customer360.js</t>
         </is>
       </c>
       <c r="E27">
-        <v>491</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28">
@@ -5861,371 +5928,371 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานและนำเสนอ</t>
+          <t xml:space="preserve">ภาพรวมการรับฟังลูกค้า</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออก Excel และไฟล์ PowerPoint</t>
+          <t xml:space="preserve">ระดับตามเกณฑ์ เสียงลูกค้า และงานที่ค้าง</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/VocReports.js</t>
+          <t xml:space="preserve">components/views/VocDash.js</t>
         </is>
       </c>
       <c r="E28">
-        <v>261</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
+          <t xml:space="preserve">ช่องทางการรับฟัง</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
+          <t xml:space="preserve">ทะเบียนช่องทางและความครอบคลุมตามเกณฑ์</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipScan.js</t>
+          <t xml:space="preserve">components/views/VocChannels.js</t>
         </is>
       </c>
       <c r="E29">
-        <v>454</v>
+        <v>482</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดส่งสินค้า</t>
+          <t xml:space="preserve">เสียงของลูกค้า</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
+          <t xml:space="preserve">บันทึกทีละเรื่อง จำแนกครบทุกมิติ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Shipping.js</t>
+          <t xml:space="preserve">components/views/VocRecords.js</t>
         </is>
       </c>
       <c r="E30">
-        <v>623</v>
+        <v>515</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานะการจัดส่ง</t>
+          <t xml:space="preserve">ประเมินความพึงพอใจ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
+          <t xml:space="preserve">รอบประเมิน ความผูกพัน และผลรายกลุ่ม</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ShipStatus.js</t>
+          <t xml:space="preserve">components/views/VocSurveys.js</t>
         </is>
       </c>
       <c r="E31">
-        <v>593</v>
+        <v>629</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานจัดส่ง</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
+          <t xml:space="preserve">ประเมินระดับตามเกณฑ์</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
+          <t xml:space="preserve">จุดตรวจ 5 ระดับ พร้อมหลักฐาน</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/BillImport.js</t>
+          <t xml:space="preserve">components/views/VocLevels.js</t>
         </is>
       </c>
       <c r="E32">
-        <v>892</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลสินค้า</t>
+          <t xml:space="preserve">แผนปรับปรุงและนวัตกรรม</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
+          <t xml:space="preserve">รายงานผู้บริหาร ความรู้ และการนำไปใช้</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Products.js</t>
+          <t xml:space="preserve">components/views/VocActions.js</t>
         </is>
       </c>
       <c r="E33">
-        <v>187</v>
+        <v>491</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (หมวด 3)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สินค้าตามจังหวัด</t>
+          <t xml:space="preserve">รายงานและนำเสนอ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
+          <t xml:space="preserve">ส่งออก Excel และไฟล์ PowerPoint</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Provinces.js</t>
+          <t xml:space="preserve">components/views/VocReports.js</t>
         </is>
       </c>
       <c r="E34">
-        <v>401</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
+          <t xml:space="preserve">สถานีสแกนจัดส่ง</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
+          <t xml:space="preserve">ยิงบาร์โค๊ดเดินสถานะทีละใบ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Locations.js</t>
+          <t xml:space="preserve">components/views/ShipScan.js</t>
         </is>
       </c>
       <c r="E35">
-        <v>697</v>
+        <v>454</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลหลัก</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายละเอียดลูกค้า</t>
+          <t xml:space="preserve">การจัดส่งสินค้า</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
+          <t xml:space="preserve">เส้นทางและสถานะการส่งของ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Customers.js</t>
+          <t xml:space="preserve">components/views/Shipping.js</t>
         </is>
       </c>
       <c r="E36">
-        <v>596</v>
+        <v>623</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
+          <t xml:space="preserve">สถานะการจัดส่ง</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
+          <t xml:space="preserve">ค้นหา ติดตาม และเวลาแต่ละขั้น</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DocGroups.js</t>
+          <t xml:space="preserve">components/views/ShipStatus.js</t>
         </is>
       </c>
       <c r="E37">
-        <v>357</v>
+        <v>593</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">งานจัดส่ง</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
+          <t xml:space="preserve">การดึงบิลอัตโนมัติ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
+          <t xml:space="preserve">ดึงบิลจากไฟล์ Excel เข้ามาติดตาม</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/PrintForms.js</t>
+          <t xml:space="preserve">components/views/BillImport.js</t>
         </is>
       </c>
       <c r="E38">
-        <v>525</v>
+        <v>892</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
+          <t xml:space="preserve">ข้อมูลสินค้า</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
+          <t xml:space="preserve">รายละเอียด รูปภาพ และบาร์โค๊ด</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
+          <t xml:space="preserve">components/views/Products.js</t>
         </is>
       </c>
       <c r="E39">
-        <v>610</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ข้อมูลกิจการ</t>
+          <t xml:space="preserve">สินค้าตามจังหวัด</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
+          <t xml:space="preserve">แผนที่และยอดคงเหลือรายจังหวัด</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Company.js</t>
+          <t xml:space="preserve">components/views/Provinces.js</t>
         </is>
       </c>
       <c r="E40">
-        <v>164</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองข้อมูล</t>
+          <t xml:space="preserve">ผังที่เก็บสินค้า</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
+          <t xml:space="preserve">กำหนดตำแหน่งจัดเก็บแบบเป็นภาพ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Backup.js</t>
+          <t xml:space="preserve">components/views/Locations.js</t>
         </is>
       </c>
       <c r="E41">
-        <v>300</v>
+        <v>697</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การจัดการระบบ</t>
+          <t xml:space="preserve">ข้อมูลหลัก</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
+          <t xml:space="preserve">รายละเอียดลูกค้า</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
+          <t xml:space="preserve">ทะเบียนลูกค้าและที่อยู่</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Users.js</t>
+          <t xml:space="preserve">components/views/Customers.js</t>
         </is>
       </c>
       <c r="E42">
-        <v>232</v>
+        <v>596</v>
       </c>
     </row>
     <row r="43">
@@ -6236,21 +6303,21 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
+          <t xml:space="preserve">การกำหนดกลุ่มเอกสาร</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SQL Server / MySQL / Access</t>
+          <t xml:space="preserve">รูปแบบเลขที่เอกสารแบบรันนิ่ง</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/SqlServer.js</t>
+          <t xml:space="preserve">components/views/DocGroups.js</t>
         </is>
       </c>
       <c r="E43">
-        <v>748</v>
+        <v>357</v>
       </c>
     </row>
     <row r="44">
@@ -6261,21 +6328,21 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
+          <t xml:space="preserve">ออกแบบฟอร์มพิมพ์</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
+          <t xml:space="preserve">เลือกส่วนที่จะแสดงบนเอกสาร</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/DataImport.js</t>
+          <t xml:space="preserve">components/views/PrintForms.js</t>
         </is>
       </c>
       <c r="E44">
-        <v>894</v>
+        <v>525</v>
       </c>
     </row>
     <row r="45">
@@ -6286,21 +6353,21 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดพนักงานขาย</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
+          <t xml:space="preserve">เพิ่ม แก้ไข และลบคลังกับช่องเก็บ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Salespersons.js</t>
+          <t xml:space="preserve">components/views/WarehouseSetup.js</t>
         </is>
       </c>
       <c r="E45">
-        <v>308</v>
+        <v>610</v>
       </c>
     </row>
     <row r="46">
@@ -6311,21 +6378,21 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+          <t xml:space="preserve">ข้อมูลกิจการ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
+          <t xml:space="preserve">ผู้ออกใบกำกับภาษี</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/ProductTerms.js</t>
+          <t xml:space="preserve">components/views/Company.js</t>
         </is>
       </c>
       <c r="E46">
-        <v>321</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47">
@@ -6336,21 +6403,21 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
+          <t xml:space="preserve">สำรองข้อมูล</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
+          <t xml:space="preserve">สำรองทั้งหมดและกู้คืนกลับมา</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/CustomerKinds.js</t>
+          <t xml:space="preserve">components/views/Backup.js</t>
         </is>
       </c>
       <c r="E47">
-        <v>372</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48">
@@ -6361,95 +6428,245 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มผู้ใช้งาน</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+          <t xml:space="preserve">สร้างบัญชีเข้าระบบด้วยอีเมล</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Password.js</t>
+          <t xml:space="preserve">components/views/Users.js</t>
         </is>
       </c>
       <c r="E48">
-        <v>170</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">เชื่อมต่อฐานข้อมูลภายนอก</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+          <t xml:space="preserve">SQL Server / MySQL / Access</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Reports.js</t>
+          <t xml:space="preserve">components/views/SqlServer.js</t>
         </is>
       </c>
       <c r="E49">
-        <v>2585</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงาน</t>
+          <t xml:space="preserve">การจัดการระบบ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุป</t>
+          <t xml:space="preserve">นำเข้าข้อมูลจาก Excel</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+          <t xml:space="preserve">เลือกหน้าจอแล้วโหลดไฟล์เข้ามา</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">components/views/Graphs.js</t>
+          <t xml:space="preserve">components/views/DataImport.js</t>
         </is>
       </c>
       <c r="E50">
-        <v>499</v>
+        <v>894</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กำหนดพนักงานขาย</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รหัสและชื่อพนักงานขาย</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Salespersons.js</t>
+        </is>
+      </c>
+      <c r="E51">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อของสามมิติ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/ProductTerms.js</t>
+        </is>
+      </c>
+      <c r="E52">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กำหนดประเภทลูกค้า</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนรหัสและชื่อประเภทลูกค้า</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/CustomerKinds.js</t>
+        </is>
+      </c>
+      <c r="E53">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การจัดการระบบ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยนรหัสผ่าน</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตั้งรหัสผ่านใหม่ของบัญชีตัวเอง</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Password.js</t>
+        </is>
+      </c>
+      <c r="E54">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">รายงาน</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr" s="2">
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงานสรุปและการตรวจนับ</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Reports.js</t>
+        </is>
+      </c>
+      <c r="E55">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กราฟสรุป</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปริมาณขึ้น-ลง และยอดคงเหลือ</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">components/views/Graphs.js</t>
+        </is>
+      </c>
+      <c r="E56">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายงาน</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สร้างรายงาน</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr" s="2">
+      <c r="C57" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">เลือกคอลัมน์และจัดรูปแบบเอง</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr" s="2">
+      <c r="D57" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">components/views/ReportBuilder.js</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E57">
         <v>537</v>
       </c>
     </row>
@@ -7136,48 +7353,138 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">app_users</t>
+          <t xml:space="preserve">quotes</t>
         </is>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, email, name, role, active, note, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, doc_no, date, customer_id, cust_code, cust_name, cust_address, cust_province, cust_tax_id, cust_branch, cust_kind, sales_id, sales_code, sales_name, valid_days, valid_to, terms, vat_rate, items_total, bill_discount, base, vat, total, note, status, invoice_id, user_name, ts, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">user_perms</t>
+          <t xml:space="preserve">quote_items</t>
         </is>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">id, user_id, screen_id, can_view, can_edit, can_date, ts, created_at, row_order</t>
+          <t xml:space="preserve">id, quote_id, product_id, qty, price, disc_pct, disc_amt, amount, note, seq, created_at, row_order</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">line_messages</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>17</v>
+      </c>
+      <c r="D39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, msg_id, source, source_kind, source_id, sender_id, sender_name, kind, text, file_url, date, order_id, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">line_orders</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>17</v>
+      </c>
+      <c r="D40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, code, date, source, source_id, party_name, customer_id, status, raw_text, note, owner, quote_id, invoice_id, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">line_order_items</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>13</v>
+      </c>
+      <c r="D41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, order_id, seq, raw, product_id, qty, unit, price, matched_by, score, note, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">line_aliases</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, word, product_id, hits, active, note, user_name, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">app_users</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>9</v>
+      </c>
+      <c r="D43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, email, name, role, active, note, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">user_perms</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>9</v>
+      </c>
+      <c r="D44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">id, user_id, screen_id, can_view, can_edit, can_date, ts, created_at, row_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">screen_perms</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr" s="2">
+      <c r="B45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สิทธิการใช้งานรายหน้าจอ (ดู / แก้ไข / เปลี่ยนวันที่)</t>
         </is>
       </c>
-      <c r="C39">
+      <c r="C45">
         <v>6</v>
       </c>
-      <c r="D39" t="inlineStr" s="2">
+      <c r="D45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">id, can_view, can_edit, can_date, created_at, row_order</t>
         </is>
@@ -7224,7 +7531,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>2804</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="3">
@@ -7239,7 +7546,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4">
@@ -7330,7 +7637,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10">
@@ -7405,7 +7712,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>1027</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="15">
@@ -7480,291 +7787,336 @@
         </is>
       </c>
       <c r="C19">
-        <v>783</v>
+        <v>885</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/image.js</t>
+          <t xml:space="preserve">lib/handoff.js</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
+          <t xml:space="preserve">ส่งร่างเอกสารข้ามหน้าจอ — ใช้ตอนกด "สร้างใบขายจากใบนี้"</t>
         </is>
       </c>
       <c r="C20">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/importSets.js</t>
+          <t xml:space="preserve">lib/image.js</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
+          <t xml:space="preserve">ย่อรูปภาพด้วย canvas ก่อนเก็บลง localStorage เพื่อไม่ให้พื้นที่จัดเก็บเต็ม</t>
         </is>
       </c>
       <c r="C21">
-        <v>266</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/inventorySummary.js</t>
+          <t xml:space="preserve">lib/importSets.js</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
+          <t xml:space="preserve">ชุดข้อมูลที่นำเข้าจาก Excel ได้ — หนึ่งชุดคือหนึ่งหน้าจอ</t>
         </is>
       </c>
       <c r="C22">
-        <v>445</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/logo.js</t>
+          <t xml:space="preserve">lib/inventorySummary.js</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตราสัญลักษณ์ One for All Ultra (OFAU) — เปลวไฟกับลูกศรพุ่งขึ้นเหนือตัวอักษร OFAU</t>
+          <t xml:space="preserve">สรุปข้อมูลคลังสินค้าให้อยู่ในรูปข้อความกระชับ สำหรับส่งให้ผู้ช่วย AI ใช้ตอบคำถาม</t>
         </is>
       </c>
       <c r="C23">
-        <v>32</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/pptx.js</t>
+          <t xml:space="preserve">lib/lineOrders.js</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์นำเสนอ PowerPoint (.pptx) จริง — เขียน XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">งานผ่านไลน์ — สถานะ การอ่านไฟล์แชทที่ส่งออกมา และตัวเลขสรุปสำหรับรายงาน</t>
         </is>
       </c>
       <c r="C24">
-        <v>652</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/printForms.js</t>
+          <t xml:space="preserve">lib/lineParse.js</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
+          <t xml:space="preserve">แปลงข้อความสั่งของจากไลน์ ให้เป็นรายการสินค้าพร้อมจำนวน</t>
         </is>
       </c>
       <c r="C25">
-        <v>191</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/productTerms.js</t>
+          <t xml:space="preserve">lib/logo.js</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
+          <t xml:space="preserve">ตราสัญลักษณ์ One for All Ultra (OFAU) — เปลวไฟกับลูกศรพุ่งขึ้นเหนือตัวอักษร OFAU</t>
         </is>
       </c>
       <c r="C26">
-        <v>88</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/reportData.js</t>
+          <t xml:space="preserve">lib/pptx.js</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์นำเสนอ PowerPoint (.pptx) จริง — เขียน XML เอง ไม่ใช้ไลบรารี</t>
         </is>
       </c>
       <c r="C27">
-        <v>470</v>
+        <v>652</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/store.js</t>
+          <t xml:space="preserve">lib/printForms.js</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
+          <t xml:space="preserve">ฟอร์มพิมพ์ที่ออกแบบเองได้</t>
         </is>
       </c>
       <c r="C28">
-        <v>1398</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/supabase.js</t>
+          <t xml:space="preserve">lib/productTerms.js</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
+          <t xml:space="preserve">ทะเบียนกลุ่มสินค้า · ยี่ห้อสินค้า · ประเภทสินค้า</t>
         </is>
       </c>
       <c r="C29">
-        <v>402</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/targets.js</t>
+          <t xml:space="preserve">lib/reportData.js</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
+          <t xml:space="preserve">ชุดข้อมูลสำหรับหน้า "สร้างรายงาน" — แปลงข้อมูลในระบบให้เป็นตารางแบน ๆ</t>
         </is>
       </c>
       <c r="C30">
-        <v>140</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/thaiAddress.js</t>
+          <t xml:space="preserve">lib/store.js</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
+          <t xml:space="preserve">React Context เก็บข้อมูลคลังสินค้าทั้งระบบ</t>
         </is>
       </c>
       <c r="C31">
-        <v>166</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/voc.js</t>
+          <t xml:space="preserve">lib/supabase.js</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">การรับฟังลูกค้า (SE-AM หมวด 3) — กติกา เกณฑ์ และการคำนวณทั้งหมด</t>
+          <t xml:space="preserve">ตัวเชื่อม Supabase แบบเรียก REST ตรงด้วย fetch — ไม่ต้องติดตั้ง package เพิ่ม</t>
         </is>
       </c>
       <c r="C32">
-        <v>1033</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/vocManual.js</t>
+          <t xml:space="preserve">lib/targets.js</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือการใช้งานหมวดการรับฟังลูกค้า — เนื้อหาของไฟล์ Word</t>
+          <t xml:space="preserve">เป้าขาย — การจับคู่เป้ากับยอดขายจริง</t>
         </is>
       </c>
       <c r="C33">
-        <v>864</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/vocReport.js</t>
+          <t xml:space="preserve">lib/thaiAddress.js</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานของหมวดการรับฟังลูกค้า — ประกอบตารางและไฟล์นำเสนอจากข้อมูลชุดเดียว</t>
+          <t xml:space="preserve">ตำบล / อำเภอ / จังหวัด / รหัสไปรษณีย์ ของไทย — ข้อมูลนิ่ง ไม่ต้องเรียกเว็บนอก</t>
         </is>
       </c>
       <c r="C34">
-        <v>498</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/whSummary.js</t>
+          <t xml:space="preserve">lib/voc.js</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า–ออกในช่วงที่เลือก</t>
+          <t xml:space="preserve">การรับฟังลูกค้า (SE-AM หมวด 3) — กติกา เกณฑ์ และการคำนวณทั้งหมด</t>
         </is>
       </c>
       <c r="C35">
-        <v>178</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsx.js</t>
+          <t xml:space="preserve">lib/vocManual.js</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+          <t xml:space="preserve">คู่มือการใช้งานหมวดการรับฟังลูกค้า — เนื้อหาของไฟล์ Word</t>
         </is>
       </c>
       <c r="C36">
-        <v>253</v>
+        <v>864</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">lib/xlsxRead.js</t>
+          <t xml:space="preserve">lib/vocReport.js</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
+          <t xml:space="preserve">รายงานของหมวดการรับฟังลูกค้า — ประกอบตารางและไฟล์นำเสนอจากข้อมูลชุดเดียว</t>
         </is>
       </c>
       <c r="C37">
-        <v>223</v>
+        <v>498</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">lib/whSummary.js</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า–ออกในช่วงที่เลือก</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">lib/xlsx.js</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งออกเป็นไฟล์ Excel (.xlsx) จริง — เขียน zip กับ XML เอง ไม่ใช้ไลบรารี</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">lib/xlsxRead.js</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อ่านไฟล์ Excel (.xlsx) และ CSV ให้กลายเป็นตารางสองมิติ</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">lib/zip.js</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="2">
+      <c r="B41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ประกอบไฟล์ zip เอง — ไม่ใช้ไลบรารี</t>
         </is>
       </c>
-      <c r="C38">
+      <c r="C41">
         <v>124</v>
       </c>
     </row>
@@ -8165,6 +8517,18 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">งานผ่านไลน์ต่อครบ และไม่มีทางลัดข้ามคน</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -102,7 +102,7 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">25 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
+          <t xml:space="preserve">26 หมวด (npm run check) — ทุกหมวดถูกทดสอบว่าจับผิดได้จริงก่อนใช้</t>
         </is>
       </c>
     </row>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">89 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 87 ครั้ง</t>
+          <t xml:space="preserve">90 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 88 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3721,6 +3721,50 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91">
+        <v>91</v>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">คู่มือติดตั้ง สำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- เพิ่ม Docs/คู่มือการติดตั้ง.md ไล่ทีละขั้น: วางโครงโฟลเดอร์ -&gt;
+สร้างฐานข้อมูลใน Supabase -&gt; ตั้งค่าและ deploy บน Vercel
+- เขียนเฉพาะสิ่งที่จำเป็น ของเสริม (ผู้ช่วย AI, รับข้อความจากไลน์
+อัตโนมัติ) แยกไว้ท้ายไฟล์และบอกชัดว่าข้ามได้
+ค่าที่จำเป็นจริง ๆ มีแค่สองตัว คือ NEXT_PUBLIC_SUPABASE_URL
+และ NEXT_PUBLIC_SUPABASE_ANON_KEY
+- มีตารางไล่สาเหตุตอนล็อกอินไม่ได้ เรียงตามข้อความที่เห็นบนหน้าจอ
+เพราะระบบมีข้อความบอกสาเหตุอยู่แล้ว แต่ไม่มีที่ไหนบอกว่าแต่ละข้อความ
+ต้องไปแก้ตรงไหน · สามสาเหตุที่พบบ่อยที่สุดคือ ลืมติ๊ก Auto Confirm
+User · ใส่ตัวแปรแล้วไม่ได้ Redeploy · ยังไม่ได้รัน schema.sql
+- เพิ่มวิธีดูจาก DevTools สำหรับกรณีที่ข้อความบนจอไม่พอ
+ดูคำขอ token?grant_type=password แล้วแยกตาม HTTP status
+(ไม่มีคำขอ = ตัวแปรไม่ถึงหน้าเว็บ · 400 = รหัสผ่าน · 401 = anon key
+· Failed to fetch = URL ผิดหรือโปรเจกต์ถูก pause)
+- เพิ่ม LINE_CHANNEL_SECRET และ SUPABASE_SERVICE_ROLE_KEY
+ใน .env.local.example ซึ่งตกไปตั้งแต่รอบ 90
+- แก้ README ที่ยังบอกว่ามี 30 ตาราง (จริง 44) และเพิ่มลิงก์ไปคู่มือ
+- เพิ่มตัวตรวจหมวด 26 เฝ้าไม่ให้คู่มือเพี้ยนจากของจริง:
+ตัวแปรทุกตัวที่โค้ดอ่านจริง ต้องมีใน .env.local.example
+(ยกเว้นตัวที่ Vercel ตั้งให้เอง ซึ่งคนใช้ตั้งไม่ได้อยู่แล้ว)
+ค่าที่ขาดไม่ได้ต้องอยู่ในคู่มือด้วย ไม่ใช่แค่ในไฟล์ตัวอย่าง
+จำนวนตารางที่คู่มือและ README บอก ต้องตรงกับ schema.sql
+จำนวนหมวดที่ตรวจ ต้องตรงกับที่คู่มือบอก
+ต้องเตือนครบทั้งสามข้อที่พลาดบ่อยที่สุด
+เหตุผล: คู่มือที่ข้อมูลไม่ตรงกับโค้ด แย่กว่าไม่มีคู่มือเลย
+เพราะคนทำตามจนสุดทางแล้วระบบยังไม่ทำงาน โดยไม่รู้ว่าตัวเองพลาด
+หรือคู่มือผิด และคนเขียนไม่มีทางรู้ตัว เพราะคู่มือไม่ได้ถูกรัน
+ตัวตรวจจับได้ทันทีที่เพิ่ม: คู่มือบอก 25 หมวด แต่มีจริง 26
+และ README ค้างที่ 30 ตารางมานาน
+ทดสอบย้อน 6 กรณี จับได้ทุกกรณี</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3758,12 +3802,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3819,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -3792,12 +3836,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3853,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -3826,29 +3870,29 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -3860,12 +3904,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -3877,12 +3921,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3894,29 +3938,29 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3928,12 +3972,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3989,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -3962,12 +4006,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -3979,12 +4023,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -3996,12 +4040,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4013,29 +4057,29 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4047,12 +4091,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4064,12 +4108,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4081,12 +4125,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4142,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4159,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4176,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4193,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4210,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4227,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4200,12 +4244,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4217,12 +4261,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4234,12 +4278,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4295,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4312,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4329,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4302,12 +4346,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4363,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4380,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4353,12 +4397,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4370,29 +4414,29 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4448,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4421,12 +4465,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4438,12 +4482,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4455,12 +4499,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4472,29 +4516,29 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4506,12 +4550,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4523,12 +4567,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4540,12 +4584,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4557,12 +4601,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4618,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4591,12 +4635,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4608,12 +4652,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4669,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4642,12 +4686,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4659,12 +4703,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4676,12 +4720,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4737,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4754,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4771,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4744,12 +4788,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4761,12 +4805,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4778,12 +4822,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4795,29 +4839,29 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4873,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4846,12 +4890,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4907,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4880,12 +4924,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4897,12 +4941,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4958,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4975,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4992,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -4965,12 +5009,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -4982,29 +5026,29 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5016,12 +5060,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5033,29 +5077,29 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5111,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5128,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5101,12 +5145,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5118,29 +5162,29 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5196,12 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5213,12 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5230,12 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5203,27 +5247,44 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr" s="2">
+      <c r="B89" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr" s="2">
+      <c r="C89" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -8529,6 +8590,18 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">คู่มือติดตั้งตรงกับของจริง</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">90 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 88 ครั้ง</t>
+          <t xml:space="preserve">91 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 89 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3765,6 +3765,55 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92">
+        <v>92</v>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าถึงขั้นไหน</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- เพิ่ม Docs/เช็คลิสต์การติดตั้ง.xlsx 6 ชีต สร้างด้วย
+tools/make-setup-xlsx.mjs ใช้ตัวเขียน .xlsx ของระบบเอง
+ไม่ลงไลบรารีเพิ่ม ตามข้อกำหนดของโครงงาน
+1 วิธีใช้                  ความหมายของช่องสถานะและช่องจำเป็น
+2 เช็คลิสต์ติดตั้ง         26 ขั้น เรียงตามลำดับที่ต้องทำจริง
+3 ค่าที่ต้องตั้ง            ตัวแปรทุกตัวที่โค้ดอ่านจริง
+4 ตั้งค่าเริ่มต้นเชิงพาณิชย์ 18 หัวข้อในโปรแกรม
+5 ตรวจรับก่อนใช้จริง       12 ข้อ เดินงานจริงหนึ่งรอบ
+6 แก้ปัญหา                 11 อาการพร้อมสาเหตุและวิธีแก้
+- ทุกชีตมีช่องสถานะ ผู้ทำ และวันที่ ให้กรอกติดตามได้
+ค่าตั้งต้นเป็น "รอทำ" ทุกแถว จะได้กรองและนับได้ว่าเหลืออีกกี่ข้อ
+- ลำดับในชีตที่ 2 เรียงตามการอ้างอิงกันจริง ไม่ได้เรียงตามใจ:
+ต้องสร้างฐานข้อมูลและได้ URL กับ key มาก่อน ถึงจะตั้งค่าที่ Vercel ได้
+จึงวางช่วงฐานข้อมูลไว้ก่อนช่วง Vercel ไม่ใช่ตามลำดับที่คนมักนึกถึง
+- ลำดับในชีตที่ 4 ก็มาจากการอ้างอิงกันจริงเช่นกัน:
+ข้อมูลกิจการต้องมาก่อนออกเอกสารใบแรก · คลังต้องมาก่อนรับสินค้า ·
+ทะเบียนจำแนกสินค้าต้องมาก่อนเพิ่มสินค้า ·
+รูปแบบเลขที่เอกสารต้องตั้งก่อนออกใบแรก เพราะเปลี่ยนทีหลัง
+เลขเก่าไม่เปลี่ยนตาม จะได้เอกสารสองรูปแบบปนกัน
+- ชีตที่ 5 บังคับให้เดินงานจริงหนึ่งรอบก่อนเปิดใช้ (ซื้อ -&gt; ตรวจยอด -&gt;
+ขาย POS -&gt; ใบกำกับภาษี -&gt; ใบเสนอราคา -&gt; จัดส่ง -&gt; รายงาน -&gt;
+สำรอง -&gt; กู้คืน -&gt; ล้างข้อมูลทดลอง) เจอปัญหาตอนนี้ดีกว่าเจอตอน
+มีลูกค้ายืนรออยู่หน้าเคาน์เตอร์ · ข้อกู้คืนไฟล์สำรองสำคัญที่สุด
+เพราะไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง
+- ตัวสร้างมีด่านของตัวเอง หยุดทำงานทันทีถ้าอ้างถึงหน้าจอที่ไม่มีอยู่จริง
+หรือเจอตัวแปรที่โค้ดอ่านแต่เช็คลิสต์ไม่ได้อธิบายไว้
+เพราะเช็คลิสต์ที่ข้อมูลผิด อันตรายกว่าไม่มีเช็คลิสต์
+คนติ๊กครบแล้วคิดว่าเสร็จ ทั้งที่ยังมีข้อที่ไม่ได้ทำ
+ทดสอบย้อน 2 กรณี จับได้ทั้งคู่
+- ขยายตัวตรวจหมวด 26 ให้ครอบไฟล์นี้ด้วย: ต้องมีตัวสร้าง ·
+ตัวสร้างต้องยังมีด่านกันเนื้อหาเพี้ยน · ตัวแปรทุกตัวต้องถูกพูดถึง ·
+และไฟล์ .xlsx ต้องถูกสร้างไว้แล้วจริง
+- เพิ่มชุดทดสอบที่เปิดไฟล์ที่สร้างออกมาด้วยตัวอ่าน xlsx ของระบบเอง
+ตรวจว่าอ่านภาษาไทยออก มีครบ 6 ชีต และมีข้อเตือนสำคัญอยู่จริง
+- เชื่อมลิงก์จาก README และจากคู่มือติดตั้งไปยังไฟล์นี้</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3797,17 +3846,17 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -3819,12 +3868,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3885,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -3853,12 +3902,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -3870,12 +3919,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -3887,29 +3936,29 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3970,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3987,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -3955,29 +4004,29 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -3989,12 +4038,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4006,12 +4055,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4072,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4089,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4057,12 +4106,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4074,29 +4123,29 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4157,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4125,12 +4174,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4191,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4208,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4225,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4242,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4210,12 +4259,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4227,12 +4276,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4293,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4310,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4278,12 +4327,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4295,12 +4344,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4361,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4329,12 +4378,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4395,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4412,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4429,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4446,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4414,12 +4463,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4431,29 +4480,29 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4514,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4531,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4499,12 +4548,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4565,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4533,29 +4582,29 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4567,12 +4616,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4633,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4650,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4618,12 +4667,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4684,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4652,12 +4701,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4669,12 +4718,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4686,12 +4735,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4703,12 +4752,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4769,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4786,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4803,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4771,12 +4820,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4837,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4805,12 +4854,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4871,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4888,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4856,29 +4905,29 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4939,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4956,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4973,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4990,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -4958,12 +5007,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -4975,12 +5024,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -4992,12 +5041,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5058,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5026,12 +5075,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5043,29 +5092,29 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5077,12 +5126,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5094,29 +5143,29 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5177,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5194,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5211,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5179,29 +5228,29 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5213,12 +5262,12 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5279,12 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5247,12 +5296,12 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5264,27 +5313,44 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr" s="2">
+      <c r="B90" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr" s="2">
+      <c r="C90" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">91 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 89 ครั้ง</t>
+          <t xml:space="preserve">92 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 90 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3814,6 +3814,56 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93">
+        <v>93</v>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- เพิ่มสองชีตในเช็คลิสต์ Excel (เป็น 8 ชีต) และสองหัวข้อในคู่มือ
+7 คำสั่งที่ต้องใช้   25 แถว แบ่งสี่กลุ่ม
+8 ความปลอดภัย      21 ข้อ แบ่งหกหมวด พร้อมช่องสถานะและผู้ตรวจ
+- ชีตคำสั่งแบ่งเป็น ติดตั้งและรันในเครื่อง · งานกับ Git และการ deploy ·
+สคริปต์ของโครงงาน · งานกับฐานข้อมูล
+แต่ละแถวบอก ทำอะไร ใช้ตอนไหน และข้อควรรู้
+เช่น push ขึ้น main คือการ deploy ขึ้นเว็บจริง และ
+git checkout ทำให้สิ่งที่แก้หายทันทีและกู้ไม่ได้
+- รายการคำสั่งอ่านจาก package.json และโฟลเดอร์ tools ตอนสร้างไฟล์
+ไม่ได้พิมพ์มือ · ถ้าเพิ่ม script หรือเพิ่มไฟล์ใน tools แล้วไม่ได้
+เขียนคำอธิบาย ตัวสร้างจะหยุดทำงานทันที
+เพราะคำสั่งที่มีอยู่แต่ไม่มีใครรู้ว่ามี ก็เท่ากับไม่มี
+หัวข้อความปลอดภัย หกหมวด
+- กุญแจและความลับ: แยก anon key กับ service_role key ให้ออก ·
+ชื่อตัวแปรลับห้ามขึ้นต้นด้วย NEXT_PUBLIC_ · .env.local ห้ามขึ้น git ·
+และวิธีเปลี่ยนกุญแจเมื่อสงสัยว่าหลุด (ลบไฟล์อย่างเดียวไม่พอ
+กุญแจที่หลุดแล้วใช้ได้ตลอดไปจนกว่าจะ reset)
+- บัญชีผู้ใช้: หนึ่งคนหนึ่งบัญชี · ปิดการสมัครเองเมื่อสร้างครบแล้ว ·
+ปิดบัญชีคนลาออกทันที · แอดมินต้องมีมากกว่าหนึ่งคน
+- สิทธิการใช้งาน: เขียนตรง ๆ ว่าสิทธิรายหน้าจอเป็นการคุมลำดับงาน
+ไม่ใช่กำแพงกันข้อมูล เพราะ policy ของตารางข้อมูลตั้งไว้ว่า
+ผู้ที่ล็อกอินแล้วเข้าถึงได้ทุกตาราง คนที่ล็อกอินจึงยังยิง API
+อ่านและเขียนได้เอง · ข้อนี้สำคัญที่สุดในหมวด เพราะถ้าเข้าใจผิด
+จะให้บัญชีระบบกับคนที่ไม่ควรเห็นข้อมูลทั้งหมด โดยคิดว่าตั้งสิทธิแล้วปลอดภัย
+ถ้าต้องกั้นถึงระดับข้อมูลจริง ต้องเขียน policy ตามบทบาทเพิ่มทุกตาราง
+- ฐานข้อมูล: สองด่าน GRANT กับ RLS ต้องผ่านทั้งคู่ และอาการต่างกัน ·
+รหัสผ่านฐานข้อมูลข้ามทุกสิทธิ์เหมือน service_role ·
+รหัสผ่านการเชื่อมต่อภายนอกไม่ควรเก็บขึ้นฐานข้อมูล
+- ไฟล์สำรองข้อมูล: เป็นข้อมูลจริงทั้งก้อน หลุดเท่ากับฐานข้อมูลหลุด ·
+ต้องทดลองกู้คืนจริงอย่างน้อยหนึ่งครั้ง เพราะไฟล์สำรองที่กู้ไม่ได้
+ไม่ใช่ไฟล์สำรอง และจะรู้ตอนที่สายเกินไปเสมอ
+- การเชื่อมต่อภายนอกและการใช้งานประจำวัน: ลายเซ็นของ webhook ·
+ข้อความจากไลน์ไม่กลายเป็นเอกสารเอง · จำกัดคนใช้ผู้ช่วย AI ·
+ออกจากระบบเมื่อใช้เครื่องร่วมกัน
+- ขยายตัวตรวจหมวด 26: ทุก script ใน package.json และทุกไฟล์ใน tools
+ต้องถูกอ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3851,29 +3901,29 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -3885,12 +3935,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3952,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -3919,12 +3969,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3986,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -3953,29 +4003,29 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -3987,12 +4037,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4054,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4021,29 +4071,29 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4105,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4072,12 +4122,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4139,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4106,12 +4156,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4123,12 +4173,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4140,29 +4190,29 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4224,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4191,12 +4241,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4258,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4275,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4292,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4309,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4276,12 +4326,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4343,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4360,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4327,12 +4377,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4394,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4361,12 +4411,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4428,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4445,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4462,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4479,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4446,12 +4496,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4513,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4530,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4497,29 +4547,29 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4531,12 +4581,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4548,12 +4598,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4615,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4632,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4599,29 +4649,29 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4633,12 +4683,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4650,12 +4700,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4717,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4684,12 +4734,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4751,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4768,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4735,12 +4785,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4802,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4769,12 +4819,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4836,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4803,12 +4853,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4820,12 +4870,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4887,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4904,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4921,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4888,12 +4938,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4955,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4922,29 +4972,29 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -4956,12 +5006,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -4973,12 +5023,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -4990,12 +5040,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5007,12 +5057,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5074,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5041,12 +5091,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5058,12 +5108,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5125,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5092,12 +5142,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5109,29 +5159,29 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5193,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5160,29 +5210,29 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5244,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5261,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5228,12 +5278,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5245,29 +5295,29 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5329,12 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5346,12 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5363,12 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5330,27 +5380,44 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr" s="2">
+      <c r="B91" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr" s="2">
+      <c r="C91" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">92 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 90 ครั้ง</t>
+          <t xml:space="preserve">93 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 91 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3864,6 +3864,54 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94">
+        <v>94</v>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตัวช่วยติดตั้ง — สั่งคำสั่งเดียวแล้วมันบอกเองว่าเหลืออะไร</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- โจทย์: คู่มือบอกได้ว่า "ต้องทำอะไรบ้าง" แต่บอกไม่ได้ว่า
+"ตอนนี้คุณอยู่ตรงไหน" คนติดตั้งจึงต้องไล่อ่านทั้งคู่มือ
+แล้วเดาเองว่าพลาดตรงไหน ซึ่งเป็นส่วนที่เสียเวลาที่สุด
+- เพิ่ม tools/setup.mjs (npm run setup) ตรวจหกหมวดแล้วสรุปเป็น
+รายการสิ่งที่ต้องทำต่อ เรียงตามลำดับ:
+1 ไฟล์ที่โปรเจกต์ต้องมี   รวมถึง .gitignore กันไฟล์ลับจริงหรือไม่
+2 ไฟล์ .env.local        มีหรือยัง (--init สร้างให้จากไฟล์ตัวอย่าง)
+3 ค่าที่ขาดไม่ได้สองตัว   ตั้งแล้วหรือยัง และยังเป็นค่าตัวอย่างอยู่ไหม
+4 เชื่อมต่อ Supabase     ต่อได้ไหม กุญแจใช้ได้ไหม ตารางครบไหม
+5 ระบบล็อกอิน            เปิดให้สมัครเองค้างไว้ไหม มีผู้ใช้หรือยัง
+6 ค่าเสริม               ตั้งอะไรไว้แล้วบ้าง (ไม่ตั้งไม่ถือว่าผิด)
+- ตรวจของจริงถึง Supabase ไม่ได้เดาจากไฟล์ · รายชื่อตารางอ่านจาก
+schema.sql ตัวเดียวกับที่ใช้สร้างจริง จึงไม่มีวันบอกจำนวนผิด
+- ทำงานจากนอกโปรแกรม จึงใช้ได้ตอนที่ยังเปิดเว็บไม่ได้หรือล็อกอินไม่ผ่าน
+ซึ่งเป็นตอนที่ต้องการความช่วยเหลือมากที่สุด
+และใช้แค่ของที่มากับ Node จึงรันได้โดยไม่ต้อง npm install
+- จับข้อผิดพลาดที่อันตรายที่สุดให้ด้วย: ถ้าเอา service_role key
+ไปใส่ช่อง ANON_KEY จะฟ้องทันทีพร้อมบอกว่าทำไมถึงอันตราย
+(อ่าน role จากตัวกุญแจเอง ไม่ต้องยิงไปถามใคร)
+ข้อนี้พลาดแล้วใครเปิดเว็บก็ลบข้อมูลได้ทั้งระบบ และไม่มีอะไรเตือน
+- แยก "ไม่ผ่าน" กับ "ข้าม" ออกจากกัน ค่าเสริมที่ไม่ได้ตั้งเป็นแค่ข้าม
+ไม่นับเป็นความผิด ไม่งั้นคนติดตั้งจะเห็นรายการยาวเหยียดแล้วท้อ
+ทั้งที่จริงเหลือแค่สองข้อ
+- ขั้นที่ตรวจไม่ได้เพราะขั้นก่อนหน้ายังไม่เสร็จ ขึ้นว่า "ข้าม" ไม่ใช่
+"ไม่ผ่าน" ไม่งั้นความผิดข้อเดียวจะกลายเป็นห้าข้อ แล้วอ่านไม่ออกว่า
+ต้นเหตุจริงคือข้อไหน
+- เพิ่มหน้า "เริ่มเร็ว 8 ขั้น" ไว้บนสุดของคู่มือ เป็นตารางแปดแถว
+สำหรับคนที่เคยติดตั้งมาแล้ว ไม่ต้องอ่านทั้งไฟล์
+- เพิ่มแถวในเช็คลิสต์ Excel ช่วง C ให้สั่ง npm run setup ตรวจ
+ตั้งแต่ตอนทำฐานข้อมูลเสร็จ ดีกว่าไปรู้ตอนขึ้น Vercel แล้วล็อกอินไม่ได้
+- ทดสอบ 15 ข้อ ครอบคลุม: ยังไม่ตั้งค่าอะไรเลย · ใส่ service_role
+ผิดช่อง · กุญแจชนิดถูกต้อง · ค่าที่ยังเป็นตัวอย่าง · ค่าเสริมที่ไม่ได้ตั้ง
+ต้องไม่ถูกนับว่าผิด · และต้องชี้ไปคู่มือกับเช็คลิสต์เสมอ
+- ตัวสร้างเช็คลิสต์จับได้เองทันทีที่เพิ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3901,12 +3949,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -3918,29 +3966,29 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -3952,12 +4000,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -3969,12 +4017,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -3986,12 +4034,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4003,12 +4051,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4020,29 +4068,29 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4102,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4119,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4088,29 +4136,29 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4170,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4187,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4204,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4173,12 +4221,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4238,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4207,29 +4255,29 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4289,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4306,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4275,12 +4323,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4340,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4309,12 +4357,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4374,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4391,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4408,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4425,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4442,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4459,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4428,12 +4476,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4493,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4462,12 +4510,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4527,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4544,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4513,12 +4561,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4578,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4547,12 +4595,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4564,29 +4612,29 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4646,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4663,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4632,12 +4680,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4697,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4666,29 +4714,29 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4700,12 +4748,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4765,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4782,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4751,12 +4799,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4768,12 +4816,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4785,12 +4833,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4802,12 +4850,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4867,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4884,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4901,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4870,12 +4918,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4887,12 +4935,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4952,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4921,12 +4969,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4986,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -4955,12 +5003,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -4972,12 +5020,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -4989,29 +5037,29 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5023,12 +5071,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5088,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5105,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5074,12 +5122,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5139,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5108,12 +5156,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5125,12 +5173,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5142,12 +5190,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5159,12 +5207,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5176,29 +5224,29 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5258,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5227,29 +5275,29 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5309,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5326,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5343,12 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5312,29 +5360,29 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5394,12 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5363,12 +5411,12 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5428,12 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5397,27 +5445,44 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr" s="2">
+      <c r="B92" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr" s="2">
+      <c r="C92" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">93 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 91 ครั้ง</t>
+          <t xml:space="preserve">94 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 92 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3912,6 +3912,47 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95">
+        <v>95</v>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- รอบก่อนตัวช่วยติดตั้งถูกพูดถึงกระจายอยู่หลายที่ในคู่มือ
+(หน้าเริ่มเร็ว ตารางคำสั่ง ส่วนรันในเครื่อง) แต่ไม่มีหัวข้อของตัวเอง
+คนอ่านจึงรู้ว่ามีคำสั่งนี้ แต่ไม่รู้ว่ามันตรวจอะไรและอ่านผลยังไง
+- เพิ่มหัวข้อ "ตัวช่วยติดตั้ง — npm run setup" วางไว้ก่อนหัวข้อล็อกอินไม่ได้
+มีตารางบอกว่าตรวจหกหมวดอะไรบ้าง · ตารางแปลความหมายของ
+ผ่าน / เตือน / ไม่ผ่าน / ข้าม · ตัวอย่างผลลัพธ์จริง
+- อธิบายว่าทำไม "ข้าม" ไม่ใช่ความผิด: ถ้านับรวมเป็นความผิด
+ความผิดข้อเดียวจะกลายเป็นห้าข้อ แล้วอ่านไม่ออกว่าต้นเหตุจริงคือข้อไหน
+- เพิ่มหัวข้อย่อย "สามเรื่องที่มันจับได้ แต่ตาคนมักมองข้าม":
+เอา service_role ไปใส่ช่อง anon (ปกติไม่มีอะไรเตือนเลย
+เพราะระบบยังทำงานได้ปกติทุกอย่าง) · ตารางขาดไปบางตัวตอนอัปเดต ·
+เปิดให้สมัครสมาชิกเองค้างไว้
+- เพิ่มหัวข้อย่อย "สิ่งที่มันตรวจไม่ได้" ซึ่งสำคัญพอกัน:
+ไม่ได้ตรวจค่าที่ตั้งไว้บน Vercel เพราะอ่านจากเครื่องที่รันคำสั่ง
+ไม่บอกไว้ คนจะเห็นว่า "พร้อมใช้งาน" แล้วงงว่าทำไมเว็บจริงยังล็อกอินไม่ได้
+รวมถึงไม่ได้ตรวจรหัสผ่านผู้ใช้ และนับจำนวนผู้ใช้ได้เฉพาะเมื่อมี
+service_role key
+- หัวข้อล็อกอินไม่ได้ ให้เริ่มจากสั่ง npm run setup ก่อนเป็นอย่างแรก
+และบอกว่าถ้ามันขึ้นว่าพร้อมแล้วแต่ยังล็อกอินไม่ได้ ข้อที่พบบ่อยที่สุด
+คือตั้งค่าที่เครื่องครบแต่ยังไม่ได้ตั้งที่ Vercel หรือตั้งแล้วไม่ได้ Redeploy
+- ชีตแก้ปัญหาในไฟล์ Excel เพิ่มแถวแรกให้สั่ง npm run setup ก่อน
+ทั้งสองที่จึงชี้ไปทางเดียวกัน
+- ขยายตัวตรวจหมวด 26 อีกสามข้อ: คู่มือต้องมีหัวข้อนี้ ·
+ทุกหมวดที่ตัวช่วยตรวจจริงต้องมีในตารางของคู่มือ (อ่านจาก head()
+ในตัวช่วยเอง จึงเพี้ยนไม่ได้) · และต้องบอกข้อจำกัดเรื่อง Vercel ไว้
+ตัวตรวจจับได้ทันทีว่าตารางในคู่มือใช้ชื่อหมวดย่อไม่ตรงกับที่ขึ้นบนจอ
+ทดสอบย้อนรวม 10 กรณี จับได้ทุกกรณี</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3949,12 +3990,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8b137dc</t>
+          <t xml:space="preserve">c0a6a56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
+          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
         </is>
       </c>
     </row>
@@ -3966,12 +4007,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -3983,29 +4024,29 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -4017,12 +4058,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4075,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4092,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4068,12 +4109,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4085,29 +4126,29 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4119,12 +4160,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4177,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4153,29 +4194,29 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4228,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4204,12 +4245,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4262,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4238,12 +4279,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4296,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4272,29 +4313,29 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4347,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4364,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4381,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4398,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4415,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4432,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4408,12 +4449,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4466,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4483,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4459,12 +4500,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4476,12 +4517,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4534,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4551,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4527,12 +4568,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4585,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4561,12 +4602,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4619,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4636,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4653,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4629,29 +4670,29 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4704,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4680,12 +4721,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4738,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4755,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4731,29 +4772,29 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4765,12 +4806,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4782,12 +4823,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4840,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4816,12 +4857,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4833,12 +4874,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4850,12 +4891,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4867,12 +4908,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4884,12 +4925,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4901,12 +4942,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4918,12 +4959,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4976,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4993,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -4969,12 +5010,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -4986,12 +5027,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -5003,12 +5044,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5061,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -5037,12 +5078,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -5054,29 +5095,29 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5129,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5105,12 +5146,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5122,12 +5163,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5139,12 +5180,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5156,12 +5197,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5214,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5190,12 +5231,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5248,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5224,12 +5265,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5241,29 +5282,29 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5316,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5292,29 +5333,29 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5326,12 +5367,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5343,12 +5384,12 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5360,12 +5401,12 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5377,29 +5418,29 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5452,12 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5469,12 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5445,12 +5486,12 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5462,27 +5503,44 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr" s="2">
+      <c r="B93" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr" s="2">
+      <c r="C93" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">94 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 92 ครั้ง</t>
+          <t xml:space="preserve">95 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 93 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3953,6 +3953,50 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96">
+        <v>96</v>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- ขั้นตอนติดตั้งเป็นเรื่องของ "อะไรต้องมาก่อนอะไร" ซึ่งอ่านจากข้อความ
+ยาว ๆ แล้วนึกภาพไม่ออก คนจึงทำ Vercel ก่อน Supabase
+แล้วไปติดตรงที่ไม่มีค่าจะใส่ ทั้งที่คู่มือเขียนลำดับไว้ถูกแล้ว
+- เพิ่ม 7 ผัง ใช้อักขระวาดเส้นธรรมดาในบล็อกโค้ด
+จึงอ่านได้เหมือนกันทั้งบน GitHub ใน VS Code และในโปรแกรมแก้ข้อความ
+ไม่ได้ใช้ mermaid เพราะที่ไม่รองรับจะเห็นเป็นโค้ดดิบอ่านไม่รู้เรื่อง
+และโครงงานนี้ไม่มีที่ไหนใช้อยู่แล้ว
+- หัวข้อใหม่ "ภาพรวม — ระบบประกอบด้วยอะไร และติดตั้งเรียงยังไง"
+วางไว้ต่อจากหน้าเริ่มเร็ว มีสามผัง:
+ผังที่ 1  ระบบมีสามส่วน (เบราว์เซอร์ -&gt; Vercel -&gt; Supabase)
+พร้อมย้ำว่าโค้ดอยู่ที่ Vercel แต่ข้อมูลอยู่ที่ Supabase
+deploy ใหม่กี่ครั้งข้อมูลก็ไม่หาย แต่ลบโปรเจกต์ Supabase
+เมื่อไรหายทันที
+ผังที่ 2  ลำดับการติดตั้ง 5 ขั้น พร้อมลูกศรชี้ว่าทำไม Supabase
+ต้องมาก่อน Vercel (ขั้นถัดไปต้องใช้ค่าจากที่นี่)
+ผังที่ 3  ค่าสองตัวไปไหนบ้าง — ค่าเดียวกันต้องใส่สองที่
+(.env.local และ Vercel) และ Vercel ต้อง Redeploy
+ถึงจะมีผล · ย้ำว่า npm run setup ตรวจได้แค่ฝั่งเครื่อง
+- ผังไล่หาสาเหตุตอนล็อกอินไม่ได้ เป็นต้นไม้ตัดสินใจ
+เริ่มจาก npm run setup แล้วแยกทางตามผลที่ได้
+ปลายทางทุกกิ่งจบที่สาเหตุที่ชัดเจน ไม่มีกิ่งไหนที่ไปแล้วตัน
+- หัวข้อใหม่ "ลำดับการตั้งค่าเริ่มต้นในโปรแกรม" พร้อมสองผัง:
+ผังการพึ่งพากันของการตั้งค่า (ข้อมูลกิจการกับกลุ่มเอกสาร
+ต้องมาก่อนออกเอกสาร · คลังต้องมาก่อนสินค้า ต้องมาก่อนยอดยกมา)
+ผังการตรวจรับ เดินงานจริงหนึ่งรอบแล้ววนกลับมาล้างข้อมูลทดลอง
+- ขยายตัวตรวจหมวด 26 สองข้อ: คู่มือต้องมีหัวข้อภาพรวม ·
+และต้องมีผังลำดับงานอย่างน้อย 6 ผัง
+ตัวจับผังนับจากบล็อกโค้ดที่มีลูกศรหรือเส้นแยกกิ่ง จึงไม่ผูกกับ
+ข้อความใดข้อความหนึ่ง ลบผังไปผังเดียวยังไม่ฟ้อง แต่ลบยกชุดฟ้องทันที
+ทดสอบย้อนรวม 12 กรณี จับได้ทุกกรณี</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -3990,12 +4034,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0a6a56</t>
+          <t xml:space="preserve">589134d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
+          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
         </is>
       </c>
     </row>
@@ -4007,12 +4051,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8b137dc</t>
+          <t xml:space="preserve">c0a6a56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
+          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
         </is>
       </c>
     </row>
@@ -4024,12 +4068,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -4041,29 +4085,29 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -4075,12 +4119,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -4092,12 +4136,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4153,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4170,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4143,29 +4187,29 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4177,12 +4221,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4194,12 +4238,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4211,29 +4255,29 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4245,12 +4289,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4262,12 +4306,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4323,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4296,12 +4340,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4313,12 +4357,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4330,29 +4374,29 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4408,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4425,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4442,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4415,12 +4459,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4432,12 +4476,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4449,12 +4493,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4510,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4527,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4544,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4517,12 +4561,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4578,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4551,12 +4595,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4568,12 +4612,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4629,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4646,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4663,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4680,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4653,12 +4697,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4714,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4687,29 +4731,29 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4765,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4782,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4755,12 +4799,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4772,12 +4816,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4789,29 +4833,29 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4867,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4884,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4857,12 +4901,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4918,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4891,12 +4935,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4908,12 +4952,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4925,12 +4969,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4986,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -4959,12 +5003,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -4976,12 +5020,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -4993,12 +5037,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -5010,12 +5054,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -5027,12 +5071,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5088,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5105,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -5078,12 +5122,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -5095,12 +5139,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -5112,29 +5156,29 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5190,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5207,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5224,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5241,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5258,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5275,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5248,12 +5292,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5265,12 +5309,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5326,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5299,29 +5343,29 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5333,12 +5377,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5350,29 +5394,29 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5428,12 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5401,12 +5445,12 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5418,12 +5462,12 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5435,29 +5479,29 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5469,12 +5513,12 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5486,12 +5530,12 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5547,12 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5520,27 +5564,44 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr" s="2">
+      <c r="B94" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr" s="2">
+      <c r="C94" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">95 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 93 ครั้ง</t>
+          <t xml:space="preserve">96 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 94 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -3997,6 +3997,37 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97">
+        <v>97</v>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel ด้วย เป็นชีตที่ 9</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- ผังในคู่มือวาดด้วยอักขระเส้นในบล็อกโค้ด ซึ่งใช้ฟอนต์ความกว้างเท่ากัน
+จึงตรงสวย แต่ Excel ใช้ฟอนต์ความกว้างไม่เท่ากัน
+ยกมาวางตรง ๆ เส้นจะเบี้ยวทั้งผังจนอ่านไม่ออก
+- จึงเปลี่ยนวิธีเล่าเรื่องให้เข้ากับสื่อ แทนที่จะยัดรูปวาดลงตาราง
+ให้หนึ่งแถวเป็นหนึ่งขั้น แล้วเพิ่มคอลัมน์ที่รูปวาดทำไม่ได้:
+"ได้อะไรส่งต่อให้ขั้นถัดไป"  ทำให้เห็นว่าทำไมต้องเรียงแบบนี้
+"ถ้าข้ามหรือทำผิดลำดับ"      บอกผลของการทำผิดลำดับตรง ๆ
+ลูกศรในรูปวาดบอกได้แค่ว่า "ไปไหนต่อ" แต่ตารางบอกได้ว่า "ส่งอะไรไป"
+ซึ่งเป็นคำตอบของคำถามว่าทำไมลำดับถึงสลับไม่ได้
+- ห้าผัง 29 แถว: ระบบประกอบด้วยอะไร · ลำดับการติดตั้ง ·
+ค่าสองตัวไปไหนบ้าง · ตั้งค่าในโปรแกรม (แยกสี่สาย) ·
+ตรวจรับก่อนเปิดใช้จริง
+- ชีตที่ 1 เพิ่มบรรทัดชี้ไปชีตนี้ และคู่มือเพิ่มกล่องชี้กลับมาที่ไฟล์ Excel
+ทั้งสองไฟล์จึงหากันเจอ ไม่ว่าจะเปิดไฟล์ไหนก่อน
+- ชุดทดสอบไฟล์ Excel เพิ่มการตรวจว่ามีครบ 9 ชีต และชีตผังมีเนื้อหาจริง
+ตรวจเพิ่มด้วยการคลายไฟล์ zip อ่าน sheet9.xml ตรง ๆ ว่ามี 30 แถว
+(หัวตาราง 1 + เนื้อหา 29) และมีข้อความสำคัญครบ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4034,12 +4065,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">589134d</t>
+          <t xml:space="preserve">c00cbf1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4082,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0a6a56</t>
+          <t xml:space="preserve">589134d</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
+          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
         </is>
       </c>
     </row>
@@ -4068,12 +4099,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8b137dc</t>
+          <t xml:space="preserve">c0a6a56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
+          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
         </is>
       </c>
     </row>
@@ -4085,12 +4116,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -4102,29 +4133,29 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4167,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4184,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -4170,12 +4201,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4218,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4204,29 +4235,29 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4238,12 +4269,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4286,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4272,29 +4303,29 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4337,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4354,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4371,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4388,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4405,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4391,29 +4422,29 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4456,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4442,12 +4473,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4459,12 +4490,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4476,12 +4507,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4524,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4541,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4527,12 +4558,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4575,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4561,12 +4592,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4609,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4626,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4643,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4629,12 +4660,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4677,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4694,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4680,12 +4711,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4728,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4745,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4731,12 +4762,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4748,29 +4779,29 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4782,12 +4813,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4799,12 +4830,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4816,12 +4847,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4833,12 +4864,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4850,29 +4881,29 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4884,12 +4915,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4901,12 +4932,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4918,12 +4949,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4966,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4983,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -4969,12 +5000,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4986,12 +5017,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -5003,12 +5034,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5051,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -5037,12 +5068,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5085,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5102,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -5088,12 +5119,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -5105,12 +5136,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -5122,12 +5153,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -5139,12 +5170,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -5156,12 +5187,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -5173,29 +5204,29 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5238,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5224,12 +5255,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5241,12 +5272,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5258,12 +5289,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5306,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5292,12 +5323,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5340,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5326,12 +5357,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5343,12 +5374,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5360,29 +5391,29 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5425,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5411,29 +5442,29 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5445,12 +5476,12 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5493,12 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5510,12 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5496,29 +5527,29 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5561,12 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5547,12 +5578,12 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5595,12 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5581,27 +5612,44 @@
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr" s="2">
+      <c r="B95" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr" s="2">
+      <c r="C95" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">96 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 94 ครั้ง</t>
+          <t xml:space="preserve">97 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 95 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -291,7 +291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -782,7 +782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4028,12 +4028,54 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98">
+        <v>98</v>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผังแบบรูปในไฟล์ Excel — เพิ่มความสามารถวาดรูปให้ตัวเขียน xlsx</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- รอบก่อนใส่ผังเป็นตาราง (ชีต 9) ซึ่งค้นหาและกรองได้
+แต่ยังไม่เห็นความสัมพันธ์ทั้งผังในสายตาเดียว
+- เพิ่มชีต 10 เป็นผังแบบรูป วาดด้วยรูปทรงของ Excel เอง
+60 รูปทรง: กล่อง 29 ใบ ลูกศร 24 อัน หัวเรื่อง 5 ป้าย และหมายเหตุ
+จัดเป็นสามคอลัมน์ แยกสีตามสาย จึงแยกผังออกจากกันได้ด้วยสายตา
+ทำไมเป็นรูปทรง ไม่ใช่ภาพ bitmap
+- ข้อความไทยในรูปทรงถูกวาดด้วยฟอนต์ของเครื่อง จึงคมทุกระดับการซูม
+ถ้าเป็น bitmap ต้องมีตัวเรนเดอร์ฟอนต์ไทยของตัวเอง
+ซึ่งใหญ่กว่าทั้งระบบรวมกัน และผิดข้อกำหนดที่ไม่เพิ่ม dependency
+- คนที่เปิดไฟล์ลากแก้กล่องและข้อความต่อเองได้ ไม่ต้องกลับมาขอให้สร้างใหม่
+- พิมพ์ออกมาคมตามความละเอียดเครื่องพิมพ์ ไม่ใช่ตามความละเอียดของภาพ
+สิ่งที่เพิ่มใน lib/xlsx.js
+- drawingXML() แปลงรายการรูปทรงเป็นไฟล์รูปวาดของชีต
+รองรับสามชนิด: box (กล่องมุมมน) · arrow (ลูกศรลง/ขวา) · label (ข้อความล้วน)
+- วางด้วยพิกัดสัมบูรณ์ (absoluteAnchor) ไม่ผูกกับเซลล์
+เพราะผูกกับเซลล์แล้วความกว้างคอลัมน์ที่ต่างกันจะทำให้ผังบิดทั้งผัง
+- เพิ่มธง noGrid ปิดเส้นตารางของชีต ให้ดูเป็นผืนผ้าใบ ไม่ใช่ตารางที่มีรูปแปะ
+- สามจุดที่พลาดแล้ว Excel เปิดไฟล์ไม่ได้ ต้องกดซ่อมก่อน จึงเขียนคอมเมนต์
+กำกับไว้ทุกจุดและมีตัวทดสอบเฝ้า:
+แท็ก drawing ต้องอยู่ท้ายสุดของ worksheet ตามลำดับที่ schema กำหนด
+worksheet ต้องประกาศ namespace r เมื่อมี drawing
+ข้อความหลายบรรทัดต้องแตกเป็นหลายย่อหน้า ใส่ตัวขึ้นบรรทัดดิบไม่ได้
+- ชีตที่ไม่ได้ขอรูป ต้องไม่มีไฟล์รูปติดมาเลย มีตัวทดสอบเฝ้าข้อนี้
+เพราะรายงานทุกตัวของระบบใช้ตัวเขียนตัวนี้ ส่วนเกินหลุดเข้าไปแล้ว
+จะติดไปกับไฟล์ที่ส่งออกทุกไฟล์
+- ทดสอบเพิ่ม 16 ข้อในชุดสมุดงาน และ 9 ข้อในชุดไฟล์เช็คลิสต์
+รวมถึงแกะไฟล์ zip อ่าน drawing10.xml ตรง ๆ ว่ามีรูปทรงครบ
+มีข้อความไทยอยู่จริง และโครงของแพ็กเกจครบทุกส่วน</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -4065,12 +4107,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c00cbf1</t>
+          <t xml:space="preserve">2aa88f3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
+          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4124,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">589134d</t>
+          <t xml:space="preserve">c00cbf1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4141,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0a6a56</t>
+          <t xml:space="preserve">589134d</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
+          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
         </is>
       </c>
     </row>
@@ -4116,12 +4158,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8b137dc</t>
+          <t xml:space="preserve">c0a6a56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
+          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
         </is>
       </c>
     </row>
@@ -4133,12 +4175,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -4150,29 +4192,29 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4226,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -4201,12 +4243,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -4218,12 +4260,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4277,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4252,29 +4294,29 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4286,12 +4328,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4303,12 +4345,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4320,29 +4362,29 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4396,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4413,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4388,12 +4430,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4405,12 +4447,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4422,12 +4464,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4439,29 +4481,29 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4515,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4532,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4507,12 +4549,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4524,12 +4566,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4583,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4600,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4575,12 +4617,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4634,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4651,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4668,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4643,12 +4685,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4702,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4677,12 +4719,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4736,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4753,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4770,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4745,12 +4787,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4804,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4779,12 +4821,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4796,29 +4838,29 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4830,12 +4872,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4847,12 +4889,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4906,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4881,12 +4923,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4898,29 +4940,29 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4932,12 +4974,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4991,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -4966,12 +5008,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -4983,12 +5025,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -5000,12 +5042,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5059,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -5034,12 +5076,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5093,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5110,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5127,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5144,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -5119,12 +5161,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -5136,12 +5178,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -5153,12 +5195,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5212,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -5187,12 +5229,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -5204,12 +5246,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -5221,29 +5263,29 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5255,12 +5297,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5314,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5331,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5306,12 +5348,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5323,12 +5365,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5340,12 +5382,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5357,12 +5399,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5374,12 +5416,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5433,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5408,29 +5450,29 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5442,12 +5484,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5459,29 +5501,29 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5535,12 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5552,12 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5569,12 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5544,29 +5586,29 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5578,12 +5620,12 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5595,12 +5637,12 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5654,12 @@
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5629,27 +5671,44 @@
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr" s="2">
+      <c r="B96" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr" s="2">
+      <c r="C96" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -5660,7 +5719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -7101,7 +7160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -7921,7 +7980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="86" customWidth="1"/>
@@ -8513,7 +8572,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>253</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40">
@@ -8551,7 +8610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -8972,7 +9031,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">97 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 95 ครั้ง</t>
+          <t xml:space="preserve">98 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 96 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -4070,6 +4070,45 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99">
+        <v>99</v>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผังแบบรูปใส่รายละเอียดให้ครบ ทำตามได้เลยโดยไม่ต้องเปิดตารางอีกที</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- รอบก่อนกล่องในผังมีแต่ชื่อขั้น ซึ่งบอกได้แค่ลำดับ
+คนอ่านต้องไปเปิดตาราง (ชีต 9) อีกทีอยู่ดี
+จึงเสียประโยชน์ของการเป็นรูปไปทั้งหมด
+- กล่องหนึ่งใบตอนนี้มีสามบรรทัด:
+บรรทัดที่ 1  ชื่อขั้น (ตัวหนา)
+บรรทัดที่ 2  ทำอะไร ที่ไหน
+บรรทัดที่ 3  ได้อะไรออกมา หรือข้อที่พลาดบ่อย
+ข้อที่พลาดบ่อยเป็นตัวหนาสีแดง จึงเห็นทันทีว่าบรรทัดไหนคือคำเตือน
+ไม่ต้องอ่านทั้งกล่องก่อนถึงจะรู้ · มี 16 บรรทัดเตือนทั่วผัง
+- เพิ่มแถบเตือนใหญ่ที่หัวผัง ย้ำสองข้อที่พลาดบ่อยที่สุด
+(Supabase ต้องมาก่อน Vercel · ใส่ค่าแล้วต้อง Redeploy)
+และเพิ่มคำอธิบายสีท้ายผัง บอกว่าสีไหนคือสายไหน
+- ขยายกล่องจาก 340x52 เป็น 430x92 และเพิ่มคำโปรยใต้หัวเรื่องของแต่ละผัง
+รวม 65 รูปทรง 129 ย่อหน้า (เดิม 60 รูปทรง ข้อความบรรทัดเดียว)
+สิ่งที่เพิ่มใน lib/xlsx.js
+- รูปทรงรับข้อความได้สองแบบ: text (ก้อนเดียว ทุกบรรทัดหน้าตาเหมือนกัน)
+และ lines (ระบุตัวหนา ขนาด สี แยกรายบรรทัด)
+มีแบบที่สองเพราะถ้าทุกบรรทัดหน้าตาเหมือนกัน
+คนอ่านจะแยกไม่ออกว่าบรรทัดไหนคือชื่อขั้น บรรทัดไหนคือรายละเอียด
+- ของเดิมที่ส่ง text มายังทำงานเหมือนเดิมทุกอย่าง มีตัวทดสอบเฝ้าไว้
+- ทดสอบเพิ่ม: ชุดสมุดงานตรวจการจัดรูปแบบรายบรรทัด (ย่อหน้าถูกแตกตามที่สั่ง ·
+ตัวหนาเฉพาะบรรทัดที่ระบุ · สีและขนาดต่างกันได้ในกล่องเดียว)
+ชุดไฟล์เช็คลิสต์ตรวจว่าผังมีรายละเอียดพอจริง (อย่างน้อย 100 ย่อหน้า ·
+มีบรรทัดสีเตือนอย่างน้อย 10 · มีคำอธิบายสี · และข้อเตือนสำคัญสี่เรื่อง
+ต้องอยู่ในผังด้วย ไม่ใช่อยู่แต่ในตาราง)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4107,12 +4146,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2aa88f3</t>
+          <t xml:space="preserve">ff03eab</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
+          <t xml:space="preserve">เพิ่มผังแบบรูปในไฟล์ Excel เป็นชีตที่ 10</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4163,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c00cbf1</t>
+          <t xml:space="preserve">2aa88f3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
+          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4180,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">589134d</t>
+          <t xml:space="preserve">c00cbf1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4197,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0a6a56</t>
+          <t xml:space="preserve">589134d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
+          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
         </is>
       </c>
     </row>
@@ -4175,12 +4214,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8b137dc</t>
+          <t xml:space="preserve">c0a6a56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
+          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
         </is>
       </c>
     </row>
@@ -4192,12 +4231,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -4209,29 +4248,29 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4282,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4299,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -4277,12 +4316,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4333,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4311,29 +4350,29 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4345,12 +4384,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4401,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4379,29 +4418,29 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4452,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4430,12 +4469,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4447,12 +4486,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4464,12 +4503,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4520,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4498,29 +4537,29 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4532,12 +4571,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4549,12 +4588,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4566,12 +4605,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4583,12 +4622,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4639,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4617,12 +4656,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4634,12 +4673,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4651,12 +4690,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4668,12 +4707,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4685,12 +4724,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4702,12 +4741,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4758,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4775,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4792,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4809,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4787,12 +4826,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4804,12 +4843,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4821,12 +4860,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4877,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4855,29 +4894,29 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4928,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4906,12 +4945,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4962,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4940,12 +4979,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -4957,29 +4996,29 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -4991,12 +5030,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -5008,12 +5047,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -5025,12 +5064,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5081,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5098,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -5076,12 +5115,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -5093,12 +5132,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -5110,12 +5149,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -5127,12 +5166,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5183,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5200,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5217,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5234,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -5212,12 +5251,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -5229,12 +5268,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5285,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -5263,12 +5302,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -5280,29 +5319,29 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5314,12 +5353,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5331,12 +5370,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5348,12 +5387,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5365,12 +5404,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5382,12 +5421,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5399,12 +5438,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5416,12 +5455,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5433,12 +5472,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5450,12 +5489,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5467,29 +5506,29 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5540,12 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5518,29 +5557,29 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5552,12 +5591,12 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5569,12 +5608,12 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5586,12 +5625,12 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5603,29 +5642,29 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5676,12 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5693,12 @@
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5671,12 +5710,12 @@
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5688,27 +5727,44 @@
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr" s="2">
+      <c r="B97" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr" s="2">
+      <c r="C97" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -8572,7 +8628,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>385</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40">

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">98 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 96 ครั้ง</t>
+          <t xml:space="preserve">99 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 97 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -4109,6 +4109,46 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผังแบบรูปอธิบายตัวเองได้ และมีคำสั่งอยู่ในผัง</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- บทเรียนจากรอบก่อน: ผังที่สวยแต่ไม่มีคำอธิบายวิธีอ่าน
+คนเปิดมาแล้วยังงง เพราะไม่รู้ว่าจะเริ่มอ่านตรงไหน
+แต่ละบรรทัดในกล่องคืออะไร และสีมีความหมายหรือไม่
+รูปไม่ได้อธิบายตัวเองเสมอไป ต้องมีคำอธิบายอยู่ในหน้าเดียวกัน
+- เพิ่มสามแผงบนหัวผัง:
+"วิธีอ่านผังนี้"      บอกว่าหนึ่งกล่องคืออะไร และสี่บรรทัดในกล่อง
+แต่ละบรรทัดคืออะไร เขียนด้วยสีเดียวกับของจริง
+คนอ่านจึงเทียบกับกล่องจริงได้ทันที
+"อ่านผังไหนก่อน"     บอกลำดับ A -&gt; B (เปิด C ไว้ข้าง ๆ) -&gt; D -&gt; E
+และบอกว่าผังไหนแค่อ่าน ผังไหนต้องลงมือ
+แถบเตือนสองข้อ       ข้อที่คนพลาดบ่อยที่สุด
+- เพิ่มบรรทัดที่ 3 ในกล่อง เป็นคำสั่งที่ต้องพิมพ์ ใช้ฟอนต์ความกว้างเท่ากัน
+และสีม่วง จะได้รู้ว่าบรรทัดนี้ต้องพิมพ์ตามตัวอักษร ไม่ใช่ข้อความอธิบาย
+ที่เขียนใหม่ด้วยคำของตัวเองได้ · ขั้นที่ทำบนเว็บจะไม่มีบรรทัดนี้
+และเขียนกำกับไว้ในชื่อขั้นว่า (ทำบนเว็บ)
+- เพิ่มแผง "คำสั่งที่ต้องใช้" ท้ายผัง แบ่งสามกลุ่ม 12 คำสั่ง
+ตอนติดตั้ง · ตอนทำงานประจำ · ตอนส่งขึ้นเว็บจริง
+แต่ละคำสั่งมีคำอธิบายสั้น ๆ ใต้บรรทัด
+- เพิ่มขั้น "3. ตรวจก่อนไปต่อ" ในผัง B ให้สั่ง npm run setup
+ตั้งแต่ตอนทำฐานข้อมูลเสร็จ ดีกว่าไปรู้ตอนขึ้น Vercel แล้วล็อกอินไม่ได้
+- รวม 71 รูปทรง 177 ย่อหน้า มีบรรทัดคำสั่ง 16 บรรทัด
+และบรรทัดเตือน 16 บรรทัด (เดิม 65 รูปทรง 129 ย่อหน้า ไม่มีคำสั่งเลย)
+- ตัววาดรับ font รายบรรทัดได้แล้ว ใช้กับบรรทัดคำสั่ง
+บรรทัดที่ไม่ระบุยังใช้ Tahoma เหมือนเดิมทุกที่
+- ทดสอบเพิ่ม: ผังต้องมีแผงวิธีอ่าน · แผงลำดับการอ่าน · คำอธิบายสี ·
+บรรทัดคำสั่งอย่างน้อย 12 บรรทัด · และคำสั่งหลักหกตัวต้องอยู่ในผังจริง</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4146,12 +4186,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ff03eab</t>
+          <t xml:space="preserve">3fe5356</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผังแบบรูปในไฟล์ Excel เป็นชีตที่ 10</t>
+          <t xml:space="preserve">ผังแบบรูปใส่รายละเอียดให้ครบ ทำตามได้เลยโดยไม่ต้องเปิดตารางอีกที</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4203,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2aa88f3</t>
+          <t xml:space="preserve">ff03eab</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
+          <t xml:space="preserve">เพิ่มผังแบบรูปในไฟล์ Excel เป็นชีตที่ 10</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4220,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c00cbf1</t>
+          <t xml:space="preserve">2aa88f3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
+          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4237,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">589134d</t>
+          <t xml:space="preserve">c00cbf1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4254,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0a6a56</t>
+          <t xml:space="preserve">589134d</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
+          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
         </is>
       </c>
     </row>
@@ -4231,12 +4271,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8b137dc</t>
+          <t xml:space="preserve">c0a6a56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
+          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4288,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -4265,29 +4305,29 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -4299,12 +4339,12 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4356,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -4333,12 +4373,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4390,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4367,29 +4407,29 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4441,12 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4458,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4435,29 +4475,29 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4509,12 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4526,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4503,12 +4543,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4560,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4537,12 +4577,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4554,29 +4594,29 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4628,12 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4645,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4662,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4639,12 +4679,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4696,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4673,12 +4713,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4730,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4707,12 +4747,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4764,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4781,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4758,12 +4798,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4815,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4792,12 +4832,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4849,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4866,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4883,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4860,12 +4900,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4877,12 +4917,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4894,12 +4934,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4911,29 +4951,29 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4985,12 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -4962,12 +5002,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -4979,12 +5019,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -4996,12 +5036,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -5013,29 +5053,29 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5087,12 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -5064,12 +5104,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5121,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5138,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -5115,12 +5155,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -5132,12 +5172,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5189,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5206,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5223,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -5200,12 +5240,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -5217,12 +5257,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5274,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -5251,12 +5291,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5308,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5325,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -5302,12 +5342,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5359,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -5336,29 +5376,29 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5410,12 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5387,12 +5427,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5444,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5461,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5438,12 +5478,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5455,12 +5495,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5512,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5529,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5546,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5523,29 +5563,29 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5557,12 +5597,12 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5574,29 +5614,29 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5648,12 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5625,12 +5665,12 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5682,12 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5659,29 +5699,29 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5733,12 @@
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5710,12 +5750,12 @@
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5767,12 @@
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5744,27 +5784,44 @@
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr" s="2">
+      <c r="B98" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr" s="2">
+      <c r="C98" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
@@ -8628,7 +8685,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="40">

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 97 ครั้ง</t>
+          <t xml:space="preserve">100 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 98 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -4149,6 +4149,47 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101">
+        <v>101</v>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผังแบบรูปสรุปว่า GitHub / Vercel / Supabase ไว้ทำอะไร</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- สามบริการนี้ชื่อคล้ายกันหมดในสายตาคนที่เพิ่งเริ่ม
+และทำงานคนละอย่างกันสิ้นเชิง ถ้าไม่รู้ว่าอันไหนทำอะไร
+เวลามีปัญหาจะไม่รู้ว่าต้องไปแก้ที่ไหน เช่น เว็บเปิดไม่ขึ้น
+แต่ไปนั่งแก้ฐานข้อมูล หรือข้อมูลหายแต่ไปกด redeploy
+- เพิ่มแผงสรุปสามแผง เรียงตามลำดับที่ของไหลจริง
+โค้ดอยู่ที่ GitHub -&gt; รันที่ Vercel -&gt; ข้อมูลอยู่ที่ Supabase
+ซึ่งเป็นประโยคเดียวที่สรุปทั้งหมดได้ จึงเอาไปเป็นหัวเรื่องของแผง
+- ทั้งสามแผงตอบคำถามชุดเดียวกัน จะได้เทียบกันได้ตรง ๆ
+ไม่ใช่ต่างแผงต่างเล่าคนละมุมจนเทียบไม่ได้:
+เก็บอะไรไว้ที่นี่
+ทำอะไรให้เรา (สามข้อ)
+ลบทิ้งแล้วเป็นยังไง
+ค่าใช้จ่าย
+- ข้อที่ตั้งใจให้เห็นชัดที่สุดคือความต่างของ "ลบทิ้งแล้วเป็นยังไง":
+GitHub ลบแล้วโค้ดยังอยู่ในเครื่อง แต่ Vercel deploy ต่อไม่ได้
+Vercel ลบแล้วเว็บเปิดไม่ได้ แต่ข้อมูลไม่หาย สร้างใหม่ต่อกลับได้
+Supabase ลบแล้วข้อมูลหายทั้งหมดทันที (เป็นตัวหนาสีแดง)
+สองแผงแรกจึงเขียนกำกับไว้ด้วยว่าไม่มีข้อมูลของกิจการอยู่เลย
+เพื่อให้เห็นว่าความเสี่ยงอยู่ที่เดียว ไม่ได้กระจายสามที่
+- จำนวนตารางในแผง Supabase อ่านจาก schema.sql ตอนสร้างไฟล์
+จึงไม่มีวันบอกจำนวนผิดเมื่อเพิ่มตารางใหม่
+- ผัง A เปลี่ยนชื่อเป็น "ของไหลไปทางไหน" และชี้ไปที่แผงด้านบน
+แทนที่จะเล่ารายละเอียดซ้ำอีกรอบในกล่อง
+- รวม 75 รูปทรง 220 ย่อหน้า (เดิม 71 รูปทรง 177 ย่อหน้า)
+- ทดสอบเพิ่ม: ต้องมีแผงของทั้งสามบริการ · ทั้งสามแผงต้องมีหัวข้อ
+ชุดเดียวกันครบทั้งสามแผง · แผง Supabase ต้องเตือนเรื่องข้อมูลหาย ·
+และสองแผงแรกต้องบอกว่าไม่มีข้อมูลของกิจการอยู่</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4186,12 +4227,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3fe5356</t>
+          <t xml:space="preserve">cdd930b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผังแบบรูปใส่รายละเอียดให้ครบ ทำตามได้เลยโดยไม่ต้องเปิดตารางอีกที</t>
+          <t xml:space="preserve">ผังแบบรูปอธิบายตัวเองได้ และมีคำสั่งอยู่ในผัง</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4244,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ff03eab</t>
+          <t xml:space="preserve">3fe5356</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผังแบบรูปในไฟล์ Excel เป็นชีตที่ 10</t>
+          <t xml:space="preserve">ผังแบบรูปใส่รายละเอียดให้ครบ ทำตามได้เลยโดยไม่ต้องเปิดตารางอีกที</t>
         </is>
       </c>
     </row>
@@ -4220,12 +4261,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2aa88f3</t>
+          <t xml:space="preserve">ff03eab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
+          <t xml:space="preserve">เพิ่มผังแบบรูปในไฟล์ Excel เป็นชีตที่ 10</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4278,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c00cbf1</t>
+          <t xml:space="preserve">2aa88f3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
+          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4295,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">589134d</t>
+          <t xml:space="preserve">c00cbf1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4312,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0a6a56</t>
+          <t xml:space="preserve">589134d</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
+          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4329,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8b137dc</t>
+          <t xml:space="preserve">c0a6a56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
+          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4346,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -4322,29 +4363,29 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -4356,12 +4397,12 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4414,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4431,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4407,12 +4448,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4424,29 +4465,29 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4499,12 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4516,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4492,29 +4533,29 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4526,12 +4567,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4543,12 +4584,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4560,12 +4601,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4577,12 +4618,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4635,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4611,29 +4652,29 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4645,12 +4686,12 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4703,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4720,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4696,12 +4737,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4754,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4771,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4747,12 +4788,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4764,12 +4805,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4781,12 +4822,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4798,12 +4839,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4815,12 +4856,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4832,12 +4873,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4849,12 +4890,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4866,12 +4907,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4883,12 +4924,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4900,12 +4941,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4917,12 +4958,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4975,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4992,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -4968,29 +5009,29 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -5002,12 +5043,12 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -5019,12 +5060,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5077,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5094,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -5070,29 +5111,29 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -5104,12 +5145,12 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -5121,12 +5162,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -5138,12 +5179,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -5155,12 +5196,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5213,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5230,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -5206,12 +5247,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -5223,12 +5264,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -5240,12 +5281,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -5257,12 +5298,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5315,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -5291,12 +5332,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -5308,12 +5349,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5366,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -5342,12 +5383,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -5359,12 +5400,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5417,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -5393,29 +5434,29 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5468,12 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5485,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5461,12 +5502,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5519,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5536,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5512,12 +5553,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5570,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5546,12 +5587,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5604,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5580,29 +5621,29 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5614,12 +5655,12 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5631,29 +5672,29 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5665,12 +5706,12 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5723,12 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5740,12 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5716,29 +5757,29 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5791,12 @@
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5767,12 +5808,12 @@
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5784,12 +5825,12 @@
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5801,27 +5842,44 @@
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr" s="2">
+      <c r="B99" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr" s="2">
+      <c r="C99" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>

--- a/Docs/ProjectProcess.xlsx
+++ b/Docs/ProjectProcess.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">100 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 98 ครั้ง</t>
+          <t xml:space="preserve">101 รอบ (ชีต ขั้นตอนการสร้างจริง) · ส่งขึ้น git แล้ว 99 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -4190,6 +4190,46 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102">
+        <v>102</v>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผังแบบรูปบอกเส้นทางการกดในหน้าเว็บของแต่ละบริการ</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">- ผังบอกได้ว่า "ต้องไปทำที่ Supabase" แต่พอเปิดเว็บจริงขึ้นมา
+หน้าจอมีเมนูเป็นสิบ แล้วไม่รู้ว่าอันไหน · เมนูของบริการพวกนี้
+ยังเปลี่ยนชื่อและย้ายที่เป็นระยะด้วย คนที่ทำครั้งแรกจึงเสียเวลา
+ไปกับการหาเมนู มากกว่าการทำงานจริง
+- เพิ่มแผง "หน้าเว็บที่ต้องเข้าไปทำ" สามแผง 14 เส้นทาง
+เขียนแบบ เมนู &gt; เมนูย่อย &gt; ปุ่ม และบอกว่าในหน้านั้นต้องกรอกอะไร
+เรียงตามลำดับที่ต้องทำจริง ไม่ได้เรียงตามลำดับเมนูบนหน้าจอ
+GitHub    3 เส้นทาง (สร้าง repo · ตรวจไฟล์ที่ขึ้นไป · เชิญเพื่อนร่วมงาน)
+Vercel    4 เส้นทาง (สร้างโปรเจกต์ · ใส่ค่า · Redeploy · โดเมน)
+Supabase  7 เส้นทาง (สร้างโปรเจกต์ · รัน SQL · สร้างผู้ใช้ ·
+ตั้งค่าอีเมล · คัดลอกกุญแจ · ดูสถานะ · ดูข้อมูลจริง)
+- แต่ละเส้นทางมีสามบรรทัด: เส้นทางเมนู · ต้องกรอกอะไร ·
+ผลที่ได้หรือข้อที่พลาดบ่อย (ตัวหนาสีแดง)
+ลงรายละเอียดถึงระดับชื่อช่องและชื่อปุ่มจริง เช่น
+Region ต้องเลือก Southeast Asia (Singapore) ·
+ตอนสร้างผู้ใช้ต้องติ๊ก Auto Confirm User ·
+ตอน Redeploy ไม่ต้องติ๊ก Use existing Build Cache
+- ที่อยู่เว็บของแต่ละบริการใช้ฟอนต์ความกว้างเท่ากันเหมือนบรรทัดคำสั่ง
+เพราะเป็นสิ่งที่ต้องพิมพ์ตามตัวอักษรเหมือนกัน
+- รวม 79 รูปทรง 283 ย่อหน้า มีบรรทัดเตือน 25 บรรทัด
+(เดิม 75 รูปทรง 220 ย่อหน้า เตือน 16 บรรทัด)
+- ทดสอบเพิ่ม 17 ข้อ: ต้องมีแผงนี้ · ต้องบอกที่อยู่เว็บทั้งสามบริการ ·
+เส้นทางที่ขาดไม่ได้แปดเส้นทางต้องมีครบ · และรายละเอียดในหน้า
+ห้าอย่างที่ลืมแล้วติดตั้งไม่ผ่านต้องถูกเขียนไว้
+ตัวทดสอบแปลง &amp;gt; กลับเป็นเครื่องหมายมากกว่าก่อนเทียบ
+เพราะไฟล์เก็บไว้ในรูป XML ที่ถูก escape แล้ว</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -4227,12 +4267,12 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cdd930b</t>
+          <t xml:space="preserve">bd35305</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผังแบบรูปอธิบายตัวเองได้ และมีคำสั่งอยู่ในผัง</t>
+          <t xml:space="preserve">ผังแบบรูปสรุปว่า GitHub Vercel Supabase ไว้ทำอะไร</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4284,12 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3fe5356</t>
+          <t xml:space="preserve">cdd930b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผังแบบรูปใส่รายละเอียดให้ครบ ทำตามได้เลยโดยไม่ต้องเปิดตารางอีกที</t>
+          <t xml:space="preserve">ผังแบบรูปอธิบายตัวเองได้ และมีคำสั่งอยู่ในผัง</t>
         </is>
       </c>
     </row>
@@ -4261,12 +4301,12 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ff03eab</t>
+          <t xml:space="preserve">3fe5356</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผังแบบรูปในไฟล์ Excel เป็นชีตที่ 10</t>
+          <t xml:space="preserve">ผังแบบรูปใส่รายละเอียดให้ครบ ทำตามได้เลยโดยไม่ต้องเปิดตารางอีกที</t>
         </is>
       </c>
     </row>
@@ -4278,12 +4318,12 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2aa88f3</t>
+          <t xml:space="preserve">ff03eab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
+          <t xml:space="preserve">เพิ่มผังแบบรูปในไฟล์ Excel เป็นชีตที่ 10</t>
         </is>
       </c>
     </row>
@@ -4295,12 +4335,12 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c00cbf1</t>
+          <t xml:space="preserve">2aa88f3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
+          <t xml:space="preserve">ใส่ผังลำดับงานในไฟล์ Excel เป็นชีตที่ 9</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4352,12 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">589134d</t>
+          <t xml:space="preserve">c00cbf1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มผังลำดับงานในคู่มือติดตั้ง ให้เห็นภาพในภาพเดียว</t>
         </is>
       </c>
     </row>
@@ -4329,12 +4369,12 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0a6a56</t>
+          <t xml:space="preserve">589134d</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
+          <t xml:space="preserve">คู่มือมีหัวข้อตัวช่วยติดตั้งของตัวเอง</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4386,12 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8b137dc</t>
+          <t xml:space="preserve">c0a6a56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
+          <t xml:space="preserve">เพิ่มตัวช่วยติดตั้ง สั่ง npm run setup แล้วมันบอกเองว่าเหลืออะไร</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4403,12 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e104477</t>
+          <t xml:space="preserve">8b137dc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
+          <t xml:space="preserve">เพิ่มคำสั่งที่ต้องใช้ และหัวข้อความปลอดภัย ในคู่มือและเช็คลิสต์</t>
         </is>
       </c>
     </row>
@@ -4380,29 +4420,29 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3428658</t>
+          <t xml:space="preserve">e104477</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
+          <t xml:space="preserve">เพิ่มเช็คลิสต์ติดตั้งเป็นไฟล์ Excel ติ๊กตามได้ว่าทำถึงขั้นไหน</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9bb450d</t>
+          <t xml:space="preserve">3428658</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
+          <t xml:space="preserve">เพิ่มคู่มือติดตั้งสำหรับเริ่มโครงการใหม่ตั้งแต่ศูนย์</t>
         </is>
       </c>
     </row>
@@ -4414,12 +4454,12 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b12657d</t>
+          <t xml:space="preserve">9bb450d</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
+          <t xml:space="preserve">เพิ่มเมนูงานผ่านไลน์ ดึงคำสั่งซื้อจากแชทมาทำเอกสาร และใบเสนอราคา</t>
         </is>
       </c>
     </row>
@@ -4431,12 +4471,12 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c0e2071</t>
+          <t xml:space="preserve">b12657d</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสรุปยอดคงเหลือรายคลัง และการเคลื่อนไหวเข้า-ออก</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4488,12 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b6a0b88</t>
+          <t xml:space="preserve">c0e2071</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
+          <t xml:space="preserve">หน้าข้อมูลสินค้าแสดงยอดคงเหลือแยกรายคลังและรายช่องเก็บ</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4505,12 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a13ec4</t>
+          <t xml:space="preserve">b6a0b88</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
+          <t xml:space="preserve">หน้าขายสินค้า (POS) เลือกลูกค้าจากทะเบียนได้ และตั้งลูกค้าเริ่มต้นได้</t>
         </is>
       </c>
     </row>
@@ -4482,29 +4522,29 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b79ba97</t>
+          <t xml:space="preserve">3a13ec4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
+          <t xml:space="preserve">แก้สิทธิ์ sequence ที่ทำให้บันทึกไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d8b73cd</t>
+          <t xml:space="preserve">b79ba97</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
+          <t xml:space="preserve">สิทธิการใช้งานแยกรายผู้ใช้ มีแอดมินเป็นคนกำหนด</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4556,12 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">897a049</t>
+          <t xml:space="preserve">d8b73cd</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">ตรวจทานหมวดการรับฟังลูกค้าทั้งหมวด และตรวจด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4573,12 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddd6cd3</t>
+          <t xml:space="preserve">897a049</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
+          <t xml:space="preserve">เพิ่มคู่มือการใช้งานหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
     </row>
@@ -4550,29 +4590,29 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e37f801</t>
+          <t xml:space="preserve">ddd6cd3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
+          <t xml:space="preserve">เพิ่มหมวดการรับฟังลูกค้า (SE-AM หมวด 3) เป็นหัวข้อใหญ่แยกของตัวเอง</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">959e70a</t>
+          <t xml:space="preserve">e37f801</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
+          <t xml:space="preserve">ปรับไฟล์โลโก้ต้นฉบับให้ใช้ได้จริง และให้ไอคอนทุกขนาดมาจากภาพเดียวกัน</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4624,12 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8a4c2</t>
+          <t xml:space="preserve">959e70a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
+          <t xml:space="preserve">โลโก้ใช้ไฟล์ภาพต้นฉบับ NewLogo.jpg แทนการวาดเลียนแบบ</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4641,12 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cd332e6</t>
+          <t xml:space="preserve">0f8a4c2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
+          <t xml:space="preserve">โลโก้เป็นตราเต็มแบบต้นฉบับ — ตัวอักษร OFAU พร้อมเปลวไฟและลูกศร</t>
         </is>
       </c>
     </row>
@@ -4618,12 +4658,12 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">76f058c</t>
+          <t xml:space="preserve">cd332e6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
+          <t xml:space="preserve">โลโก้ใช้พื้นสีขาวแทนพื้นเขียว ให้ลูกศรและเปลวไฟชัดทั้งคู่</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4675,12 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">42442b8</t>
+          <t xml:space="preserve">76f058c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
+          <t xml:space="preserve">เปลี่ยนตราสัญลักษณ์เป็นโลโก้ OFAU (เปลวไฟกับลูกศรพุ่งขึ้น)</t>
         </is>
       </c>
     </row>
@@ -4652,12 +4692,12 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27d5371</t>
+          <t xml:space="preserve">42442b8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
+          <t xml:space="preserve">เพิ่มหน้าจอวิธีการใช้งาน — Flow ของทุกหน้าจอและความเชื่อมโยง</t>
         </is>
       </c>
     </row>
@@ -4669,29 +4709,29 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddec640</t>
+          <t xml:space="preserve">27d5371</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
+          <t xml:space="preserve">ทะเบียนประเภทลูกค้า และเก็บประเภทไว้ในเอกสารที่เอาไปใช้</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-06</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39aba99</t>
+          <t xml:space="preserve">ddec640</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น One for All Ultra (OFAU) และเพิ่มงานลูกค้าสัมพันธ์ (CRM) เฟส 1</t>
         </is>
       </c>
     </row>
@@ -4703,12 +4743,12 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8db5b16</t>
+          <t xml:space="preserve">39aba99</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
+          <t xml:space="preserve">ทะเบียนกลุ่ม ยี่ห้อ ประเภทสินค้า และช่องกดเลือกที่หน้าข้อมูลสินค้า</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4760,12 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fa674e6</t>
+          <t xml:space="preserve">8db5b16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
+          <t xml:space="preserve">แก้บั๊กร้ายแรง: ชื่อซ้ำใน lib/api.js ทำให้ทั้งระบบ build ไม่ผ่าน</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4777,12 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">61992c4</t>
+          <t xml:space="preserve">fa674e6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
+          <t xml:space="preserve">กลุ่มเมนูที่หุบอยู่บอกว่าซ่อนกี่หน้าไว้</t>
         </is>
       </c>
     </row>
@@ -4754,12 +4794,12 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a860eb8</t>
+          <t xml:space="preserve">61992c4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
+          <t xml:space="preserve">บอกรุ่นของโปรแกรมที่หน้าจอ และเข้าถึงหน้าเป้าขาย/Quick View ได้ง่ายขึ้น</t>
         </is>
       </c>
     </row>
@@ -4771,12 +4811,12 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">39e6538</t>
+          <t xml:space="preserve">a860eb8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
+          <t xml:space="preserve">ออกแบบฟอร์มที่ใช้พิมพ์เองได้ และเอกสารกระบวนการสร้างเป็นไฟล์ Excel</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4828,12 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bcec88c</t>
+          <t xml:space="preserve">39e6538</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
+          <t xml:space="preserve">เป้าขาย พนักงานขาย มิติสินค้า Quick View และกราฟหลายแบบ</t>
         </is>
       </c>
     </row>
@@ -4805,12 +4845,12 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">449cccb</t>
+          <t xml:space="preserve">bcec88c</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
+          <t xml:space="preserve">แดชบอร์ดเลือกได้ว่าจะดูอะไร พร้อมจัดตำแหน่งให้เอง</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4862,12 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ef8bc74</t>
+          <t xml:space="preserve">449cccb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
+          <t xml:space="preserve">เพิ่มหน้าจอนำเข้าข้อมูลจาก Excel ใช้ได้หลายหน้าจอในที่เดียว</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4879,12 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b35c10a</t>
+          <t xml:space="preserve">ef8bc74</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
+          <t xml:space="preserve">เพิ่ม row_order ทุกตาราง และรองรับ MySQL/Access ในหน้าเชื่อมต่อ</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4896,12 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8332479</t>
+          <t xml:space="preserve">b35c10a</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเชื่อมต่อ SQL Server — เก็บค่าการเชื่อมต่อไว้ใช้ซ้ำ</t>
         </is>
       </c>
     </row>
@@ -4873,12 +4913,12 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9ae66e7</t>
+          <t xml:space="preserve">8332479</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
+          <t xml:space="preserve">ตรวจทั้งระบบอย่างละเอียด — แก้บั๊ก 5 จุด และเพิ่มการตรวจถาวรอีก 4 หมวด</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4930,12 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cddfec3</t>
+          <t xml:space="preserve">9ae66e7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
+          <t xml:space="preserve">หน้าดึงบิลอัตโนมัติ: บอกรูปแบบไฟล์ ดูข้อมูลก่อน และถามยืนยันก่อนอัพโหลด</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4947,12 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ba4d322</t>
+          <t xml:space="preserve">cddfec3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
+          <t xml:space="preserve">รายงานครบทุกหน้าจอที่บันทึกข้อมูล และค้นหาได้ทุกแท็บ</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4964,12 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ee55fb0</t>
+          <t xml:space="preserve">ba4d322</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
+          <t xml:space="preserve">เพิ่มหน้าจอเพิ่มผู้ใช้งาน — สร้างบัญชีด้วยอีเมล ไม่ต้องยืนยันอีเมล</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4981,12 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b274b08</t>
+          <t xml:space="preserve">ee55fb0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
+          <t xml:space="preserve">เพิ่มเมนูงานจัดส่ง: สถานีสแกน เวลาแต่ละขั้น ดึงบิลจาก Excel และเปลี่ยนรหัสผ่าน</t>
         </is>
       </c>
     </row>
@@ -4958,12 +4998,12 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">feaee18</t>
+          <t xml:space="preserve">b274b08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
+          <t xml:space="preserve">หน้านับสินค้ามือถือ: แสดงรายการทั้งใบพร้อมสถานะ และพิมพ์เป็นรายงานได้</t>
         </is>
       </c>
     </row>
@@ -4975,12 +5015,12 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">d0d4d3e</t>
+          <t xml:space="preserve">feaee18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
+          <t xml:space="preserve">แก้หน้าข้อมูลสินค้า, กราฟเลือกช่วงเวลา, แยกตรวจนับเป็น 2 หน้าจอ</t>
         </is>
       </c>
     </row>
@@ -4992,12 +5032,12 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">5690fb6</t>
+          <t xml:space="preserve">d0d4d3e</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
+          <t xml:space="preserve">เอกสารที่ทำไปแล้วทุกหน้า ค้นหาและเลื่อนดูได้ครบ</t>
         </is>
       </c>
     </row>
@@ -5009,12 +5049,12 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b857e42</t>
+          <t xml:space="preserve">5690fb6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
+          <t xml:space="preserve">เพิ่มหน้าจอสำรองข้อมูลและกู้คืน ใต้การจัดการระบบ</t>
         </is>
       </c>
     </row>
@@ -5026,29 +5066,29 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9889cd2</t>
+          <t xml:space="preserve">b857e42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
+          <t xml:space="preserve">ช่องเลือกทุกช่องพิมพ์ค้นหาได้ และส่งออกได้ทั้ง Excel CSV PDF</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2026-09-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">fc6f0f6</t>
+          <t xml:space="preserve">9889cd2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
+          <t xml:space="preserve">เพิ่มงานซื้อทั้งชุด ตรวจนับสินค้า และหน้าสร้างรายงานเอง</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5100,12 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7776b68</t>
+          <t xml:space="preserve">fc6f0f6</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
+          <t xml:space="preserve">แก้คอลัมน์ในกระดานสถานะที่เลื่อนไปทั้งตาราง</t>
         </is>
       </c>
     </row>
@@ -5077,12 +5117,12 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">b56614f</t>
+          <t xml:space="preserve">7776b68</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
+          <t xml:space="preserve">เพิ่มคอลัมน์ระยะทาง (กม.) ก่อนคอลัมน์สถานะ</t>
         </is>
       </c>
     </row>
@@ -5094,12 +5134,12 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f040f5a</t>
+          <t xml:space="preserve">b56614f</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
+          <t xml:space="preserve">ค้นหาที่หน้าสถานะการจัดส่ง เจอส่วนไหนก็แสดงทุกใบที่ใกล้เคียง</t>
         </is>
       </c>
     </row>
@@ -5111,12 +5151,12 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3d2b94f</t>
+          <t xml:space="preserve">f040f5a</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
+          <t xml:space="preserve">กระดานสถานะอัพเดทเองทุก 10 นาที และแก้บั๊กวันที่เป็น UTC</t>
         </is>
       </c>
     </row>
@@ -5128,29 +5168,29 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f25c94b</t>
+          <t xml:space="preserve">3d2b94f</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
+          <t xml:space="preserve">แยกหน้าที่: จัดส่งสินค้าเป็นที่ทำงาน สถานะการจัดส่งเป็นกระดาน</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-04</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ab1a743</t>
+          <t xml:space="preserve">f25c94b</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
+          <t xml:space="preserve">เพิ่มหน้ากำหนดสิทธิการใช้งาน และหน้าสถานะการจัดส่ง</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5202,12 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ddc7c65</t>
+          <t xml:space="preserve">ab1a743</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
+          <t xml:space="preserve">เพิ่มหน้าขายสินค้าและบริการ จัดส่งสินค้า และข้อมูลกิจการ</t>
         </is>
       </c>
     </row>
@@ -5179,12 +5219,12 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7f5a61d</t>
+          <t xml:space="preserve">ddc7c65</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
+          <t xml:space="preserve">ปักหมุดตำแหน่งคลังเองได้ที่หน้าสินค้าตามจังหวัด</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5236,12 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">e03f7dc</t>
+          <t xml:space="preserve">7f5a61d</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
+          <t xml:space="preserve">ที่อยู่ลูกค้าเลือกจากเขตปกครองจริง รหัสไปรษณีย์ตรงเสมอ</t>
         </is>
       </c>
     </row>
@@ -5213,12 +5253,12 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">026a54e</t>
+          <t xml:space="preserve">e03f7dc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
+          <t xml:space="preserve">เพิ่มหน้าลูกค้า กลุ่มเอกสาร กำหนดคลัง/ที่เก็บ และเมนูหุบเป็นกลุ่มได้</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5270,12 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f55e227</t>
+          <t xml:space="preserve">026a54e</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
+          <t xml:space="preserve">แถบผู้ใช้ท้ายเมนู หุบ/ขยายได้</t>
         </is>
       </c>
     </row>
@@ -5247,12 +5287,12 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a7f7750</t>
+          <t xml:space="preserve">f55e227</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
+          <t xml:space="preserve">กราฟสรุปเลือกดูตามชื่อรายงานได้</t>
         </is>
       </c>
     </row>
@@ -5264,12 +5304,12 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a1af5d</t>
+          <t xml:space="preserve">a7f7750</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
+          <t xml:space="preserve">ห้ามลบสินค้า/ช่องเก็บที่ยังมีของ และใส่ไอคอนถังขยะ</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5321,12 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9d2f5bc</t>
+          <t xml:space="preserve">3a1af5d</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้กับปุ่มออกจากระบบไปท้ายแถบเมนูซ้าย</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5338,12 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">faa0057</t>
+          <t xml:space="preserve">9d2f5bc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
+          <t xml:space="preserve">หน้ารับ/เบิก/โอน เปลี่ยนเป็นตารางทีละบรรทัด</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5355,12 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2293a5a</t>
+          <t xml:space="preserve">faa0057</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
+          <t xml:space="preserve">โดน 400 แล้วลดรูปคำขอทีละขั้น แทนการเดาจากข้อความ</t>
         </is>
       </c>
     </row>
@@ -5332,12 +5372,12 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ded63b1</t>
+          <t xml:space="preserve">2293a5a</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
+          <t xml:space="preserve">รับมือ Google ปลดระวางรุ่น ให้ระบบบอกวิธีแก้เอง</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5389,12 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ea4fbbe</t>
+          <t xml:space="preserve">ded63b1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
+          <t xml:space="preserve">ลอง API หลายเวอร์ชัน และแสดงเหตุผลจริงจาก Google</t>
         </is>
       </c>
     </row>
@@ -5366,12 +5406,12 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">68c7eb8</t>
+          <t xml:space="preserve">ea4fbbe</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
+          <t xml:space="preserve">เปลี่ยนโมเดลเริ่มต้นเป็น gemini-2.5-flash และปิด thinking ให้ครบ</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5423,12 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f59a2d5</t>
+          <t xml:space="preserve">68c7eb8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
+          <t xml:space="preserve">แก้บั๊ก รายชื่อโมเดลไม่เคยถูกต่อท้ายข้อความ error</t>
         </is>
       </c>
     </row>
@@ -5400,12 +5440,12 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">dff3fd0</t>
+          <t xml:space="preserve">f59a2d5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
+          <t xml:space="preserve">เก็บกวาดชื่อหน่วยงานที่ยังหลงเหลือ</t>
         </is>
       </c>
     </row>
@@ -5417,12 +5457,12 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">37b3857</t>
+          <t xml:space="preserve">dff3fd0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
+          <t xml:space="preserve">แก้ช่องกรอกจำนวนในตารางที่ตัวเลขหายไป</t>
         </is>
       </c>
     </row>
@@ -5434,12 +5474,12 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9f11cd4</t>
+          <t xml:space="preserve">37b3857</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
+          <t xml:space="preserve">ช่องกรอกจำนวนมีปุ่มลบ/บวกทุกที่</t>
         </is>
       </c>
     </row>
@@ -5451,29 +5491,29 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7219244</t>
+          <t xml:space="preserve">9f11cd4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
+          <t xml:space="preserve">เลือกสินค้าแบบพิมพ์ค้นหาได้ + หน้าปรับปรุงสินค้าเป็นตาราง</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-03</t>
+          <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">837dd71</t>
+          <t xml:space="preserve">7219244</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
+          <t xml:space="preserve">ผู้ช่วย AI บอกได้เองว่าคีย์นี้ใช้โมเดลไหนได้</t>
         </is>
       </c>
     </row>
@@ -5485,12 +5525,12 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">44b12b6</t>
+          <t xml:space="preserve">837dd71</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
+          <t xml:space="preserve">เปลี่ยนชื่อเป็น Ultra ERP + ธีมสี + ช่วงวันที่แดชบอร์ด + เลขที่บิล POS</t>
         </is>
       </c>
     </row>
@@ -5502,12 +5542,12 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">99ed882</t>
+          <t xml:space="preserve">44b12b6</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
+          <t xml:space="preserve">แก้แถบคั่นหน้า POS ที่ลากปรับขนาดไม่ได้จริง</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5559,12 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">524f627</t>
+          <t xml:space="preserve">99ed882</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
+          <t xml:space="preserve">หน้า POS ลากปรับความกว้างแผงบิลได้</t>
         </is>
       </c>
     </row>
@@ -5536,12 +5576,12 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a4e6ae0</t>
+          <t xml:space="preserve">524f627</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
+          <t xml:space="preserve">กำหนดคลังและที่เก็บประจำของสินค้าได้ แล้วหน้าจออื่นเลือกตามให้</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5593,12 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">c2d0497</t>
+          <t xml:space="preserve">a4e6ae0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
+          <t xml:space="preserve">เติมที่เก็บสินค้าในหน้าจอที่ยังเหลือ</t>
         </is>
       </c>
     </row>
@@ -5570,12 +5610,12 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">148a6e6</t>
+          <t xml:space="preserve">c2d0497</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
+          <t xml:space="preserve">คลังสินค้ากับที่เก็บต้องไปด้วยกันตลอด</t>
         </is>
       </c>
     </row>
@@ -5587,12 +5627,12 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2c8d559</t>
+          <t xml:space="preserve">148a6e6</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
+          <t xml:space="preserve">เพิ่ม app/favicon.ico ให้ไอคอนบนแท็บคมขึ้น</t>
         </is>
       </c>
     </row>
@@ -5604,12 +5644,12 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">bfbc686</t>
+          <t xml:space="preserve">2c8d559</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
+          <t xml:space="preserve">แก้บั๊ก service worker แคชไอคอนแบบ cache-first จนรูปใหม่ไม่เคยขึ้น</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5661,12 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0f8c7b2</t>
+          <t xml:space="preserve">bfbc686</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
+          <t xml:space="preserve">ทำการ์ดพรีวิวตอนแชร์ลิงก์ใน LINE (Open Graph)</t>
         </is>
       </c>
     </row>
@@ -5638,29 +5678,29 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">0a9a9f4</t>
+          <t xml:space="preserve">0f8c7b2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
+          <t xml:space="preserve">เปลี่ยนไอคอนเว็บมาใช้ภาพ ERP.jpg</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">36aee24</t>
+          <t xml:space="preserve">0a9a9f4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
+          <t xml:space="preserve">ทำให้ติดตั้งเป็นแอปได้ (PWA)</t>
         </is>
       </c>
     </row>
@@ -5672,12 +5712,12 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1f5b02b</t>
+          <t xml:space="preserve">36aee24</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
+          <t xml:space="preserve">ย้ายชื่อผู้ใช้และปุ่มออกจากระบบไปมุมขวาล่าง</t>
         </is>
       </c>
     </row>
@@ -5689,29 +5729,29 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7c96318</t>
+          <t xml:space="preserve">1f5b02b</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
+          <t xml:space="preserve">แก้ลำดับการตรวจใน /api/chat และแจ้งสถานะตั้งแต่เปิดแผงแชท</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-01</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">130f3ea</t>
+          <t xml:space="preserve">7c96318</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
+          <t xml:space="preserve">เพิ่มผู้ช่วย AI (Chatbot ด้วย Gemini)</t>
         </is>
       </c>
     </row>
@@ -5723,12 +5763,12 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9c49288</t>
+          <t xml:space="preserve">130f3ea</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
+          <t xml:space="preserve">ตรวจทาน ProjectPlan.txt ให้ตรงกับของจริง</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5780,12 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3433dc8</t>
+          <t xml:space="preserve">9c49288</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
+          <t xml:space="preserve">แก้บั๊ก SQL: ชื่อ policy ต้องใช้ %I ไม่ใช่ %L</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5797,12 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">a362093</t>
+          <t xml:space="preserve">3433dc8</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
+          <t xml:space="preserve">รวมเหลือไฟล์ SQL เดียว ปิดช่องโหว่ขายเกินสต็อก และเพิ่มตัวตรวจสอบระบบในแอป</t>
         </is>
       </c>
     </row>
@@ -5774,29 +5814,29 @@
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">cf764d5</t>
+          <t xml:space="preserve">a362093</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
+          <t xml:space="preserve">แก้ PGRST205: ตารางใหม่ที่ยังไม่มี ไม่ควรทำให้ทั้งระบบใช้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-08-28</t>
+          <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3a0ac85</t>
+          <t xml:space="preserve">cf764d5</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
+          <t xml:space="preserve">เพิ่มหน้าจอผังที่เก็บสินค้า และหน้าจอขายสินค้า POS</t>
         </is>
       </c>
     </row>
@@ -5808,12 +5848,12 @@
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">f304aa0</t>
+          <t xml:space="preserve">3a0ac85</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: ยืนยันใช้งานกับ Supabase จริงได้แล้ว</t>
         </is>
       </c>
     </row>
@@ -5825,12 +5865,12 @@
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1e98b03</t>
+          <t xml:space="preserve">f304aa0</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
+          <t xml:space="preserve">ทำ fix-permissions.sql ให้ล้มไม่ได้ และสรุปผลเป็นตารางเดียว</t>
         </is>
       </c>
     </row>
@@ -5842,12 +5882,12 @@
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4598764</t>
+          <t xml:space="preserve">1e98b03</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
+          <t xml:space="preserve">อัปเดต ProjectPlan.txt: บันทึกสาเหตุและวิธีแก้ปัญหา 403</t>
         </is>
       </c>
     </row>
@@ -5859,27 +5899,44 @@
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7eb8597</t>
+          <t xml:space="preserve">4598764</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+          <t xml:space="preserve">แก้ 403: เพิ่ม GRANT ระดับตาราง และแสดงสาเหตุจริงของ error</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2026-08-28</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">7eb8597</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยน login เป็น Supabase Auth และย้ายข้อมูลขึ้น Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr" s="2">
+      <c r="B100" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">6a64db3</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr" s="2">
+      <c r="C100" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">first commit</t>
         </is>
